--- a/templates/input_usaha.contoh.xlsx
+++ b/templates/input_usaha.contoh.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="petunjuk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gabungan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="input_usaha" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contoh" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nama Wilayah" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="opsi" sheetId="5" state="hidden" r:id="rId5"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -466,7 +466,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Judul kolom (tab gabungan)</t>
+          <t>Judul kolom (tab input_usaha)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Isi '-' kalau tidak ada nomor.</t>
+          <t>Isi '-' kalau tidak ada nomor (mode normal mengisi '-' otomatis kalau kosong; mode murni tidak).</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>opsional</t>
+          <t>bersyarat</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kosong atau 'Tidak Ada'.</t>
+          <t>'Tidak Ada'. Hanya dipakai di SLS yang punya daftar UMKM prelist (mode murni: wajib kalau form memunculkannya).</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1673,22 +1673,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Pilih dari Master KBLI</t>
+          <t>13. d. Apa input yang digunakan?</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>kbli</t>
+          <t>input_produksi</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>WAJIB</t>
+          <t>bersyarat</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>WAJIB. Kode KBLI 5 digit.</t>
+          <t>WAJIB kalau 13b1 = '1. Ya' (usaha memproduksi barang), mis. 'singkong, minyak goreng'.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -1699,25 +1699,103 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
+          <t>13. e. Bagaimana proses produksinya?</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>proses_produksi</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB kalau 13b1 = '1. Ya', mis. 'mengupas, mengiris, menggoreng, mengemas'.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>13. f. Apa produk utama yang dihasilkan?</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>produk</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB (murni)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Produk utama. Mode normal: kosong = disalin dari 13a. Mode murni: WAJIB.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Pilih dari Master KBLI</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>kbli</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB. Kode KBLI 5 digit.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>14. a. Apa jaringan usaha dari usaha/perusahaan ini?</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>jaringan</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>WAJIB</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Pilih dari dropdown.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Tunggal
 2. Kantor pusat
@@ -1728,121 +1806,28 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>16. a. Apakah usaha/perusahaan ini menggunakan internet dalam menjalankan usaha?</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>internet</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Kalau '1. Ya': 16b1-16b6 &amp; 16c wajib, minimal satu 16b = '1. Ya'.</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>16. b1. Menerima pesanan barang/jasa</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>internet_pesanan</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>bersyarat</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Hanya kalau 16a = '1. Ya'.</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>16. b2. Produksi barang/jasa</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>internet_produksi</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>bersyarat</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Hanya kalau 16a = '1. Ya'.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>16. b3. Distribusi barang/jasa</t>
+          <t>16. a. Apakah usaha/perusahaan ini menggunakan internet dalam menjalankan usaha?</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>internet_distribusi</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>bersyarat</t>
+          <t>WAJIB</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Hanya kalau 16a = '1. Ya'.</t>
+          <t>Kalau '1. Ya': 16b1-16b6 &amp; 16c wajib, minimal satu 16b = '1. Ya'.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -1858,12 +1843,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>16. b4. Membeli bahan baku online</t>
+          <t>16. b1. Menerima pesanan barang/jasa</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>internet_beli</t>
+          <t>internet_pesanan</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1889,12 +1874,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>16. b5. Promosi</t>
+          <t>16. b2. Produksi barang/jasa</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>internet_promosi</t>
+          <t>internet_produksi</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1920,12 +1905,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>16. b6. Lainnya</t>
+          <t>16. b3. Distribusi barang/jasa</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>internet_lainnya</t>
+          <t>internet_distribusi</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1951,12 +1936,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16. c. Apakah usaha/perusahaan ini memanfaatkan teknologi digital Aritifical Intelligence (AI), Internet of Things (IoT), big data, printer 3D, blockchain, atau cloud computing?</t>
+          <t>16. b4. Membeli bahan baku online</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>digital</t>
+          <t>internet_beli</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1982,25 +1967,118 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
+          <t>16. b5. Promosi</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>internet_promosi</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Hanya kalau 16a = '1. Ya'.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>16. b6. Lainnya</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>internet_lainnya</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Hanya kalau 16a = '1. Ya'.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>16. c. Apakah usaha/perusahaan ini memanfaatkan teknologi digital Aritifical Intelligence (AI), Internet of Things (IoT), big data, printer 3D, blockchain, atau cloud computing?</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Hanya kalau 16a = '1. Ya'.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>17. a. Apakah usaha/perusahaan ini memproduksi barang/jasa yang ramah lingkungan?</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>produksi_lingkungan</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>WAJIB</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Pilih dari dropdown.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Ya, seluruhnya
 2. Ya, sebagian
@@ -2008,124 +2086,293 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>17. b. Apakah usaha/perusahaan ini menggunakan input untuk tujuan perlindungan lingkungan dan/atau pembelian barang dan jasa yang ramah lingkungan?</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>perlindungan_lingkungan</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Pilih dari dropdown.</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>18. Apakah usaha/perusahaan ini menggunakan produk karya seni, sastra, desain, teknologi atau warisan budaya, baik diproduksi sendiri maupun oleh pihak lain?</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>produk_seni</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Pilih dari dropdown.</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>21. Apakah usaha/perusahaan ini bermitra dengan Koperasi Desa/Kelurahan Merah Putih (KDKMP)?</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>mitra_kdkmp</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Pilih dari dropdown.</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
+          <t>17. b. Apakah usaha/perusahaan ini menggunakan input untuk tujuan perlindungan lingkungan dan/atau pembelian barang dan jasa yang ramah lingkungan?</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>perlindungan_lingkungan</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Pilih dari dropdown.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>18. Apakah usaha/perusahaan ini menggunakan produk karya seni, sastra, desain, teknologi atau warisan budaya, baik diproduksi sendiri maupun oleh pihak lain?</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>produk_seni</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Pilih dari dropdown.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>19. a. Apakah usaha/perusahaan ini menghasilkan produk bersertifikat halal?</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>halal</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Hanya ditanyakan form utk kategori usaha tertentu (BPJPH). Kosong: mode normal pakai default config, mode murni baris di-skip kalau form memunculkannya.</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya, oleh BPJPH
+2. Ya, bukan oleh BPJPH
+3. Tidak/Belum
+4. Dalam proses</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>19. b. Berapa jumlah varian produk yang sudah bersertifikat halal BPJPH?</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>sudah_halal</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Bilangan bulat; wajib kalau form memunculkannya (19a = Ya).</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>19. c. Berapa jumlah varian produk yang belum bersertifikat halal BPJPH?</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>belum_halal</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Bilangan bulat (kategori tertentu).</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>20. a. Apakah usaha/perusahaan ini memiliki izin edar?</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>izin_edar</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Hanya ditanyakan form utk kategori usaha tertentu (BPOM, mis. perdagangan &amp; makanan).</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya, oleh BPOM
+2. Ya, bukan oleh BPOM
+3. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>20. b. Berapa jumlah varian produk yang sudah memiliki izin edar BPOM?</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>sudah_bpom</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Bilangan bulat (kalau form memunculkannya).</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>20. c. Berapa jumlah varian produk yang belum memiliki izin edar BPOM?</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>belum_bpom</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>bersyarat</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Bilangan bulat; form memintanya di semua jawaban 20a.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>21. Apakah usaha/perusahaan ini bermitra dengan Koperasi Desa/Kelurahan Merah Putih (KDKMP)?</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>mitra_kdkmp</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Pilih dari dropdown.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22. Apakah usaha/perusahaan ini terlibat dalam program Makan Bergizi Gratis (MBG)?</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>peran_mbg</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>WAJIB</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Pilih dari dropdown.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Ya, sebagai SATUAN PELAYANAN PEMENUHAN GIZI (SPPG)
 2. Ya, sebagai supplier
@@ -2135,267 +2382,18 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>23. a. Penjualan dan/atau pembelian barang</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>barang_non_pddk</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Pilih dari dropdown.</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>23. b. Penjualan jasa</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>jasa_non_pddk</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Pilih dari dropdown.</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>23. c. Pembelian jasa</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>beli_jasa_non_pddk</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Pilih dari dropdown.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>1. Ya
-2. Tidak</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24. a1. Pekerja laki-laki</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>tk_laki</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Bilangan bulat. 24a1+24b1 harus = 24a2+24b2.</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24. b1. Pekerja perempuan</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>tk_pr</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Bilangan bulat.</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24. a2. Pekerja dibayar</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>tk_dibayar</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Bilangan bulat.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24. b2. Pekerja tidak dibayar</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>tk_tdk_dibayar</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Bilangan bulat.</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>25. Tahun berapa usaha/perusahaan ini mulai beroperasi secara komersial?</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>tahun_operasi</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>4 digit. Tahun berjalan TIDAK didukung (form memakai rincian 30-33 bulanan).</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>idsubsls</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>idsubsls</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>WAJIB. 16 digit, format TEKS (bukan angka).</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-    </row>
     <row r="67">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>26. a. Total upah dan gaji, serta jaminan sosial pegawai</t>
+          <t>23. a. Penjualan dan/atau pembelian barang</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>gaji</t>
+          <t>barang_non_pddk</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2405,10 +2403,15 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Rupiah, bilangan bulat tanpa titik.</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
+          <t>Pilih dari dropdown.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -2416,12 +2419,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>26. b. Biaya produksi</t>
+          <t>23. b. Penjualan jasa</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>biaya_produksi</t>
+          <t>jasa_non_pddk</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2431,10 +2434,15 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Rupiah.</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>Pilih dari dropdown.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -2442,12 +2450,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>26. c. Biaya pembelian barang yang terjual</t>
+          <t>23. c. Pembelian jasa</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>biaya_pembelian</t>
+          <t>beli_jasa_non_pddk</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2457,10 +2465,15 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Rupiah.</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
+          <t>Pilih dari dropdown.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Ya
+2. Tidak</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -2468,12 +2481,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>26. d. Biaya operasional (air, listrik, gas, internet, pulsa, pemeliharaan, biaya angkutan, dll.)</t>
+          <t>24. a1. Pekerja laki-laki</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>operasional</t>
+          <t>tk_laki</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2483,7 +2496,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Rupiah.</t>
+          <t>Bilangan bulat. 24a1+24b1 harus = 24a2+24b2.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -2494,12 +2507,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>26. e. Biaya non-operasional</t>
+          <t>24. b1. Pekerja perempuan</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>non_operasional</t>
+          <t>tk_pr</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2509,7 +2522,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Rupiah. Total 26a-26e minimal 100.000.</t>
+          <t>Bilangan bulat.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -2520,12 +2533,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27. a. Nilai produksi/pendapatan/penjualan barang dan jasa</t>
+          <t>24. a2. Pekerja dibayar</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>nilai_pendapatan</t>
+          <t>tk_dibayar</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2535,7 +2548,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Rupiah.</t>
+          <t>Bilangan bulat.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -2546,12 +2559,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27. b. Pendapatan lainnya yang dihasilkan perusahaan</t>
+          <t>24. b2. Pekerja tidak dibayar</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>pendapatan_lain</t>
+          <t>tk_tdk_dibayar</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2561,7 +2574,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Rupiah. Total 27a+27b minimal 100.000.</t>
+          <t>Bilangan bulat.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -2572,12 +2585,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>27. d. Berapa persentase pendapatan yang dilakukan secara online ?</t>
+          <t>25. Tahun berapa usaha/perusahaan ini mulai beroperasi secara komersial?</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>pendapatan_online</t>
+          <t>tahun_operasi</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2587,7 +2600,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>0-100.</t>
+          <t>4 digit. Tahun berjalan TIDAK didukung (form memakai rincian 30-33 bulanan).</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -2598,12 +2611,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>28. a. Nilai aset tanah dan bangunan pada 31 Desember 2025</t>
+          <t>idsubsls</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>aset_usaha_thn</t>
+          <t>idsubsls</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -2613,7 +2626,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Rupiah.</t>
+          <t>WAJIB. 16 digit, format TEKS (bukan angka).</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -2624,12 +2637,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>28. b. Nilai aset selain tanah dan bangunan pada 31 Desember 2025</t>
+          <t>26. a. Total upah dan gaji, serta jaminan sosial pegawai</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>aset_lain_thn</t>
+          <t>gaji</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2639,7 +2652,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Rupiah.</t>
+          <t>Rupiah, bilangan bulat tanpa titik.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -2650,12 +2663,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>28. d. Berapa luas tanah yang dikuasai dan digunakan untuk kegiatan usaha pada 31 Desember 2025 ? (m2)</t>
+          <t>26. b. Biaya produksi</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>luas_tanah_thn</t>
+          <t>biaya_produksi</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2665,7 +2678,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>m2, bilangan bulat.</t>
+          <t>Rupiah.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -2676,12 +2689,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>29. a. Pribadi/Perorangan</t>
+          <t>26. c. Biaya pembelian barang yang terjual</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>pribadi</t>
+          <t>biaya_pembelian</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2691,7 +2704,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Persen. 29a-29f harus berjumlah 100.</t>
+          <t>Rupiah. KBLI kategori B-F (golongan 05-43) &amp; golongan 56: form TIDAK punya 26c — isi 0 dan masukkan biaya pembelian ke 26b.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -2702,12 +2715,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>29. b. Lembaga Nonprofit yang Melayani Rumah Tangga</t>
+          <t>26. d. Biaya operasional (air, listrik, gas, internet, pulsa, pemeliharaan, biaya angkutan, dll.)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>non_profit</t>
+          <t>operasional</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -2717,7 +2730,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Persen.</t>
+          <t>Rupiah.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -2728,12 +2741,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>29. c. Korporasi Publik</t>
+          <t>26. e. Biaya non-operasional</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>publik</t>
+          <t>non_operasional</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2743,7 +2756,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Persen.</t>
+          <t>Rupiah. Total 26a-26e minimal 100.000.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -2754,12 +2767,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>29. d. Korporasi Non Publik</t>
+          <t>27. a. Nilai produksi/pendapatan/penjualan barang dan jasa</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>non_publik</t>
+          <t>nilai_pendapatan</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2769,7 +2782,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Persen.</t>
+          <t>Rupiah.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -2780,12 +2793,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>29. e. Pemerintah</t>
+          <t>27. b. Pendapatan lainnya yang dihasilkan perusahaan</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>pemerintah</t>
+          <t>pendapatan_lain</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -2795,7 +2808,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Persen.</t>
+          <t>Rupiah. Total 27a+27b minimal 100.000.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -2806,12 +2819,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>29. f. Asing</t>
+          <t>27. d. Berapa persentase pendapatan yang dilakukan secara online ?</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>asing</t>
+          <t>pendapatan_online</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2821,7 +2834,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Persen.</t>
+          <t>0-100.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -2832,60 +2845,301 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
+          <t>28. a. Nilai aset tanah dan bangunan pada 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>aset_usaha_thn</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Rupiah.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>28. b. Nilai aset selain tanah dan bangunan pada 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>aset_lain_thn</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Rupiah.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>28. d. Berapa luas tanah yang dikuasai dan digunakan untuk kegiatan usaha pada 31 Desember 2025 ? (m2)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>luas_tanah_thn</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>m2, bilangan bulat.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>29. a. Pribadi/Perorangan</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>pribadi</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Persen. 29a-29f harus berjumlah 100.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>29. b. Lembaga Nonprofit yang Melayani Rumah Tangga</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>non_profit</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Persen.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>29. c. Korporasi Publik</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>publik</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Persen.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>29. d. Korporasi Non Publik</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>non_publik</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Persen.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>29. e. Pemerintah</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>pemerintah</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Persen.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>29. f. Asing</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>asing</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>WAJIB</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Persen.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>Nama Pemberi Informasi</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>nama_info_list</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>opsional</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Hanya 'Lainnya'.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Lainnya</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Cara pakai: isi tab 'gabungan' mulai baris 2 (satu baris = satu usaha/dokumen). Nilai = jawaban FINAL per rincian form (tidak ada kalkulasi 10%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="3" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Cara pakai: isi tab 'input_usaha' mulai baris 2 (satu baris = satu usaha/dokumen, jenis usaha apa pun). Nilai = jawaban FINAL per rincian form hasil pendataan lapangan (tidak ada kalkulasi 10%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Mode murni (GABUNGAN_MODE_MURNI = True di inti/config_lokal.py): SEMUA isian diambil dari sheet, tanpa aturan/default skrip. Kolom 'bersyarat' wajib diisi kalau form memunculkan rinciannya — kalau kosong, baris di-skip (tidak ditebak).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>Teks opsi harus PERSIS seperti di dropdown (termasuk nomor &amp; titik), mis. '2. Tidak'.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="3" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>Kolom kode (idsubsls, kodepos, NIK, HP, KBLI) berformat TEKS; jangan diubah ke angka.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Periksa tanpa browser: python input_gabungan/main_gabungan.py --sumber Agenda.xlsx --cek</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="3" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Periksa tanpa browser: python input_gabungan/main_gabungan.py --sumber input_usaha.xlsx --cek</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>Google Sheets: File &gt; Import &gt; unggah file ini, lalu File &gt; Download &gt; .xlsx setelah diisi.</t>
         </is>
@@ -2902,7 +3156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE501"/>
+  <dimension ref="A1:CN501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2988,6 +3242,15 @@
     <col width="24" customWidth="1" min="81" max="81"/>
     <col width="24" customWidth="1" min="82" max="82"/>
     <col width="24" customWidth="1" min="83" max="83"/>
+    <col width="24" customWidth="1" min="84" max="84"/>
+    <col width="24" customWidth="1" min="85" max="85"/>
+    <col width="24" customWidth="1" min="86" max="86"/>
+    <col width="24" customWidth="1" min="87" max="87"/>
+    <col width="24" customWidth="1" min="88" max="88"/>
+    <col width="24" customWidth="1" min="89" max="89"/>
+    <col width="24" customWidth="1" min="90" max="90"/>
+    <col width="24" customWidth="1" min="91" max="91"/>
+    <col width="24" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1">
@@ -3198,210 +3461,255 @@
       </c>
       <c r="AP1" s="4" t="inlineStr">
         <is>
+          <t>13. d. Apa input yang digunakan?</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>13. e. Bagaimana proses produksinya?</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>13. f. Apa produk utama yang dihasilkan?</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
           <t>Pilih dari Master KBLI</t>
         </is>
       </c>
-      <c r="AQ1" s="4" t="inlineStr">
+      <c r="AT1" s="4" t="inlineStr">
         <is>
           <t>14. a. Apa jaringan usaha dari usaha/perusahaan ini?</t>
         </is>
       </c>
-      <c r="AR1" s="4" t="inlineStr">
+      <c r="AU1" s="4" t="inlineStr">
         <is>
           <t>16. a. Apakah usaha/perusahaan ini menggunakan internet dalam menjalankan usaha?</t>
         </is>
       </c>
-      <c r="AS1" s="4" t="inlineStr">
+      <c r="AV1" s="4" t="inlineStr">
         <is>
           <t>16. b1. Menerima pesanan barang/jasa</t>
         </is>
       </c>
-      <c r="AT1" s="4" t="inlineStr">
+      <c r="AW1" s="4" t="inlineStr">
         <is>
           <t>16. b2. Produksi barang/jasa</t>
         </is>
       </c>
-      <c r="AU1" s="4" t="inlineStr">
+      <c r="AX1" s="4" t="inlineStr">
         <is>
           <t>16. b3. Distribusi barang/jasa</t>
         </is>
       </c>
-      <c r="AV1" s="4" t="inlineStr">
+      <c r="AY1" s="4" t="inlineStr">
         <is>
           <t>16. b4. Membeli bahan baku online</t>
         </is>
       </c>
-      <c r="AW1" s="4" t="inlineStr">
+      <c r="AZ1" s="4" t="inlineStr">
         <is>
           <t>16. b5. Promosi</t>
         </is>
       </c>
-      <c r="AX1" s="4" t="inlineStr">
+      <c r="BA1" s="4" t="inlineStr">
         <is>
           <t>16. b6. Lainnya</t>
         </is>
       </c>
-      <c r="AY1" s="4" t="inlineStr">
+      <c r="BB1" s="4" t="inlineStr">
         <is>
           <t>16. c. Apakah usaha/perusahaan ini memanfaatkan teknologi digital Aritifical Intelligence (AI), Internet of Things (IoT), big data, printer 3D, blockchain, atau cloud computing?</t>
         </is>
       </c>
-      <c r="AZ1" s="4" t="inlineStr">
+      <c r="BC1" s="4" t="inlineStr">
         <is>
           <t>17. a. Apakah usaha/perusahaan ini memproduksi barang/jasa yang ramah lingkungan?</t>
         </is>
       </c>
-      <c r="BA1" s="4" t="inlineStr">
+      <c r="BD1" s="4" t="inlineStr">
         <is>
           <t>17. b. Apakah usaha/perusahaan ini menggunakan input untuk tujuan perlindungan lingkungan dan/atau pembelian barang dan jasa yang ramah lingkungan?</t>
         </is>
       </c>
-      <c r="BB1" s="4" t="inlineStr">
+      <c r="BE1" s="4" t="inlineStr">
         <is>
           <t>18. Apakah usaha/perusahaan ini menggunakan produk karya seni, sastra, desain, teknologi atau warisan budaya, baik diproduksi sendiri maupun oleh pihak lain?</t>
         </is>
       </c>
-      <c r="BC1" s="4" t="inlineStr">
+      <c r="BF1" s="4" t="inlineStr">
+        <is>
+          <t>19. a. Apakah usaha/perusahaan ini menghasilkan produk bersertifikat halal?</t>
+        </is>
+      </c>
+      <c r="BG1" s="4" t="inlineStr">
+        <is>
+          <t>19. b. Berapa jumlah varian produk yang sudah bersertifikat halal BPJPH?</t>
+        </is>
+      </c>
+      <c r="BH1" s="4" t="inlineStr">
+        <is>
+          <t>19. c. Berapa jumlah varian produk yang belum bersertifikat halal BPJPH?</t>
+        </is>
+      </c>
+      <c r="BI1" s="4" t="inlineStr">
+        <is>
+          <t>20. a. Apakah usaha/perusahaan ini memiliki izin edar?</t>
+        </is>
+      </c>
+      <c r="BJ1" s="4" t="inlineStr">
+        <is>
+          <t>20. b. Berapa jumlah varian produk yang sudah memiliki izin edar BPOM?</t>
+        </is>
+      </c>
+      <c r="BK1" s="4" t="inlineStr">
+        <is>
+          <t>20. c. Berapa jumlah varian produk yang belum memiliki izin edar BPOM?</t>
+        </is>
+      </c>
+      <c r="BL1" s="4" t="inlineStr">
         <is>
           <t>21. Apakah usaha/perusahaan ini bermitra dengan Koperasi Desa/Kelurahan Merah Putih (KDKMP)?</t>
         </is>
       </c>
-      <c r="BD1" s="4" t="inlineStr">
+      <c r="BM1" s="4" t="inlineStr">
         <is>
           <t>22. Apakah usaha/perusahaan ini terlibat dalam program Makan Bergizi Gratis (MBG)?</t>
         </is>
       </c>
-      <c r="BE1" s="4" t="inlineStr">
+      <c r="BN1" s="4" t="inlineStr">
         <is>
           <t>23. a. Penjualan dan/atau pembelian barang</t>
         </is>
       </c>
-      <c r="BF1" s="4" t="inlineStr">
+      <c r="BO1" s="4" t="inlineStr">
         <is>
           <t>23. b. Penjualan jasa</t>
         </is>
       </c>
-      <c r="BG1" s="4" t="inlineStr">
+      <c r="BP1" s="4" t="inlineStr">
         <is>
           <t>23. c. Pembelian jasa</t>
         </is>
       </c>
-      <c r="BH1" s="4" t="inlineStr">
+      <c r="BQ1" s="4" t="inlineStr">
         <is>
           <t>24. a1. Pekerja laki-laki</t>
         </is>
       </c>
-      <c r="BI1" s="4" t="inlineStr">
+      <c r="BR1" s="4" t="inlineStr">
         <is>
           <t>24. b1. Pekerja perempuan</t>
         </is>
       </c>
-      <c r="BJ1" s="4" t="inlineStr">
+      <c r="BS1" s="4" t="inlineStr">
         <is>
           <t>24. a2. Pekerja dibayar</t>
         </is>
       </c>
-      <c r="BK1" s="4" t="inlineStr">
+      <c r="BT1" s="4" t="inlineStr">
         <is>
           <t>24. b2. Pekerja tidak dibayar</t>
         </is>
       </c>
-      <c r="BL1" s="4" t="inlineStr">
+      <c r="BU1" s="4" t="inlineStr">
         <is>
           <t>25. Tahun berapa usaha/perusahaan ini mulai beroperasi secara komersial?</t>
         </is>
       </c>
-      <c r="BM1" s="4" t="inlineStr">
+      <c r="BV1" s="4" t="inlineStr">
         <is>
           <t>idsubsls</t>
         </is>
       </c>
-      <c r="BN1" s="4" t="inlineStr">
+      <c r="BW1" s="4" t="inlineStr">
         <is>
           <t>26. a. Total upah dan gaji, serta jaminan sosial pegawai</t>
         </is>
       </c>
-      <c r="BO1" s="4" t="inlineStr">
+      <c r="BX1" s="4" t="inlineStr">
         <is>
           <t>26. b. Biaya produksi</t>
         </is>
       </c>
-      <c r="BP1" s="4" t="inlineStr">
+      <c r="BY1" s="4" t="inlineStr">
         <is>
           <t>26. c. Biaya pembelian barang yang terjual</t>
         </is>
       </c>
-      <c r="BQ1" s="4" t="inlineStr">
+      <c r="BZ1" s="4" t="inlineStr">
         <is>
           <t>26. d. Biaya operasional (air, listrik, gas, internet, pulsa, pemeliharaan, biaya angkutan, dll.)</t>
         </is>
       </c>
-      <c r="BR1" s="4" t="inlineStr">
+      <c r="CA1" s="4" t="inlineStr">
         <is>
           <t>26. e. Biaya non-operasional</t>
         </is>
       </c>
-      <c r="BS1" s="4" t="inlineStr">
+      <c r="CB1" s="4" t="inlineStr">
         <is>
           <t>27. a. Nilai produksi/pendapatan/penjualan barang dan jasa</t>
         </is>
       </c>
-      <c r="BT1" s="4" t="inlineStr">
+      <c r="CC1" s="4" t="inlineStr">
         <is>
           <t>27. b. Pendapatan lainnya yang dihasilkan perusahaan</t>
         </is>
       </c>
-      <c r="BU1" s="4" t="inlineStr">
+      <c r="CD1" s="4" t="inlineStr">
         <is>
           <t>27. d. Berapa persentase pendapatan yang dilakukan secara online ?</t>
         </is>
       </c>
-      <c r="BV1" s="4" t="inlineStr">
+      <c r="CE1" s="4" t="inlineStr">
         <is>
           <t>28. a. Nilai aset tanah dan bangunan pada 31 Desember 2025</t>
         </is>
       </c>
-      <c r="BW1" s="4" t="inlineStr">
+      <c r="CF1" s="4" t="inlineStr">
         <is>
           <t>28. b. Nilai aset selain tanah dan bangunan pada 31 Desember 2025</t>
         </is>
       </c>
-      <c r="BX1" s="4" t="inlineStr">
+      <c r="CG1" s="4" t="inlineStr">
         <is>
           <t>28. d. Berapa luas tanah yang dikuasai dan digunakan untuk kegiatan usaha pada 31 Desember 2025 ? (m2)</t>
         </is>
       </c>
-      <c r="BY1" s="4" t="inlineStr">
+      <c r="CH1" s="4" t="inlineStr">
         <is>
           <t>29. a. Pribadi/Perorangan</t>
         </is>
       </c>
-      <c r="BZ1" s="4" t="inlineStr">
+      <c r="CI1" s="4" t="inlineStr">
         <is>
           <t>29. b. Lembaga Nonprofit yang Melayani Rumah Tangga</t>
         </is>
       </c>
-      <c r="CA1" s="4" t="inlineStr">
+      <c r="CJ1" s="4" t="inlineStr">
         <is>
           <t>29. c. Korporasi Publik</t>
         </is>
       </c>
-      <c r="CB1" s="4" t="inlineStr">
+      <c r="CK1" s="4" t="inlineStr">
         <is>
           <t>29. d. Korporasi Non Publik</t>
         </is>
       </c>
-      <c r="CC1" s="4" t="inlineStr">
+      <c r="CL1" s="4" t="inlineStr">
         <is>
           <t>29. e. Pemerintah</t>
         </is>
       </c>
-      <c r="CD1" s="4" t="inlineStr">
+      <c r="CM1" s="4" t="inlineStr">
         <is>
           <t>29. f. Asing</t>
         </is>
       </c>
-      <c r="CE1" s="4" t="inlineStr">
+      <c r="CN1" s="4" t="inlineStr">
         <is>
           <t>Nama Pemberi Informasi</t>
         </is>
@@ -3418,8 +3726,8 @@
       <c r="Y2" s="5" t="n"/>
       <c r="AB2" s="5" t="n"/>
       <c r="AI2" s="5" t="n"/>
-      <c r="AP2" s="5" t="n"/>
-      <c r="BM2" s="5" t="n"/>
+      <c r="AS2" s="5" t="n"/>
+      <c r="BV2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="C3" s="5" t="n"/>
@@ -3432,8 +3740,8 @@
       <c r="Y3" s="5" t="n"/>
       <c r="AB3" s="5" t="n"/>
       <c r="AI3" s="5" t="n"/>
-      <c r="AP3" s="5" t="n"/>
-      <c r="BM3" s="5" t="n"/>
+      <c r="AS3" s="5" t="n"/>
+      <c r="BV3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="C4" s="5" t="n"/>
@@ -3446,8 +3754,8 @@
       <c r="Y4" s="5" t="n"/>
       <c r="AB4" s="5" t="n"/>
       <c r="AI4" s="5" t="n"/>
-      <c r="AP4" s="5" t="n"/>
-      <c r="BM4" s="5" t="n"/>
+      <c r="AS4" s="5" t="n"/>
+      <c r="BV4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="5" t="n"/>
@@ -3460,8 +3768,8 @@
       <c r="Y5" s="5" t="n"/>
       <c r="AB5" s="5" t="n"/>
       <c r="AI5" s="5" t="n"/>
-      <c r="AP5" s="5" t="n"/>
-      <c r="BM5" s="5" t="n"/>
+      <c r="AS5" s="5" t="n"/>
+      <c r="BV5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="5" t="n"/>
@@ -3474,8 +3782,8 @@
       <c r="Y6" s="5" t="n"/>
       <c r="AB6" s="5" t="n"/>
       <c r="AI6" s="5" t="n"/>
-      <c r="AP6" s="5" t="n"/>
-      <c r="BM6" s="5" t="n"/>
+      <c r="AS6" s="5" t="n"/>
+      <c r="BV6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="5" t="n"/>
@@ -3488,8 +3796,8 @@
       <c r="Y7" s="5" t="n"/>
       <c r="AB7" s="5" t="n"/>
       <c r="AI7" s="5" t="n"/>
-      <c r="AP7" s="5" t="n"/>
-      <c r="BM7" s="5" t="n"/>
+      <c r="AS7" s="5" t="n"/>
+      <c r="BV7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="5" t="n"/>
@@ -3502,8 +3810,8 @@
       <c r="Y8" s="5" t="n"/>
       <c r="AB8" s="5" t="n"/>
       <c r="AI8" s="5" t="n"/>
-      <c r="AP8" s="5" t="n"/>
-      <c r="BM8" s="5" t="n"/>
+      <c r="AS8" s="5" t="n"/>
+      <c r="BV8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="C9" s="5" t="n"/>
@@ -3516,8 +3824,8 @@
       <c r="Y9" s="5" t="n"/>
       <c r="AB9" s="5" t="n"/>
       <c r="AI9" s="5" t="n"/>
-      <c r="AP9" s="5" t="n"/>
-      <c r="BM9" s="5" t="n"/>
+      <c r="AS9" s="5" t="n"/>
+      <c r="BV9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="C10" s="5" t="n"/>
@@ -3530,8 +3838,8 @@
       <c r="Y10" s="5" t="n"/>
       <c r="AB10" s="5" t="n"/>
       <c r="AI10" s="5" t="n"/>
-      <c r="AP10" s="5" t="n"/>
-      <c r="BM10" s="5" t="n"/>
+      <c r="AS10" s="5" t="n"/>
+      <c r="BV10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="C11" s="5" t="n"/>
@@ -3544,8 +3852,8 @@
       <c r="Y11" s="5" t="n"/>
       <c r="AB11" s="5" t="n"/>
       <c r="AI11" s="5" t="n"/>
-      <c r="AP11" s="5" t="n"/>
-      <c r="BM11" s="5" t="n"/>
+      <c r="AS11" s="5" t="n"/>
+      <c r="BV11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
@@ -3558,8 +3866,8 @@
       <c r="Y12" s="5" t="n"/>
       <c r="AB12" s="5" t="n"/>
       <c r="AI12" s="5" t="n"/>
-      <c r="AP12" s="5" t="n"/>
-      <c r="BM12" s="5" t="n"/>
+      <c r="AS12" s="5" t="n"/>
+      <c r="BV12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="5" t="n"/>
@@ -3572,8 +3880,8 @@
       <c r="Y13" s="5" t="n"/>
       <c r="AB13" s="5" t="n"/>
       <c r="AI13" s="5" t="n"/>
-      <c r="AP13" s="5" t="n"/>
-      <c r="BM13" s="5" t="n"/>
+      <c r="AS13" s="5" t="n"/>
+      <c r="BV13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="C14" s="5" t="n"/>
@@ -3586,8 +3894,8 @@
       <c r="Y14" s="5" t="n"/>
       <c r="AB14" s="5" t="n"/>
       <c r="AI14" s="5" t="n"/>
-      <c r="AP14" s="5" t="n"/>
-      <c r="BM14" s="5" t="n"/>
+      <c r="AS14" s="5" t="n"/>
+      <c r="BV14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="C15" s="5" t="n"/>
@@ -3600,8 +3908,8 @@
       <c r="Y15" s="5" t="n"/>
       <c r="AB15" s="5" t="n"/>
       <c r="AI15" s="5" t="n"/>
-      <c r="AP15" s="5" t="n"/>
-      <c r="BM15" s="5" t="n"/>
+      <c r="AS15" s="5" t="n"/>
+      <c r="BV15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="C16" s="5" t="n"/>
@@ -3614,8 +3922,8 @@
       <c r="Y16" s="5" t="n"/>
       <c r="AB16" s="5" t="n"/>
       <c r="AI16" s="5" t="n"/>
-      <c r="AP16" s="5" t="n"/>
-      <c r="BM16" s="5" t="n"/>
+      <c r="AS16" s="5" t="n"/>
+      <c r="BV16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="C17" s="5" t="n"/>
@@ -3628,8 +3936,8 @@
       <c r="Y17" s="5" t="n"/>
       <c r="AB17" s="5" t="n"/>
       <c r="AI17" s="5" t="n"/>
-      <c r="AP17" s="5" t="n"/>
-      <c r="BM17" s="5" t="n"/>
+      <c r="AS17" s="5" t="n"/>
+      <c r="BV17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="5" t="n"/>
@@ -3642,8 +3950,8 @@
       <c r="Y18" s="5" t="n"/>
       <c r="AB18" s="5" t="n"/>
       <c r="AI18" s="5" t="n"/>
-      <c r="AP18" s="5" t="n"/>
-      <c r="BM18" s="5" t="n"/>
+      <c r="AS18" s="5" t="n"/>
+      <c r="BV18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="C19" s="5" t="n"/>
@@ -3656,8 +3964,8 @@
       <c r="Y19" s="5" t="n"/>
       <c r="AB19" s="5" t="n"/>
       <c r="AI19" s="5" t="n"/>
-      <c r="AP19" s="5" t="n"/>
-      <c r="BM19" s="5" t="n"/>
+      <c r="AS19" s="5" t="n"/>
+      <c r="BV19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="5" t="n"/>
@@ -3670,8 +3978,8 @@
       <c r="Y20" s="5" t="n"/>
       <c r="AB20" s="5" t="n"/>
       <c r="AI20" s="5" t="n"/>
-      <c r="AP20" s="5" t="n"/>
-      <c r="BM20" s="5" t="n"/>
+      <c r="AS20" s="5" t="n"/>
+      <c r="BV20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="5" t="n"/>
@@ -3684,8 +3992,8 @@
       <c r="Y21" s="5" t="n"/>
       <c r="AB21" s="5" t="n"/>
       <c r="AI21" s="5" t="n"/>
-      <c r="AP21" s="5" t="n"/>
-      <c r="BM21" s="5" t="n"/>
+      <c r="AS21" s="5" t="n"/>
+      <c r="BV21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="C22" s="5" t="n"/>
@@ -3698,8 +4006,8 @@
       <c r="Y22" s="5" t="n"/>
       <c r="AB22" s="5" t="n"/>
       <c r="AI22" s="5" t="n"/>
-      <c r="AP22" s="5" t="n"/>
-      <c r="BM22" s="5" t="n"/>
+      <c r="AS22" s="5" t="n"/>
+      <c r="BV22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="C23" s="5" t="n"/>
@@ -3712,8 +4020,8 @@
       <c r="Y23" s="5" t="n"/>
       <c r="AB23" s="5" t="n"/>
       <c r="AI23" s="5" t="n"/>
-      <c r="AP23" s="5" t="n"/>
-      <c r="BM23" s="5" t="n"/>
+      <c r="AS23" s="5" t="n"/>
+      <c r="BV23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="C24" s="5" t="n"/>
@@ -3726,8 +4034,8 @@
       <c r="Y24" s="5" t="n"/>
       <c r="AB24" s="5" t="n"/>
       <c r="AI24" s="5" t="n"/>
-      <c r="AP24" s="5" t="n"/>
-      <c r="BM24" s="5" t="n"/>
+      <c r="AS24" s="5" t="n"/>
+      <c r="BV24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="C25" s="5" t="n"/>
@@ -3740,8 +4048,8 @@
       <c r="Y25" s="5" t="n"/>
       <c r="AB25" s="5" t="n"/>
       <c r="AI25" s="5" t="n"/>
-      <c r="AP25" s="5" t="n"/>
-      <c r="BM25" s="5" t="n"/>
+      <c r="AS25" s="5" t="n"/>
+      <c r="BV25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="C26" s="5" t="n"/>
@@ -3754,8 +4062,8 @@
       <c r="Y26" s="5" t="n"/>
       <c r="AB26" s="5" t="n"/>
       <c r="AI26" s="5" t="n"/>
-      <c r="AP26" s="5" t="n"/>
-      <c r="BM26" s="5" t="n"/>
+      <c r="AS26" s="5" t="n"/>
+      <c r="BV26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="C27" s="5" t="n"/>
@@ -3768,8 +4076,8 @@
       <c r="Y27" s="5" t="n"/>
       <c r="AB27" s="5" t="n"/>
       <c r="AI27" s="5" t="n"/>
-      <c r="AP27" s="5" t="n"/>
-      <c r="BM27" s="5" t="n"/>
+      <c r="AS27" s="5" t="n"/>
+      <c r="BV27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="C28" s="5" t="n"/>
@@ -3782,8 +4090,8 @@
       <c r="Y28" s="5" t="n"/>
       <c r="AB28" s="5" t="n"/>
       <c r="AI28" s="5" t="n"/>
-      <c r="AP28" s="5" t="n"/>
-      <c r="BM28" s="5" t="n"/>
+      <c r="AS28" s="5" t="n"/>
+      <c r="BV28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="C29" s="5" t="n"/>
@@ -3796,8 +4104,8 @@
       <c r="Y29" s="5" t="n"/>
       <c r="AB29" s="5" t="n"/>
       <c r="AI29" s="5" t="n"/>
-      <c r="AP29" s="5" t="n"/>
-      <c r="BM29" s="5" t="n"/>
+      <c r="AS29" s="5" t="n"/>
+      <c r="BV29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="C30" s="5" t="n"/>
@@ -3810,8 +4118,8 @@
       <c r="Y30" s="5" t="n"/>
       <c r="AB30" s="5" t="n"/>
       <c r="AI30" s="5" t="n"/>
-      <c r="AP30" s="5" t="n"/>
-      <c r="BM30" s="5" t="n"/>
+      <c r="AS30" s="5" t="n"/>
+      <c r="BV30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="C31" s="5" t="n"/>
@@ -3824,8 +4132,8 @@
       <c r="Y31" s="5" t="n"/>
       <c r="AB31" s="5" t="n"/>
       <c r="AI31" s="5" t="n"/>
-      <c r="AP31" s="5" t="n"/>
-      <c r="BM31" s="5" t="n"/>
+      <c r="AS31" s="5" t="n"/>
+      <c r="BV31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="C32" s="5" t="n"/>
@@ -3838,8 +4146,8 @@
       <c r="Y32" s="5" t="n"/>
       <c r="AB32" s="5" t="n"/>
       <c r="AI32" s="5" t="n"/>
-      <c r="AP32" s="5" t="n"/>
-      <c r="BM32" s="5" t="n"/>
+      <c r="AS32" s="5" t="n"/>
+      <c r="BV32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="C33" s="5" t="n"/>
@@ -3852,8 +4160,8 @@
       <c r="Y33" s="5" t="n"/>
       <c r="AB33" s="5" t="n"/>
       <c r="AI33" s="5" t="n"/>
-      <c r="AP33" s="5" t="n"/>
-      <c r="BM33" s="5" t="n"/>
+      <c r="AS33" s="5" t="n"/>
+      <c r="BV33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="C34" s="5" t="n"/>
@@ -3866,8 +4174,8 @@
       <c r="Y34" s="5" t="n"/>
       <c r="AB34" s="5" t="n"/>
       <c r="AI34" s="5" t="n"/>
-      <c r="AP34" s="5" t="n"/>
-      <c r="BM34" s="5" t="n"/>
+      <c r="AS34" s="5" t="n"/>
+      <c r="BV34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="C35" s="5" t="n"/>
@@ -3880,8 +4188,8 @@
       <c r="Y35" s="5" t="n"/>
       <c r="AB35" s="5" t="n"/>
       <c r="AI35" s="5" t="n"/>
-      <c r="AP35" s="5" t="n"/>
-      <c r="BM35" s="5" t="n"/>
+      <c r="AS35" s="5" t="n"/>
+      <c r="BV35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="C36" s="5" t="n"/>
@@ -3894,8 +4202,8 @@
       <c r="Y36" s="5" t="n"/>
       <c r="AB36" s="5" t="n"/>
       <c r="AI36" s="5" t="n"/>
-      <c r="AP36" s="5" t="n"/>
-      <c r="BM36" s="5" t="n"/>
+      <c r="AS36" s="5" t="n"/>
+      <c r="BV36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="C37" s="5" t="n"/>
@@ -3908,8 +4216,8 @@
       <c r="Y37" s="5" t="n"/>
       <c r="AB37" s="5" t="n"/>
       <c r="AI37" s="5" t="n"/>
-      <c r="AP37" s="5" t="n"/>
-      <c r="BM37" s="5" t="n"/>
+      <c r="AS37" s="5" t="n"/>
+      <c r="BV37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="C38" s="5" t="n"/>
@@ -3922,8 +4230,8 @@
       <c r="Y38" s="5" t="n"/>
       <c r="AB38" s="5" t="n"/>
       <c r="AI38" s="5" t="n"/>
-      <c r="AP38" s="5" t="n"/>
-      <c r="BM38" s="5" t="n"/>
+      <c r="AS38" s="5" t="n"/>
+      <c r="BV38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="C39" s="5" t="n"/>
@@ -3936,8 +4244,8 @@
       <c r="Y39" s="5" t="n"/>
       <c r="AB39" s="5" t="n"/>
       <c r="AI39" s="5" t="n"/>
-      <c r="AP39" s="5" t="n"/>
-      <c r="BM39" s="5" t="n"/>
+      <c r="AS39" s="5" t="n"/>
+      <c r="BV39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="C40" s="5" t="n"/>
@@ -3950,8 +4258,8 @@
       <c r="Y40" s="5" t="n"/>
       <c r="AB40" s="5" t="n"/>
       <c r="AI40" s="5" t="n"/>
-      <c r="AP40" s="5" t="n"/>
-      <c r="BM40" s="5" t="n"/>
+      <c r="AS40" s="5" t="n"/>
+      <c r="BV40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="C41" s="5" t="n"/>
@@ -3964,8 +4272,8 @@
       <c r="Y41" s="5" t="n"/>
       <c r="AB41" s="5" t="n"/>
       <c r="AI41" s="5" t="n"/>
-      <c r="AP41" s="5" t="n"/>
-      <c r="BM41" s="5" t="n"/>
+      <c r="AS41" s="5" t="n"/>
+      <c r="BV41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="C42" s="5" t="n"/>
@@ -3978,8 +4286,8 @@
       <c r="Y42" s="5" t="n"/>
       <c r="AB42" s="5" t="n"/>
       <c r="AI42" s="5" t="n"/>
-      <c r="AP42" s="5" t="n"/>
-      <c r="BM42" s="5" t="n"/>
+      <c r="AS42" s="5" t="n"/>
+      <c r="BV42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="C43" s="5" t="n"/>
@@ -3992,8 +4300,8 @@
       <c r="Y43" s="5" t="n"/>
       <c r="AB43" s="5" t="n"/>
       <c r="AI43" s="5" t="n"/>
-      <c r="AP43" s="5" t="n"/>
-      <c r="BM43" s="5" t="n"/>
+      <c r="AS43" s="5" t="n"/>
+      <c r="BV43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="C44" s="5" t="n"/>
@@ -4006,8 +4314,8 @@
       <c r="Y44" s="5" t="n"/>
       <c r="AB44" s="5" t="n"/>
       <c r="AI44" s="5" t="n"/>
-      <c r="AP44" s="5" t="n"/>
-      <c r="BM44" s="5" t="n"/>
+      <c r="AS44" s="5" t="n"/>
+      <c r="BV44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="C45" s="5" t="n"/>
@@ -4020,8 +4328,8 @@
       <c r="Y45" s="5" t="n"/>
       <c r="AB45" s="5" t="n"/>
       <c r="AI45" s="5" t="n"/>
-      <c r="AP45" s="5" t="n"/>
-      <c r="BM45" s="5" t="n"/>
+      <c r="AS45" s="5" t="n"/>
+      <c r="BV45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="C46" s="5" t="n"/>
@@ -4034,8 +4342,8 @@
       <c r="Y46" s="5" t="n"/>
       <c r="AB46" s="5" t="n"/>
       <c r="AI46" s="5" t="n"/>
-      <c r="AP46" s="5" t="n"/>
-      <c r="BM46" s="5" t="n"/>
+      <c r="AS46" s="5" t="n"/>
+      <c r="BV46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="C47" s="5" t="n"/>
@@ -4048,8 +4356,8 @@
       <c r="Y47" s="5" t="n"/>
       <c r="AB47" s="5" t="n"/>
       <c r="AI47" s="5" t="n"/>
-      <c r="AP47" s="5" t="n"/>
-      <c r="BM47" s="5" t="n"/>
+      <c r="AS47" s="5" t="n"/>
+      <c r="BV47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="C48" s="5" t="n"/>
@@ -4062,8 +4370,8 @@
       <c r="Y48" s="5" t="n"/>
       <c r="AB48" s="5" t="n"/>
       <c r="AI48" s="5" t="n"/>
-      <c r="AP48" s="5" t="n"/>
-      <c r="BM48" s="5" t="n"/>
+      <c r="AS48" s="5" t="n"/>
+      <c r="BV48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="C49" s="5" t="n"/>
@@ -4076,8 +4384,8 @@
       <c r="Y49" s="5" t="n"/>
       <c r="AB49" s="5" t="n"/>
       <c r="AI49" s="5" t="n"/>
-      <c r="AP49" s="5" t="n"/>
-      <c r="BM49" s="5" t="n"/>
+      <c r="AS49" s="5" t="n"/>
+      <c r="BV49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="C50" s="5" t="n"/>
@@ -4090,8 +4398,8 @@
       <c r="Y50" s="5" t="n"/>
       <c r="AB50" s="5" t="n"/>
       <c r="AI50" s="5" t="n"/>
-      <c r="AP50" s="5" t="n"/>
-      <c r="BM50" s="5" t="n"/>
+      <c r="AS50" s="5" t="n"/>
+      <c r="BV50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="C51" s="5" t="n"/>
@@ -4104,8 +4412,8 @@
       <c r="Y51" s="5" t="n"/>
       <c r="AB51" s="5" t="n"/>
       <c r="AI51" s="5" t="n"/>
-      <c r="AP51" s="5" t="n"/>
-      <c r="BM51" s="5" t="n"/>
+      <c r="AS51" s="5" t="n"/>
+      <c r="BV51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="C52" s="5" t="n"/>
@@ -4118,8 +4426,8 @@
       <c r="Y52" s="5" t="n"/>
       <c r="AB52" s="5" t="n"/>
       <c r="AI52" s="5" t="n"/>
-      <c r="AP52" s="5" t="n"/>
-      <c r="BM52" s="5" t="n"/>
+      <c r="AS52" s="5" t="n"/>
+      <c r="BV52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="C53" s="5" t="n"/>
@@ -4132,8 +4440,8 @@
       <c r="Y53" s="5" t="n"/>
       <c r="AB53" s="5" t="n"/>
       <c r="AI53" s="5" t="n"/>
-      <c r="AP53" s="5" t="n"/>
-      <c r="BM53" s="5" t="n"/>
+      <c r="AS53" s="5" t="n"/>
+      <c r="BV53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="C54" s="5" t="n"/>
@@ -4146,8 +4454,8 @@
       <c r="Y54" s="5" t="n"/>
       <c r="AB54" s="5" t="n"/>
       <c r="AI54" s="5" t="n"/>
-      <c r="AP54" s="5" t="n"/>
-      <c r="BM54" s="5" t="n"/>
+      <c r="AS54" s="5" t="n"/>
+      <c r="BV54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="C55" s="5" t="n"/>
@@ -4160,8 +4468,8 @@
       <c r="Y55" s="5" t="n"/>
       <c r="AB55" s="5" t="n"/>
       <c r="AI55" s="5" t="n"/>
-      <c r="AP55" s="5" t="n"/>
-      <c r="BM55" s="5" t="n"/>
+      <c r="AS55" s="5" t="n"/>
+      <c r="BV55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="C56" s="5" t="n"/>
@@ -4174,8 +4482,8 @@
       <c r="Y56" s="5" t="n"/>
       <c r="AB56" s="5" t="n"/>
       <c r="AI56" s="5" t="n"/>
-      <c r="AP56" s="5" t="n"/>
-      <c r="BM56" s="5" t="n"/>
+      <c r="AS56" s="5" t="n"/>
+      <c r="BV56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="C57" s="5" t="n"/>
@@ -4188,8 +4496,8 @@
       <c r="Y57" s="5" t="n"/>
       <c r="AB57" s="5" t="n"/>
       <c r="AI57" s="5" t="n"/>
-      <c r="AP57" s="5" t="n"/>
-      <c r="BM57" s="5" t="n"/>
+      <c r="AS57" s="5" t="n"/>
+      <c r="BV57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="C58" s="5" t="n"/>
@@ -4202,8 +4510,8 @@
       <c r="Y58" s="5" t="n"/>
       <c r="AB58" s="5" t="n"/>
       <c r="AI58" s="5" t="n"/>
-      <c r="AP58" s="5" t="n"/>
-      <c r="BM58" s="5" t="n"/>
+      <c r="AS58" s="5" t="n"/>
+      <c r="BV58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="C59" s="5" t="n"/>
@@ -4216,8 +4524,8 @@
       <c r="Y59" s="5" t="n"/>
       <c r="AB59" s="5" t="n"/>
       <c r="AI59" s="5" t="n"/>
-      <c r="AP59" s="5" t="n"/>
-      <c r="BM59" s="5" t="n"/>
+      <c r="AS59" s="5" t="n"/>
+      <c r="BV59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="C60" s="5" t="n"/>
@@ -4230,8 +4538,8 @@
       <c r="Y60" s="5" t="n"/>
       <c r="AB60" s="5" t="n"/>
       <c r="AI60" s="5" t="n"/>
-      <c r="AP60" s="5" t="n"/>
-      <c r="BM60" s="5" t="n"/>
+      <c r="AS60" s="5" t="n"/>
+      <c r="BV60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="C61" s="5" t="n"/>
@@ -4244,8 +4552,8 @@
       <c r="Y61" s="5" t="n"/>
       <c r="AB61" s="5" t="n"/>
       <c r="AI61" s="5" t="n"/>
-      <c r="AP61" s="5" t="n"/>
-      <c r="BM61" s="5" t="n"/>
+      <c r="AS61" s="5" t="n"/>
+      <c r="BV61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="C62" s="5" t="n"/>
@@ -4258,8 +4566,8 @@
       <c r="Y62" s="5" t="n"/>
       <c r="AB62" s="5" t="n"/>
       <c r="AI62" s="5" t="n"/>
-      <c r="AP62" s="5" t="n"/>
-      <c r="BM62" s="5" t="n"/>
+      <c r="AS62" s="5" t="n"/>
+      <c r="BV62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="C63" s="5" t="n"/>
@@ -4272,8 +4580,8 @@
       <c r="Y63" s="5" t="n"/>
       <c r="AB63" s="5" t="n"/>
       <c r="AI63" s="5" t="n"/>
-      <c r="AP63" s="5" t="n"/>
-      <c r="BM63" s="5" t="n"/>
+      <c r="AS63" s="5" t="n"/>
+      <c r="BV63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="C64" s="5" t="n"/>
@@ -4286,8 +4594,8 @@
       <c r="Y64" s="5" t="n"/>
       <c r="AB64" s="5" t="n"/>
       <c r="AI64" s="5" t="n"/>
-      <c r="AP64" s="5" t="n"/>
-      <c r="BM64" s="5" t="n"/>
+      <c r="AS64" s="5" t="n"/>
+      <c r="BV64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="C65" s="5" t="n"/>
@@ -4300,8 +4608,8 @@
       <c r="Y65" s="5" t="n"/>
       <c r="AB65" s="5" t="n"/>
       <c r="AI65" s="5" t="n"/>
-      <c r="AP65" s="5" t="n"/>
-      <c r="BM65" s="5" t="n"/>
+      <c r="AS65" s="5" t="n"/>
+      <c r="BV65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="C66" s="5" t="n"/>
@@ -4314,8 +4622,8 @@
       <c r="Y66" s="5" t="n"/>
       <c r="AB66" s="5" t="n"/>
       <c r="AI66" s="5" t="n"/>
-      <c r="AP66" s="5" t="n"/>
-      <c r="BM66" s="5" t="n"/>
+      <c r="AS66" s="5" t="n"/>
+      <c r="BV66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="C67" s="5" t="n"/>
@@ -4328,8 +4636,8 @@
       <c r="Y67" s="5" t="n"/>
       <c r="AB67" s="5" t="n"/>
       <c r="AI67" s="5" t="n"/>
-      <c r="AP67" s="5" t="n"/>
-      <c r="BM67" s="5" t="n"/>
+      <c r="AS67" s="5" t="n"/>
+      <c r="BV67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="C68" s="5" t="n"/>
@@ -4342,8 +4650,8 @@
       <c r="Y68" s="5" t="n"/>
       <c r="AB68" s="5" t="n"/>
       <c r="AI68" s="5" t="n"/>
-      <c r="AP68" s="5" t="n"/>
-      <c r="BM68" s="5" t="n"/>
+      <c r="AS68" s="5" t="n"/>
+      <c r="BV68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="C69" s="5" t="n"/>
@@ -4356,8 +4664,8 @@
       <c r="Y69" s="5" t="n"/>
       <c r="AB69" s="5" t="n"/>
       <c r="AI69" s="5" t="n"/>
-      <c r="AP69" s="5" t="n"/>
-      <c r="BM69" s="5" t="n"/>
+      <c r="AS69" s="5" t="n"/>
+      <c r="BV69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="C70" s="5" t="n"/>
@@ -4370,8 +4678,8 @@
       <c r="Y70" s="5" t="n"/>
       <c r="AB70" s="5" t="n"/>
       <c r="AI70" s="5" t="n"/>
-      <c r="AP70" s="5" t="n"/>
-      <c r="BM70" s="5" t="n"/>
+      <c r="AS70" s="5" t="n"/>
+      <c r="BV70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="C71" s="5" t="n"/>
@@ -4384,8 +4692,8 @@
       <c r="Y71" s="5" t="n"/>
       <c r="AB71" s="5" t="n"/>
       <c r="AI71" s="5" t="n"/>
-      <c r="AP71" s="5" t="n"/>
-      <c r="BM71" s="5" t="n"/>
+      <c r="AS71" s="5" t="n"/>
+      <c r="BV71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="C72" s="5" t="n"/>
@@ -4398,8 +4706,8 @@
       <c r="Y72" s="5" t="n"/>
       <c r="AB72" s="5" t="n"/>
       <c r="AI72" s="5" t="n"/>
-      <c r="AP72" s="5" t="n"/>
-      <c r="BM72" s="5" t="n"/>
+      <c r="AS72" s="5" t="n"/>
+      <c r="BV72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="C73" s="5" t="n"/>
@@ -4412,8 +4720,8 @@
       <c r="Y73" s="5" t="n"/>
       <c r="AB73" s="5" t="n"/>
       <c r="AI73" s="5" t="n"/>
-      <c r="AP73" s="5" t="n"/>
-      <c r="BM73" s="5" t="n"/>
+      <c r="AS73" s="5" t="n"/>
+      <c r="BV73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="C74" s="5" t="n"/>
@@ -4426,8 +4734,8 @@
       <c r="Y74" s="5" t="n"/>
       <c r="AB74" s="5" t="n"/>
       <c r="AI74" s="5" t="n"/>
-      <c r="AP74" s="5" t="n"/>
-      <c r="BM74" s="5" t="n"/>
+      <c r="AS74" s="5" t="n"/>
+      <c r="BV74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="C75" s="5" t="n"/>
@@ -4440,8 +4748,8 @@
       <c r="Y75" s="5" t="n"/>
       <c r="AB75" s="5" t="n"/>
       <c r="AI75" s="5" t="n"/>
-      <c r="AP75" s="5" t="n"/>
-      <c r="BM75" s="5" t="n"/>
+      <c r="AS75" s="5" t="n"/>
+      <c r="BV75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="C76" s="5" t="n"/>
@@ -4454,8 +4762,8 @@
       <c r="Y76" s="5" t="n"/>
       <c r="AB76" s="5" t="n"/>
       <c r="AI76" s="5" t="n"/>
-      <c r="AP76" s="5" t="n"/>
-      <c r="BM76" s="5" t="n"/>
+      <c r="AS76" s="5" t="n"/>
+      <c r="BV76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="C77" s="5" t="n"/>
@@ -4468,8 +4776,8 @@
       <c r="Y77" s="5" t="n"/>
       <c r="AB77" s="5" t="n"/>
       <c r="AI77" s="5" t="n"/>
-      <c r="AP77" s="5" t="n"/>
-      <c r="BM77" s="5" t="n"/>
+      <c r="AS77" s="5" t="n"/>
+      <c r="BV77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="C78" s="5" t="n"/>
@@ -4482,8 +4790,8 @@
       <c r="Y78" s="5" t="n"/>
       <c r="AB78" s="5" t="n"/>
       <c r="AI78" s="5" t="n"/>
-      <c r="AP78" s="5" t="n"/>
-      <c r="BM78" s="5" t="n"/>
+      <c r="AS78" s="5" t="n"/>
+      <c r="BV78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="C79" s="5" t="n"/>
@@ -4496,8 +4804,8 @@
       <c r="Y79" s="5" t="n"/>
       <c r="AB79" s="5" t="n"/>
       <c r="AI79" s="5" t="n"/>
-      <c r="AP79" s="5" t="n"/>
-      <c r="BM79" s="5" t="n"/>
+      <c r="AS79" s="5" t="n"/>
+      <c r="BV79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="C80" s="5" t="n"/>
@@ -4510,8 +4818,8 @@
       <c r="Y80" s="5" t="n"/>
       <c r="AB80" s="5" t="n"/>
       <c r="AI80" s="5" t="n"/>
-      <c r="AP80" s="5" t="n"/>
-      <c r="BM80" s="5" t="n"/>
+      <c r="AS80" s="5" t="n"/>
+      <c r="BV80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="C81" s="5" t="n"/>
@@ -4524,8 +4832,8 @@
       <c r="Y81" s="5" t="n"/>
       <c r="AB81" s="5" t="n"/>
       <c r="AI81" s="5" t="n"/>
-      <c r="AP81" s="5" t="n"/>
-      <c r="BM81" s="5" t="n"/>
+      <c r="AS81" s="5" t="n"/>
+      <c r="BV81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="C82" s="5" t="n"/>
@@ -4538,8 +4846,8 @@
       <c r="Y82" s="5" t="n"/>
       <c r="AB82" s="5" t="n"/>
       <c r="AI82" s="5" t="n"/>
-      <c r="AP82" s="5" t="n"/>
-      <c r="BM82" s="5" t="n"/>
+      <c r="AS82" s="5" t="n"/>
+      <c r="BV82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="C83" s="5" t="n"/>
@@ -4552,8 +4860,8 @@
       <c r="Y83" s="5" t="n"/>
       <c r="AB83" s="5" t="n"/>
       <c r="AI83" s="5" t="n"/>
-      <c r="AP83" s="5" t="n"/>
-      <c r="BM83" s="5" t="n"/>
+      <c r="AS83" s="5" t="n"/>
+      <c r="BV83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="C84" s="5" t="n"/>
@@ -4566,8 +4874,8 @@
       <c r="Y84" s="5" t="n"/>
       <c r="AB84" s="5" t="n"/>
       <c r="AI84" s="5" t="n"/>
-      <c r="AP84" s="5" t="n"/>
-      <c r="BM84" s="5" t="n"/>
+      <c r="AS84" s="5" t="n"/>
+      <c r="BV84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="C85" s="5" t="n"/>
@@ -4580,8 +4888,8 @@
       <c r="Y85" s="5" t="n"/>
       <c r="AB85" s="5" t="n"/>
       <c r="AI85" s="5" t="n"/>
-      <c r="AP85" s="5" t="n"/>
-      <c r="BM85" s="5" t="n"/>
+      <c r="AS85" s="5" t="n"/>
+      <c r="BV85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="C86" s="5" t="n"/>
@@ -4594,8 +4902,8 @@
       <c r="Y86" s="5" t="n"/>
       <c r="AB86" s="5" t="n"/>
       <c r="AI86" s="5" t="n"/>
-      <c r="AP86" s="5" t="n"/>
-      <c r="BM86" s="5" t="n"/>
+      <c r="AS86" s="5" t="n"/>
+      <c r="BV86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="C87" s="5" t="n"/>
@@ -4608,8 +4916,8 @@
       <c r="Y87" s="5" t="n"/>
       <c r="AB87" s="5" t="n"/>
       <c r="AI87" s="5" t="n"/>
-      <c r="AP87" s="5" t="n"/>
-      <c r="BM87" s="5" t="n"/>
+      <c r="AS87" s="5" t="n"/>
+      <c r="BV87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="C88" s="5" t="n"/>
@@ -4622,8 +4930,8 @@
       <c r="Y88" s="5" t="n"/>
       <c r="AB88" s="5" t="n"/>
       <c r="AI88" s="5" t="n"/>
-      <c r="AP88" s="5" t="n"/>
-      <c r="BM88" s="5" t="n"/>
+      <c r="AS88" s="5" t="n"/>
+      <c r="BV88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="C89" s="5" t="n"/>
@@ -4636,8 +4944,8 @@
       <c r="Y89" s="5" t="n"/>
       <c r="AB89" s="5" t="n"/>
       <c r="AI89" s="5" t="n"/>
-      <c r="AP89" s="5" t="n"/>
-      <c r="BM89" s="5" t="n"/>
+      <c r="AS89" s="5" t="n"/>
+      <c r="BV89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="C90" s="5" t="n"/>
@@ -4650,8 +4958,8 @@
       <c r="Y90" s="5" t="n"/>
       <c r="AB90" s="5" t="n"/>
       <c r="AI90" s="5" t="n"/>
-      <c r="AP90" s="5" t="n"/>
-      <c r="BM90" s="5" t="n"/>
+      <c r="AS90" s="5" t="n"/>
+      <c r="BV90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="C91" s="5" t="n"/>
@@ -4664,8 +4972,8 @@
       <c r="Y91" s="5" t="n"/>
       <c r="AB91" s="5" t="n"/>
       <c r="AI91" s="5" t="n"/>
-      <c r="AP91" s="5" t="n"/>
-      <c r="BM91" s="5" t="n"/>
+      <c r="AS91" s="5" t="n"/>
+      <c r="BV91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="C92" s="5" t="n"/>
@@ -4678,8 +4986,8 @@
       <c r="Y92" s="5" t="n"/>
       <c r="AB92" s="5" t="n"/>
       <c r="AI92" s="5" t="n"/>
-      <c r="AP92" s="5" t="n"/>
-      <c r="BM92" s="5" t="n"/>
+      <c r="AS92" s="5" t="n"/>
+      <c r="BV92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="C93" s="5" t="n"/>
@@ -4692,8 +5000,8 @@
       <c r="Y93" s="5" t="n"/>
       <c r="AB93" s="5" t="n"/>
       <c r="AI93" s="5" t="n"/>
-      <c r="AP93" s="5" t="n"/>
-      <c r="BM93" s="5" t="n"/>
+      <c r="AS93" s="5" t="n"/>
+      <c r="BV93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="C94" s="5" t="n"/>
@@ -4706,8 +5014,8 @@
       <c r="Y94" s="5" t="n"/>
       <c r="AB94" s="5" t="n"/>
       <c r="AI94" s="5" t="n"/>
-      <c r="AP94" s="5" t="n"/>
-      <c r="BM94" s="5" t="n"/>
+      <c r="AS94" s="5" t="n"/>
+      <c r="BV94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="C95" s="5" t="n"/>
@@ -4720,8 +5028,8 @@
       <c r="Y95" s="5" t="n"/>
       <c r="AB95" s="5" t="n"/>
       <c r="AI95" s="5" t="n"/>
-      <c r="AP95" s="5" t="n"/>
-      <c r="BM95" s="5" t="n"/>
+      <c r="AS95" s="5" t="n"/>
+      <c r="BV95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="C96" s="5" t="n"/>
@@ -4734,8 +5042,8 @@
       <c r="Y96" s="5" t="n"/>
       <c r="AB96" s="5" t="n"/>
       <c r="AI96" s="5" t="n"/>
-      <c r="AP96" s="5" t="n"/>
-      <c r="BM96" s="5" t="n"/>
+      <c r="AS96" s="5" t="n"/>
+      <c r="BV96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="C97" s="5" t="n"/>
@@ -4748,8 +5056,8 @@
       <c r="Y97" s="5" t="n"/>
       <c r="AB97" s="5" t="n"/>
       <c r="AI97" s="5" t="n"/>
-      <c r="AP97" s="5" t="n"/>
-      <c r="BM97" s="5" t="n"/>
+      <c r="AS97" s="5" t="n"/>
+      <c r="BV97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="C98" s="5" t="n"/>
@@ -4762,8 +5070,8 @@
       <c r="Y98" s="5" t="n"/>
       <c r="AB98" s="5" t="n"/>
       <c r="AI98" s="5" t="n"/>
-      <c r="AP98" s="5" t="n"/>
-      <c r="BM98" s="5" t="n"/>
+      <c r="AS98" s="5" t="n"/>
+      <c r="BV98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="C99" s="5" t="n"/>
@@ -4776,8 +5084,8 @@
       <c r="Y99" s="5" t="n"/>
       <c r="AB99" s="5" t="n"/>
       <c r="AI99" s="5" t="n"/>
-      <c r="AP99" s="5" t="n"/>
-      <c r="BM99" s="5" t="n"/>
+      <c r="AS99" s="5" t="n"/>
+      <c r="BV99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="C100" s="5" t="n"/>
@@ -4790,8 +5098,8 @@
       <c r="Y100" s="5" t="n"/>
       <c r="AB100" s="5" t="n"/>
       <c r="AI100" s="5" t="n"/>
-      <c r="AP100" s="5" t="n"/>
-      <c r="BM100" s="5" t="n"/>
+      <c r="AS100" s="5" t="n"/>
+      <c r="BV100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="C101" s="5" t="n"/>
@@ -4804,8 +5112,8 @@
       <c r="Y101" s="5" t="n"/>
       <c r="AB101" s="5" t="n"/>
       <c r="AI101" s="5" t="n"/>
-      <c r="AP101" s="5" t="n"/>
-      <c r="BM101" s="5" t="n"/>
+      <c r="AS101" s="5" t="n"/>
+      <c r="BV101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="C102" s="5" t="n"/>
@@ -4818,8 +5126,8 @@
       <c r="Y102" s="5" t="n"/>
       <c r="AB102" s="5" t="n"/>
       <c r="AI102" s="5" t="n"/>
-      <c r="AP102" s="5" t="n"/>
-      <c r="BM102" s="5" t="n"/>
+      <c r="AS102" s="5" t="n"/>
+      <c r="BV102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="C103" s="5" t="n"/>
@@ -4832,8 +5140,8 @@
       <c r="Y103" s="5" t="n"/>
       <c r="AB103" s="5" t="n"/>
       <c r="AI103" s="5" t="n"/>
-      <c r="AP103" s="5" t="n"/>
-      <c r="BM103" s="5" t="n"/>
+      <c r="AS103" s="5" t="n"/>
+      <c r="BV103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="C104" s="5" t="n"/>
@@ -4846,8 +5154,8 @@
       <c r="Y104" s="5" t="n"/>
       <c r="AB104" s="5" t="n"/>
       <c r="AI104" s="5" t="n"/>
-      <c r="AP104" s="5" t="n"/>
-      <c r="BM104" s="5" t="n"/>
+      <c r="AS104" s="5" t="n"/>
+      <c r="BV104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="C105" s="5" t="n"/>
@@ -4860,8 +5168,8 @@
       <c r="Y105" s="5" t="n"/>
       <c r="AB105" s="5" t="n"/>
       <c r="AI105" s="5" t="n"/>
-      <c r="AP105" s="5" t="n"/>
-      <c r="BM105" s="5" t="n"/>
+      <c r="AS105" s="5" t="n"/>
+      <c r="BV105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="C106" s="5" t="n"/>
@@ -4874,8 +5182,8 @@
       <c r="Y106" s="5" t="n"/>
       <c r="AB106" s="5" t="n"/>
       <c r="AI106" s="5" t="n"/>
-      <c r="AP106" s="5" t="n"/>
-      <c r="BM106" s="5" t="n"/>
+      <c r="AS106" s="5" t="n"/>
+      <c r="BV106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="C107" s="5" t="n"/>
@@ -4888,8 +5196,8 @@
       <c r="Y107" s="5" t="n"/>
       <c r="AB107" s="5" t="n"/>
       <c r="AI107" s="5" t="n"/>
-      <c r="AP107" s="5" t="n"/>
-      <c r="BM107" s="5" t="n"/>
+      <c r="AS107" s="5" t="n"/>
+      <c r="BV107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="C108" s="5" t="n"/>
@@ -4902,8 +5210,8 @@
       <c r="Y108" s="5" t="n"/>
       <c r="AB108" s="5" t="n"/>
       <c r="AI108" s="5" t="n"/>
-      <c r="AP108" s="5" t="n"/>
-      <c r="BM108" s="5" t="n"/>
+      <c r="AS108" s="5" t="n"/>
+      <c r="BV108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="C109" s="5" t="n"/>
@@ -4916,8 +5224,8 @@
       <c r="Y109" s="5" t="n"/>
       <c r="AB109" s="5" t="n"/>
       <c r="AI109" s="5" t="n"/>
-      <c r="AP109" s="5" t="n"/>
-      <c r="BM109" s="5" t="n"/>
+      <c r="AS109" s="5" t="n"/>
+      <c r="BV109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="C110" s="5" t="n"/>
@@ -4930,8 +5238,8 @@
       <c r="Y110" s="5" t="n"/>
       <c r="AB110" s="5" t="n"/>
       <c r="AI110" s="5" t="n"/>
-      <c r="AP110" s="5" t="n"/>
-      <c r="BM110" s="5" t="n"/>
+      <c r="AS110" s="5" t="n"/>
+      <c r="BV110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="C111" s="5" t="n"/>
@@ -4944,8 +5252,8 @@
       <c r="Y111" s="5" t="n"/>
       <c r="AB111" s="5" t="n"/>
       <c r="AI111" s="5" t="n"/>
-      <c r="AP111" s="5" t="n"/>
-      <c r="BM111" s="5" t="n"/>
+      <c r="AS111" s="5" t="n"/>
+      <c r="BV111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="C112" s="5" t="n"/>
@@ -4958,8 +5266,8 @@
       <c r="Y112" s="5" t="n"/>
       <c r="AB112" s="5" t="n"/>
       <c r="AI112" s="5" t="n"/>
-      <c r="AP112" s="5" t="n"/>
-      <c r="BM112" s="5" t="n"/>
+      <c r="AS112" s="5" t="n"/>
+      <c r="BV112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="C113" s="5" t="n"/>
@@ -4972,8 +5280,8 @@
       <c r="Y113" s="5" t="n"/>
       <c r="AB113" s="5" t="n"/>
       <c r="AI113" s="5" t="n"/>
-      <c r="AP113" s="5" t="n"/>
-      <c r="BM113" s="5" t="n"/>
+      <c r="AS113" s="5" t="n"/>
+      <c r="BV113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="C114" s="5" t="n"/>
@@ -4986,8 +5294,8 @@
       <c r="Y114" s="5" t="n"/>
       <c r="AB114" s="5" t="n"/>
       <c r="AI114" s="5" t="n"/>
-      <c r="AP114" s="5" t="n"/>
-      <c r="BM114" s="5" t="n"/>
+      <c r="AS114" s="5" t="n"/>
+      <c r="BV114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="C115" s="5" t="n"/>
@@ -5000,8 +5308,8 @@
       <c r="Y115" s="5" t="n"/>
       <c r="AB115" s="5" t="n"/>
       <c r="AI115" s="5" t="n"/>
-      <c r="AP115" s="5" t="n"/>
-      <c r="BM115" s="5" t="n"/>
+      <c r="AS115" s="5" t="n"/>
+      <c r="BV115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="C116" s="5" t="n"/>
@@ -5014,8 +5322,8 @@
       <c r="Y116" s="5" t="n"/>
       <c r="AB116" s="5" t="n"/>
       <c r="AI116" s="5" t="n"/>
-      <c r="AP116" s="5" t="n"/>
-      <c r="BM116" s="5" t="n"/>
+      <c r="AS116" s="5" t="n"/>
+      <c r="BV116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="C117" s="5" t="n"/>
@@ -5028,8 +5336,8 @@
       <c r="Y117" s="5" t="n"/>
       <c r="AB117" s="5" t="n"/>
       <c r="AI117" s="5" t="n"/>
-      <c r="AP117" s="5" t="n"/>
-      <c r="BM117" s="5" t="n"/>
+      <c r="AS117" s="5" t="n"/>
+      <c r="BV117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="C118" s="5" t="n"/>
@@ -5042,8 +5350,8 @@
       <c r="Y118" s="5" t="n"/>
       <c r="AB118" s="5" t="n"/>
       <c r="AI118" s="5" t="n"/>
-      <c r="AP118" s="5" t="n"/>
-      <c r="BM118" s="5" t="n"/>
+      <c r="AS118" s="5" t="n"/>
+      <c r="BV118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="C119" s="5" t="n"/>
@@ -5056,8 +5364,8 @@
       <c r="Y119" s="5" t="n"/>
       <c r="AB119" s="5" t="n"/>
       <c r="AI119" s="5" t="n"/>
-      <c r="AP119" s="5" t="n"/>
-      <c r="BM119" s="5" t="n"/>
+      <c r="AS119" s="5" t="n"/>
+      <c r="BV119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="C120" s="5" t="n"/>
@@ -5070,8 +5378,8 @@
       <c r="Y120" s="5" t="n"/>
       <c r="AB120" s="5" t="n"/>
       <c r="AI120" s="5" t="n"/>
-      <c r="AP120" s="5" t="n"/>
-      <c r="BM120" s="5" t="n"/>
+      <c r="AS120" s="5" t="n"/>
+      <c r="BV120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="C121" s="5" t="n"/>
@@ -5084,8 +5392,8 @@
       <c r="Y121" s="5" t="n"/>
       <c r="AB121" s="5" t="n"/>
       <c r="AI121" s="5" t="n"/>
-      <c r="AP121" s="5" t="n"/>
-      <c r="BM121" s="5" t="n"/>
+      <c r="AS121" s="5" t="n"/>
+      <c r="BV121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="C122" s="5" t="n"/>
@@ -5098,8 +5406,8 @@
       <c r="Y122" s="5" t="n"/>
       <c r="AB122" s="5" t="n"/>
       <c r="AI122" s="5" t="n"/>
-      <c r="AP122" s="5" t="n"/>
-      <c r="BM122" s="5" t="n"/>
+      <c r="AS122" s="5" t="n"/>
+      <c r="BV122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="C123" s="5" t="n"/>
@@ -5112,8 +5420,8 @@
       <c r="Y123" s="5" t="n"/>
       <c r="AB123" s="5" t="n"/>
       <c r="AI123" s="5" t="n"/>
-      <c r="AP123" s="5" t="n"/>
-      <c r="BM123" s="5" t="n"/>
+      <c r="AS123" s="5" t="n"/>
+      <c r="BV123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="C124" s="5" t="n"/>
@@ -5126,8 +5434,8 @@
       <c r="Y124" s="5" t="n"/>
       <c r="AB124" s="5" t="n"/>
       <c r="AI124" s="5" t="n"/>
-      <c r="AP124" s="5" t="n"/>
-      <c r="BM124" s="5" t="n"/>
+      <c r="AS124" s="5" t="n"/>
+      <c r="BV124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="C125" s="5" t="n"/>
@@ -5140,8 +5448,8 @@
       <c r="Y125" s="5" t="n"/>
       <c r="AB125" s="5" t="n"/>
       <c r="AI125" s="5" t="n"/>
-      <c r="AP125" s="5" t="n"/>
-      <c r="BM125" s="5" t="n"/>
+      <c r="AS125" s="5" t="n"/>
+      <c r="BV125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="C126" s="5" t="n"/>
@@ -5154,8 +5462,8 @@
       <c r="Y126" s="5" t="n"/>
       <c r="AB126" s="5" t="n"/>
       <c r="AI126" s="5" t="n"/>
-      <c r="AP126" s="5" t="n"/>
-      <c r="BM126" s="5" t="n"/>
+      <c r="AS126" s="5" t="n"/>
+      <c r="BV126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="C127" s="5" t="n"/>
@@ -5168,8 +5476,8 @@
       <c r="Y127" s="5" t="n"/>
       <c r="AB127" s="5" t="n"/>
       <c r="AI127" s="5" t="n"/>
-      <c r="AP127" s="5" t="n"/>
-      <c r="BM127" s="5" t="n"/>
+      <c r="AS127" s="5" t="n"/>
+      <c r="BV127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="C128" s="5" t="n"/>
@@ -5182,8 +5490,8 @@
       <c r="Y128" s="5" t="n"/>
       <c r="AB128" s="5" t="n"/>
       <c r="AI128" s="5" t="n"/>
-      <c r="AP128" s="5" t="n"/>
-      <c r="BM128" s="5" t="n"/>
+      <c r="AS128" s="5" t="n"/>
+      <c r="BV128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="C129" s="5" t="n"/>
@@ -5196,8 +5504,8 @@
       <c r="Y129" s="5" t="n"/>
       <c r="AB129" s="5" t="n"/>
       <c r="AI129" s="5" t="n"/>
-      <c r="AP129" s="5" t="n"/>
-      <c r="BM129" s="5" t="n"/>
+      <c r="AS129" s="5" t="n"/>
+      <c r="BV129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="C130" s="5" t="n"/>
@@ -5210,8 +5518,8 @@
       <c r="Y130" s="5" t="n"/>
       <c r="AB130" s="5" t="n"/>
       <c r="AI130" s="5" t="n"/>
-      <c r="AP130" s="5" t="n"/>
-      <c r="BM130" s="5" t="n"/>
+      <c r="AS130" s="5" t="n"/>
+      <c r="BV130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="C131" s="5" t="n"/>
@@ -5224,8 +5532,8 @@
       <c r="Y131" s="5" t="n"/>
       <c r="AB131" s="5" t="n"/>
       <c r="AI131" s="5" t="n"/>
-      <c r="AP131" s="5" t="n"/>
-      <c r="BM131" s="5" t="n"/>
+      <c r="AS131" s="5" t="n"/>
+      <c r="BV131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="C132" s="5" t="n"/>
@@ -5238,8 +5546,8 @@
       <c r="Y132" s="5" t="n"/>
       <c r="AB132" s="5" t="n"/>
       <c r="AI132" s="5" t="n"/>
-      <c r="AP132" s="5" t="n"/>
-      <c r="BM132" s="5" t="n"/>
+      <c r="AS132" s="5" t="n"/>
+      <c r="BV132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="C133" s="5" t="n"/>
@@ -5252,8 +5560,8 @@
       <c r="Y133" s="5" t="n"/>
       <c r="AB133" s="5" t="n"/>
       <c r="AI133" s="5" t="n"/>
-      <c r="AP133" s="5" t="n"/>
-      <c r="BM133" s="5" t="n"/>
+      <c r="AS133" s="5" t="n"/>
+      <c r="BV133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="C134" s="5" t="n"/>
@@ -5266,8 +5574,8 @@
       <c r="Y134" s="5" t="n"/>
       <c r="AB134" s="5" t="n"/>
       <c r="AI134" s="5" t="n"/>
-      <c r="AP134" s="5" t="n"/>
-      <c r="BM134" s="5" t="n"/>
+      <c r="AS134" s="5" t="n"/>
+      <c r="BV134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="C135" s="5" t="n"/>
@@ -5280,8 +5588,8 @@
       <c r="Y135" s="5" t="n"/>
       <c r="AB135" s="5" t="n"/>
       <c r="AI135" s="5" t="n"/>
-      <c r="AP135" s="5" t="n"/>
-      <c r="BM135" s="5" t="n"/>
+      <c r="AS135" s="5" t="n"/>
+      <c r="BV135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="C136" s="5" t="n"/>
@@ -5294,8 +5602,8 @@
       <c r="Y136" s="5" t="n"/>
       <c r="AB136" s="5" t="n"/>
       <c r="AI136" s="5" t="n"/>
-      <c r="AP136" s="5" t="n"/>
-      <c r="BM136" s="5" t="n"/>
+      <c r="AS136" s="5" t="n"/>
+      <c r="BV136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="C137" s="5" t="n"/>
@@ -5308,8 +5616,8 @@
       <c r="Y137" s="5" t="n"/>
       <c r="AB137" s="5" t="n"/>
       <c r="AI137" s="5" t="n"/>
-      <c r="AP137" s="5" t="n"/>
-      <c r="BM137" s="5" t="n"/>
+      <c r="AS137" s="5" t="n"/>
+      <c r="BV137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="C138" s="5" t="n"/>
@@ -5322,8 +5630,8 @@
       <c r="Y138" s="5" t="n"/>
       <c r="AB138" s="5" t="n"/>
       <c r="AI138" s="5" t="n"/>
-      <c r="AP138" s="5" t="n"/>
-      <c r="BM138" s="5" t="n"/>
+      <c r="AS138" s="5" t="n"/>
+      <c r="BV138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="C139" s="5" t="n"/>
@@ -5336,8 +5644,8 @@
       <c r="Y139" s="5" t="n"/>
       <c r="AB139" s="5" t="n"/>
       <c r="AI139" s="5" t="n"/>
-      <c r="AP139" s="5" t="n"/>
-      <c r="BM139" s="5" t="n"/>
+      <c r="AS139" s="5" t="n"/>
+      <c r="BV139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="C140" s="5" t="n"/>
@@ -5350,8 +5658,8 @@
       <c r="Y140" s="5" t="n"/>
       <c r="AB140" s="5" t="n"/>
       <c r="AI140" s="5" t="n"/>
-      <c r="AP140" s="5" t="n"/>
-      <c r="BM140" s="5" t="n"/>
+      <c r="AS140" s="5" t="n"/>
+      <c r="BV140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="C141" s="5" t="n"/>
@@ -5364,8 +5672,8 @@
       <c r="Y141" s="5" t="n"/>
       <c r="AB141" s="5" t="n"/>
       <c r="AI141" s="5" t="n"/>
-      <c r="AP141" s="5" t="n"/>
-      <c r="BM141" s="5" t="n"/>
+      <c r="AS141" s="5" t="n"/>
+      <c r="BV141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="C142" s="5" t="n"/>
@@ -5378,8 +5686,8 @@
       <c r="Y142" s="5" t="n"/>
       <c r="AB142" s="5" t="n"/>
       <c r="AI142" s="5" t="n"/>
-      <c r="AP142" s="5" t="n"/>
-      <c r="BM142" s="5" t="n"/>
+      <c r="AS142" s="5" t="n"/>
+      <c r="BV142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="C143" s="5" t="n"/>
@@ -5392,8 +5700,8 @@
       <c r="Y143" s="5" t="n"/>
       <c r="AB143" s="5" t="n"/>
       <c r="AI143" s="5" t="n"/>
-      <c r="AP143" s="5" t="n"/>
-      <c r="BM143" s="5" t="n"/>
+      <c r="AS143" s="5" t="n"/>
+      <c r="BV143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="C144" s="5" t="n"/>
@@ -5406,8 +5714,8 @@
       <c r="Y144" s="5" t="n"/>
       <c r="AB144" s="5" t="n"/>
       <c r="AI144" s="5" t="n"/>
-      <c r="AP144" s="5" t="n"/>
-      <c r="BM144" s="5" t="n"/>
+      <c r="AS144" s="5" t="n"/>
+      <c r="BV144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="C145" s="5" t="n"/>
@@ -5420,8 +5728,8 @@
       <c r="Y145" s="5" t="n"/>
       <c r="AB145" s="5" t="n"/>
       <c r="AI145" s="5" t="n"/>
-      <c r="AP145" s="5" t="n"/>
-      <c r="BM145" s="5" t="n"/>
+      <c r="AS145" s="5" t="n"/>
+      <c r="BV145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="C146" s="5" t="n"/>
@@ -5434,8 +5742,8 @@
       <c r="Y146" s="5" t="n"/>
       <c r="AB146" s="5" t="n"/>
       <c r="AI146" s="5" t="n"/>
-      <c r="AP146" s="5" t="n"/>
-      <c r="BM146" s="5" t="n"/>
+      <c r="AS146" s="5" t="n"/>
+      <c r="BV146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="C147" s="5" t="n"/>
@@ -5448,8 +5756,8 @@
       <c r="Y147" s="5" t="n"/>
       <c r="AB147" s="5" t="n"/>
       <c r="AI147" s="5" t="n"/>
-      <c r="AP147" s="5" t="n"/>
-      <c r="BM147" s="5" t="n"/>
+      <c r="AS147" s="5" t="n"/>
+      <c r="BV147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="C148" s="5" t="n"/>
@@ -5462,8 +5770,8 @@
       <c r="Y148" s="5" t="n"/>
       <c r="AB148" s="5" t="n"/>
       <c r="AI148" s="5" t="n"/>
-      <c r="AP148" s="5" t="n"/>
-      <c r="BM148" s="5" t="n"/>
+      <c r="AS148" s="5" t="n"/>
+      <c r="BV148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="C149" s="5" t="n"/>
@@ -5476,8 +5784,8 @@
       <c r="Y149" s="5" t="n"/>
       <c r="AB149" s="5" t="n"/>
       <c r="AI149" s="5" t="n"/>
-      <c r="AP149" s="5" t="n"/>
-      <c r="BM149" s="5" t="n"/>
+      <c r="AS149" s="5" t="n"/>
+      <c r="BV149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="C150" s="5" t="n"/>
@@ -5490,8 +5798,8 @@
       <c r="Y150" s="5" t="n"/>
       <c r="AB150" s="5" t="n"/>
       <c r="AI150" s="5" t="n"/>
-      <c r="AP150" s="5" t="n"/>
-      <c r="BM150" s="5" t="n"/>
+      <c r="AS150" s="5" t="n"/>
+      <c r="BV150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="C151" s="5" t="n"/>
@@ -5504,8 +5812,8 @@
       <c r="Y151" s="5" t="n"/>
       <c r="AB151" s="5" t="n"/>
       <c r="AI151" s="5" t="n"/>
-      <c r="AP151" s="5" t="n"/>
-      <c r="BM151" s="5" t="n"/>
+      <c r="AS151" s="5" t="n"/>
+      <c r="BV151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="C152" s="5" t="n"/>
@@ -5518,8 +5826,8 @@
       <c r="Y152" s="5" t="n"/>
       <c r="AB152" s="5" t="n"/>
       <c r="AI152" s="5" t="n"/>
-      <c r="AP152" s="5" t="n"/>
-      <c r="BM152" s="5" t="n"/>
+      <c r="AS152" s="5" t="n"/>
+      <c r="BV152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="C153" s="5" t="n"/>
@@ -5532,8 +5840,8 @@
       <c r="Y153" s="5" t="n"/>
       <c r="AB153" s="5" t="n"/>
       <c r="AI153" s="5" t="n"/>
-      <c r="AP153" s="5" t="n"/>
-      <c r="BM153" s="5" t="n"/>
+      <c r="AS153" s="5" t="n"/>
+      <c r="BV153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="C154" s="5" t="n"/>
@@ -5546,8 +5854,8 @@
       <c r="Y154" s="5" t="n"/>
       <c r="AB154" s="5" t="n"/>
       <c r="AI154" s="5" t="n"/>
-      <c r="AP154" s="5" t="n"/>
-      <c r="BM154" s="5" t="n"/>
+      <c r="AS154" s="5" t="n"/>
+      <c r="BV154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="C155" s="5" t="n"/>
@@ -5560,8 +5868,8 @@
       <c r="Y155" s="5" t="n"/>
       <c r="AB155" s="5" t="n"/>
       <c r="AI155" s="5" t="n"/>
-      <c r="AP155" s="5" t="n"/>
-      <c r="BM155" s="5" t="n"/>
+      <c r="AS155" s="5" t="n"/>
+      <c r="BV155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="C156" s="5" t="n"/>
@@ -5574,8 +5882,8 @@
       <c r="Y156" s="5" t="n"/>
       <c r="AB156" s="5" t="n"/>
       <c r="AI156" s="5" t="n"/>
-      <c r="AP156" s="5" t="n"/>
-      <c r="BM156" s="5" t="n"/>
+      <c r="AS156" s="5" t="n"/>
+      <c r="BV156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="C157" s="5" t="n"/>
@@ -5588,8 +5896,8 @@
       <c r="Y157" s="5" t="n"/>
       <c r="AB157" s="5" t="n"/>
       <c r="AI157" s="5" t="n"/>
-      <c r="AP157" s="5" t="n"/>
-      <c r="BM157" s="5" t="n"/>
+      <c r="AS157" s="5" t="n"/>
+      <c r="BV157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="C158" s="5" t="n"/>
@@ -5602,8 +5910,8 @@
       <c r="Y158" s="5" t="n"/>
       <c r="AB158" s="5" t="n"/>
       <c r="AI158" s="5" t="n"/>
-      <c r="AP158" s="5" t="n"/>
-      <c r="BM158" s="5" t="n"/>
+      <c r="AS158" s="5" t="n"/>
+      <c r="BV158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="C159" s="5" t="n"/>
@@ -5616,8 +5924,8 @@
       <c r="Y159" s="5" t="n"/>
       <c r="AB159" s="5" t="n"/>
       <c r="AI159" s="5" t="n"/>
-      <c r="AP159" s="5" t="n"/>
-      <c r="BM159" s="5" t="n"/>
+      <c r="AS159" s="5" t="n"/>
+      <c r="BV159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="C160" s="5" t="n"/>
@@ -5630,8 +5938,8 @@
       <c r="Y160" s="5" t="n"/>
       <c r="AB160" s="5" t="n"/>
       <c r="AI160" s="5" t="n"/>
-      <c r="AP160" s="5" t="n"/>
-      <c r="BM160" s="5" t="n"/>
+      <c r="AS160" s="5" t="n"/>
+      <c r="BV160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="C161" s="5" t="n"/>
@@ -5644,8 +5952,8 @@
       <c r="Y161" s="5" t="n"/>
       <c r="AB161" s="5" t="n"/>
       <c r="AI161" s="5" t="n"/>
-      <c r="AP161" s="5" t="n"/>
-      <c r="BM161" s="5" t="n"/>
+      <c r="AS161" s="5" t="n"/>
+      <c r="BV161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="C162" s="5" t="n"/>
@@ -5658,8 +5966,8 @@
       <c r="Y162" s="5" t="n"/>
       <c r="AB162" s="5" t="n"/>
       <c r="AI162" s="5" t="n"/>
-      <c r="AP162" s="5" t="n"/>
-      <c r="BM162" s="5" t="n"/>
+      <c r="AS162" s="5" t="n"/>
+      <c r="BV162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="C163" s="5" t="n"/>
@@ -5672,8 +5980,8 @@
       <c r="Y163" s="5" t="n"/>
       <c r="AB163" s="5" t="n"/>
       <c r="AI163" s="5" t="n"/>
-      <c r="AP163" s="5" t="n"/>
-      <c r="BM163" s="5" t="n"/>
+      <c r="AS163" s="5" t="n"/>
+      <c r="BV163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="C164" s="5" t="n"/>
@@ -5686,8 +5994,8 @@
       <c r="Y164" s="5" t="n"/>
       <c r="AB164" s="5" t="n"/>
       <c r="AI164" s="5" t="n"/>
-      <c r="AP164" s="5" t="n"/>
-      <c r="BM164" s="5" t="n"/>
+      <c r="AS164" s="5" t="n"/>
+      <c r="BV164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="C165" s="5" t="n"/>
@@ -5700,8 +6008,8 @@
       <c r="Y165" s="5" t="n"/>
       <c r="AB165" s="5" t="n"/>
       <c r="AI165" s="5" t="n"/>
-      <c r="AP165" s="5" t="n"/>
-      <c r="BM165" s="5" t="n"/>
+      <c r="AS165" s="5" t="n"/>
+      <c r="BV165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="C166" s="5" t="n"/>
@@ -5714,8 +6022,8 @@
       <c r="Y166" s="5" t="n"/>
       <c r="AB166" s="5" t="n"/>
       <c r="AI166" s="5" t="n"/>
-      <c r="AP166" s="5" t="n"/>
-      <c r="BM166" s="5" t="n"/>
+      <c r="AS166" s="5" t="n"/>
+      <c r="BV166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="C167" s="5" t="n"/>
@@ -5728,8 +6036,8 @@
       <c r="Y167" s="5" t="n"/>
       <c r="AB167" s="5" t="n"/>
       <c r="AI167" s="5" t="n"/>
-      <c r="AP167" s="5" t="n"/>
-      <c r="BM167" s="5" t="n"/>
+      <c r="AS167" s="5" t="n"/>
+      <c r="BV167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="C168" s="5" t="n"/>
@@ -5742,8 +6050,8 @@
       <c r="Y168" s="5" t="n"/>
       <c r="AB168" s="5" t="n"/>
       <c r="AI168" s="5" t="n"/>
-      <c r="AP168" s="5" t="n"/>
-      <c r="BM168" s="5" t="n"/>
+      <c r="AS168" s="5" t="n"/>
+      <c r="BV168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="C169" s="5" t="n"/>
@@ -5756,8 +6064,8 @@
       <c r="Y169" s="5" t="n"/>
       <c r="AB169" s="5" t="n"/>
       <c r="AI169" s="5" t="n"/>
-      <c r="AP169" s="5" t="n"/>
-      <c r="BM169" s="5" t="n"/>
+      <c r="AS169" s="5" t="n"/>
+      <c r="BV169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="C170" s="5" t="n"/>
@@ -5770,8 +6078,8 @@
       <c r="Y170" s="5" t="n"/>
       <c r="AB170" s="5" t="n"/>
       <c r="AI170" s="5" t="n"/>
-      <c r="AP170" s="5" t="n"/>
-      <c r="BM170" s="5" t="n"/>
+      <c r="AS170" s="5" t="n"/>
+      <c r="BV170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="C171" s="5" t="n"/>
@@ -5784,8 +6092,8 @@
       <c r="Y171" s="5" t="n"/>
       <c r="AB171" s="5" t="n"/>
       <c r="AI171" s="5" t="n"/>
-      <c r="AP171" s="5" t="n"/>
-      <c r="BM171" s="5" t="n"/>
+      <c r="AS171" s="5" t="n"/>
+      <c r="BV171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="C172" s="5" t="n"/>
@@ -5798,8 +6106,8 @@
       <c r="Y172" s="5" t="n"/>
       <c r="AB172" s="5" t="n"/>
       <c r="AI172" s="5" t="n"/>
-      <c r="AP172" s="5" t="n"/>
-      <c r="BM172" s="5" t="n"/>
+      <c r="AS172" s="5" t="n"/>
+      <c r="BV172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="C173" s="5" t="n"/>
@@ -5812,8 +6120,8 @@
       <c r="Y173" s="5" t="n"/>
       <c r="AB173" s="5" t="n"/>
       <c r="AI173" s="5" t="n"/>
-      <c r="AP173" s="5" t="n"/>
-      <c r="BM173" s="5" t="n"/>
+      <c r="AS173" s="5" t="n"/>
+      <c r="BV173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="C174" s="5" t="n"/>
@@ -5826,8 +6134,8 @@
       <c r="Y174" s="5" t="n"/>
       <c r="AB174" s="5" t="n"/>
       <c r="AI174" s="5" t="n"/>
-      <c r="AP174" s="5" t="n"/>
-      <c r="BM174" s="5" t="n"/>
+      <c r="AS174" s="5" t="n"/>
+      <c r="BV174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="C175" s="5" t="n"/>
@@ -5840,8 +6148,8 @@
       <c r="Y175" s="5" t="n"/>
       <c r="AB175" s="5" t="n"/>
       <c r="AI175" s="5" t="n"/>
-      <c r="AP175" s="5" t="n"/>
-      <c r="BM175" s="5" t="n"/>
+      <c r="AS175" s="5" t="n"/>
+      <c r="BV175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="C176" s="5" t="n"/>
@@ -5854,8 +6162,8 @@
       <c r="Y176" s="5" t="n"/>
       <c r="AB176" s="5" t="n"/>
       <c r="AI176" s="5" t="n"/>
-      <c r="AP176" s="5" t="n"/>
-      <c r="BM176" s="5" t="n"/>
+      <c r="AS176" s="5" t="n"/>
+      <c r="BV176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="C177" s="5" t="n"/>
@@ -5868,8 +6176,8 @@
       <c r="Y177" s="5" t="n"/>
       <c r="AB177" s="5" t="n"/>
       <c r="AI177" s="5" t="n"/>
-      <c r="AP177" s="5" t="n"/>
-      <c r="BM177" s="5" t="n"/>
+      <c r="AS177" s="5" t="n"/>
+      <c r="BV177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="C178" s="5" t="n"/>
@@ -5882,8 +6190,8 @@
       <c r="Y178" s="5" t="n"/>
       <c r="AB178" s="5" t="n"/>
       <c r="AI178" s="5" t="n"/>
-      <c r="AP178" s="5" t="n"/>
-      <c r="BM178" s="5" t="n"/>
+      <c r="AS178" s="5" t="n"/>
+      <c r="BV178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="C179" s="5" t="n"/>
@@ -5896,8 +6204,8 @@
       <c r="Y179" s="5" t="n"/>
       <c r="AB179" s="5" t="n"/>
       <c r="AI179" s="5" t="n"/>
-      <c r="AP179" s="5" t="n"/>
-      <c r="BM179" s="5" t="n"/>
+      <c r="AS179" s="5" t="n"/>
+      <c r="BV179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="C180" s="5" t="n"/>
@@ -5910,8 +6218,8 @@
       <c r="Y180" s="5" t="n"/>
       <c r="AB180" s="5" t="n"/>
       <c r="AI180" s="5" t="n"/>
-      <c r="AP180" s="5" t="n"/>
-      <c r="BM180" s="5" t="n"/>
+      <c r="AS180" s="5" t="n"/>
+      <c r="BV180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="C181" s="5" t="n"/>
@@ -5924,8 +6232,8 @@
       <c r="Y181" s="5" t="n"/>
       <c r="AB181" s="5" t="n"/>
       <c r="AI181" s="5" t="n"/>
-      <c r="AP181" s="5" t="n"/>
-      <c r="BM181" s="5" t="n"/>
+      <c r="AS181" s="5" t="n"/>
+      <c r="BV181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="C182" s="5" t="n"/>
@@ -5938,8 +6246,8 @@
       <c r="Y182" s="5" t="n"/>
       <c r="AB182" s="5" t="n"/>
       <c r="AI182" s="5" t="n"/>
-      <c r="AP182" s="5" t="n"/>
-      <c r="BM182" s="5" t="n"/>
+      <c r="AS182" s="5" t="n"/>
+      <c r="BV182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="C183" s="5" t="n"/>
@@ -5952,8 +6260,8 @@
       <c r="Y183" s="5" t="n"/>
       <c r="AB183" s="5" t="n"/>
       <c r="AI183" s="5" t="n"/>
-      <c r="AP183" s="5" t="n"/>
-      <c r="BM183" s="5" t="n"/>
+      <c r="AS183" s="5" t="n"/>
+      <c r="BV183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="C184" s="5" t="n"/>
@@ -5966,8 +6274,8 @@
       <c r="Y184" s="5" t="n"/>
       <c r="AB184" s="5" t="n"/>
       <c r="AI184" s="5" t="n"/>
-      <c r="AP184" s="5" t="n"/>
-      <c r="BM184" s="5" t="n"/>
+      <c r="AS184" s="5" t="n"/>
+      <c r="BV184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="C185" s="5" t="n"/>
@@ -5980,8 +6288,8 @@
       <c r="Y185" s="5" t="n"/>
       <c r="AB185" s="5" t="n"/>
       <c r="AI185" s="5" t="n"/>
-      <c r="AP185" s="5" t="n"/>
-      <c r="BM185" s="5" t="n"/>
+      <c r="AS185" s="5" t="n"/>
+      <c r="BV185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="C186" s="5" t="n"/>
@@ -5994,8 +6302,8 @@
       <c r="Y186" s="5" t="n"/>
       <c r="AB186" s="5" t="n"/>
       <c r="AI186" s="5" t="n"/>
-      <c r="AP186" s="5" t="n"/>
-      <c r="BM186" s="5" t="n"/>
+      <c r="AS186" s="5" t="n"/>
+      <c r="BV186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="C187" s="5" t="n"/>
@@ -6008,8 +6316,8 @@
       <c r="Y187" s="5" t="n"/>
       <c r="AB187" s="5" t="n"/>
       <c r="AI187" s="5" t="n"/>
-      <c r="AP187" s="5" t="n"/>
-      <c r="BM187" s="5" t="n"/>
+      <c r="AS187" s="5" t="n"/>
+      <c r="BV187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="C188" s="5" t="n"/>
@@ -6022,8 +6330,8 @@
       <c r="Y188" s="5" t="n"/>
       <c r="AB188" s="5" t="n"/>
       <c r="AI188" s="5" t="n"/>
-      <c r="AP188" s="5" t="n"/>
-      <c r="BM188" s="5" t="n"/>
+      <c r="AS188" s="5" t="n"/>
+      <c r="BV188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="C189" s="5" t="n"/>
@@ -6036,8 +6344,8 @@
       <c r="Y189" s="5" t="n"/>
       <c r="AB189" s="5" t="n"/>
       <c r="AI189" s="5" t="n"/>
-      <c r="AP189" s="5" t="n"/>
-      <c r="BM189" s="5" t="n"/>
+      <c r="AS189" s="5" t="n"/>
+      <c r="BV189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="C190" s="5" t="n"/>
@@ -6050,8 +6358,8 @@
       <c r="Y190" s="5" t="n"/>
       <c r="AB190" s="5" t="n"/>
       <c r="AI190" s="5" t="n"/>
-      <c r="AP190" s="5" t="n"/>
-      <c r="BM190" s="5" t="n"/>
+      <c r="AS190" s="5" t="n"/>
+      <c r="BV190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="C191" s="5" t="n"/>
@@ -6064,8 +6372,8 @@
       <c r="Y191" s="5" t="n"/>
       <c r="AB191" s="5" t="n"/>
       <c r="AI191" s="5" t="n"/>
-      <c r="AP191" s="5" t="n"/>
-      <c r="BM191" s="5" t="n"/>
+      <c r="AS191" s="5" t="n"/>
+      <c r="BV191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="C192" s="5" t="n"/>
@@ -6078,8 +6386,8 @@
       <c r="Y192" s="5" t="n"/>
       <c r="AB192" s="5" t="n"/>
       <c r="AI192" s="5" t="n"/>
-      <c r="AP192" s="5" t="n"/>
-      <c r="BM192" s="5" t="n"/>
+      <c r="AS192" s="5" t="n"/>
+      <c r="BV192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="C193" s="5" t="n"/>
@@ -6092,8 +6400,8 @@
       <c r="Y193" s="5" t="n"/>
       <c r="AB193" s="5" t="n"/>
       <c r="AI193" s="5" t="n"/>
-      <c r="AP193" s="5" t="n"/>
-      <c r="BM193" s="5" t="n"/>
+      <c r="AS193" s="5" t="n"/>
+      <c r="BV193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="C194" s="5" t="n"/>
@@ -6106,8 +6414,8 @@
       <c r="Y194" s="5" t="n"/>
       <c r="AB194" s="5" t="n"/>
       <c r="AI194" s="5" t="n"/>
-      <c r="AP194" s="5" t="n"/>
-      <c r="BM194" s="5" t="n"/>
+      <c r="AS194" s="5" t="n"/>
+      <c r="BV194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="C195" s="5" t="n"/>
@@ -6120,8 +6428,8 @@
       <c r="Y195" s="5" t="n"/>
       <c r="AB195" s="5" t="n"/>
       <c r="AI195" s="5" t="n"/>
-      <c r="AP195" s="5" t="n"/>
-      <c r="BM195" s="5" t="n"/>
+      <c r="AS195" s="5" t="n"/>
+      <c r="BV195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="C196" s="5" t="n"/>
@@ -6134,8 +6442,8 @@
       <c r="Y196" s="5" t="n"/>
       <c r="AB196" s="5" t="n"/>
       <c r="AI196" s="5" t="n"/>
-      <c r="AP196" s="5" t="n"/>
-      <c r="BM196" s="5" t="n"/>
+      <c r="AS196" s="5" t="n"/>
+      <c r="BV196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="C197" s="5" t="n"/>
@@ -6148,8 +6456,8 @@
       <c r="Y197" s="5" t="n"/>
       <c r="AB197" s="5" t="n"/>
       <c r="AI197" s="5" t="n"/>
-      <c r="AP197" s="5" t="n"/>
-      <c r="BM197" s="5" t="n"/>
+      <c r="AS197" s="5" t="n"/>
+      <c r="BV197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="C198" s="5" t="n"/>
@@ -6162,8 +6470,8 @@
       <c r="Y198" s="5" t="n"/>
       <c r="AB198" s="5" t="n"/>
       <c r="AI198" s="5" t="n"/>
-      <c r="AP198" s="5" t="n"/>
-      <c r="BM198" s="5" t="n"/>
+      <c r="AS198" s="5" t="n"/>
+      <c r="BV198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="C199" s="5" t="n"/>
@@ -6176,8 +6484,8 @@
       <c r="Y199" s="5" t="n"/>
       <c r="AB199" s="5" t="n"/>
       <c r="AI199" s="5" t="n"/>
-      <c r="AP199" s="5" t="n"/>
-      <c r="BM199" s="5" t="n"/>
+      <c r="AS199" s="5" t="n"/>
+      <c r="BV199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="C200" s="5" t="n"/>
@@ -6190,8 +6498,8 @@
       <c r="Y200" s="5" t="n"/>
       <c r="AB200" s="5" t="n"/>
       <c r="AI200" s="5" t="n"/>
-      <c r="AP200" s="5" t="n"/>
-      <c r="BM200" s="5" t="n"/>
+      <c r="AS200" s="5" t="n"/>
+      <c r="BV200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="C201" s="5" t="n"/>
@@ -6204,8 +6512,8 @@
       <c r="Y201" s="5" t="n"/>
       <c r="AB201" s="5" t="n"/>
       <c r="AI201" s="5" t="n"/>
-      <c r="AP201" s="5" t="n"/>
-      <c r="BM201" s="5" t="n"/>
+      <c r="AS201" s="5" t="n"/>
+      <c r="BV201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="C202" s="5" t="n"/>
@@ -6218,8 +6526,8 @@
       <c r="Y202" s="5" t="n"/>
       <c r="AB202" s="5" t="n"/>
       <c r="AI202" s="5" t="n"/>
-      <c r="AP202" s="5" t="n"/>
-      <c r="BM202" s="5" t="n"/>
+      <c r="AS202" s="5" t="n"/>
+      <c r="BV202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="C203" s="5" t="n"/>
@@ -6232,8 +6540,8 @@
       <c r="Y203" s="5" t="n"/>
       <c r="AB203" s="5" t="n"/>
       <c r="AI203" s="5" t="n"/>
-      <c r="AP203" s="5" t="n"/>
-      <c r="BM203" s="5" t="n"/>
+      <c r="AS203" s="5" t="n"/>
+      <c r="BV203" s="5" t="n"/>
     </row>
     <row r="204">
       <c r="C204" s="5" t="n"/>
@@ -6246,8 +6554,8 @@
       <c r="Y204" s="5" t="n"/>
       <c r="AB204" s="5" t="n"/>
       <c r="AI204" s="5" t="n"/>
-      <c r="AP204" s="5" t="n"/>
-      <c r="BM204" s="5" t="n"/>
+      <c r="AS204" s="5" t="n"/>
+      <c r="BV204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="C205" s="5" t="n"/>
@@ -6260,8 +6568,8 @@
       <c r="Y205" s="5" t="n"/>
       <c r="AB205" s="5" t="n"/>
       <c r="AI205" s="5" t="n"/>
-      <c r="AP205" s="5" t="n"/>
-      <c r="BM205" s="5" t="n"/>
+      <c r="AS205" s="5" t="n"/>
+      <c r="BV205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="C206" s="5" t="n"/>
@@ -6274,8 +6582,8 @@
       <c r="Y206" s="5" t="n"/>
       <c r="AB206" s="5" t="n"/>
       <c r="AI206" s="5" t="n"/>
-      <c r="AP206" s="5" t="n"/>
-      <c r="BM206" s="5" t="n"/>
+      <c r="AS206" s="5" t="n"/>
+      <c r="BV206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="C207" s="5" t="n"/>
@@ -6288,8 +6596,8 @@
       <c r="Y207" s="5" t="n"/>
       <c r="AB207" s="5" t="n"/>
       <c r="AI207" s="5" t="n"/>
-      <c r="AP207" s="5" t="n"/>
-      <c r="BM207" s="5" t="n"/>
+      <c r="AS207" s="5" t="n"/>
+      <c r="BV207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="C208" s="5" t="n"/>
@@ -6302,8 +6610,8 @@
       <c r="Y208" s="5" t="n"/>
       <c r="AB208" s="5" t="n"/>
       <c r="AI208" s="5" t="n"/>
-      <c r="AP208" s="5" t="n"/>
-      <c r="BM208" s="5" t="n"/>
+      <c r="AS208" s="5" t="n"/>
+      <c r="BV208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="C209" s="5" t="n"/>
@@ -6316,8 +6624,8 @@
       <c r="Y209" s="5" t="n"/>
       <c r="AB209" s="5" t="n"/>
       <c r="AI209" s="5" t="n"/>
-      <c r="AP209" s="5" t="n"/>
-      <c r="BM209" s="5" t="n"/>
+      <c r="AS209" s="5" t="n"/>
+      <c r="BV209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="C210" s="5" t="n"/>
@@ -6330,8 +6638,8 @@
       <c r="Y210" s="5" t="n"/>
       <c r="AB210" s="5" t="n"/>
       <c r="AI210" s="5" t="n"/>
-      <c r="AP210" s="5" t="n"/>
-      <c r="BM210" s="5" t="n"/>
+      <c r="AS210" s="5" t="n"/>
+      <c r="BV210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="C211" s="5" t="n"/>
@@ -6344,8 +6652,8 @@
       <c r="Y211" s="5" t="n"/>
       <c r="AB211" s="5" t="n"/>
       <c r="AI211" s="5" t="n"/>
-      <c r="AP211" s="5" t="n"/>
-      <c r="BM211" s="5" t="n"/>
+      <c r="AS211" s="5" t="n"/>
+      <c r="BV211" s="5" t="n"/>
     </row>
     <row r="212">
       <c r="C212" s="5" t="n"/>
@@ -6358,8 +6666,8 @@
       <c r="Y212" s="5" t="n"/>
       <c r="AB212" s="5" t="n"/>
       <c r="AI212" s="5" t="n"/>
-      <c r="AP212" s="5" t="n"/>
-      <c r="BM212" s="5" t="n"/>
+      <c r="AS212" s="5" t="n"/>
+      <c r="BV212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="C213" s="5" t="n"/>
@@ -6372,8 +6680,8 @@
       <c r="Y213" s="5" t="n"/>
       <c r="AB213" s="5" t="n"/>
       <c r="AI213" s="5" t="n"/>
-      <c r="AP213" s="5" t="n"/>
-      <c r="BM213" s="5" t="n"/>
+      <c r="AS213" s="5" t="n"/>
+      <c r="BV213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="C214" s="5" t="n"/>
@@ -6386,8 +6694,8 @@
       <c r="Y214" s="5" t="n"/>
       <c r="AB214" s="5" t="n"/>
       <c r="AI214" s="5" t="n"/>
-      <c r="AP214" s="5" t="n"/>
-      <c r="BM214" s="5" t="n"/>
+      <c r="AS214" s="5" t="n"/>
+      <c r="BV214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="C215" s="5" t="n"/>
@@ -6400,8 +6708,8 @@
       <c r="Y215" s="5" t="n"/>
       <c r="AB215" s="5" t="n"/>
       <c r="AI215" s="5" t="n"/>
-      <c r="AP215" s="5" t="n"/>
-      <c r="BM215" s="5" t="n"/>
+      <c r="AS215" s="5" t="n"/>
+      <c r="BV215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="C216" s="5" t="n"/>
@@ -6414,8 +6722,8 @@
       <c r="Y216" s="5" t="n"/>
       <c r="AB216" s="5" t="n"/>
       <c r="AI216" s="5" t="n"/>
-      <c r="AP216" s="5" t="n"/>
-      <c r="BM216" s="5" t="n"/>
+      <c r="AS216" s="5" t="n"/>
+      <c r="BV216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="C217" s="5" t="n"/>
@@ -6428,8 +6736,8 @@
       <c r="Y217" s="5" t="n"/>
       <c r="AB217" s="5" t="n"/>
       <c r="AI217" s="5" t="n"/>
-      <c r="AP217" s="5" t="n"/>
-      <c r="BM217" s="5" t="n"/>
+      <c r="AS217" s="5" t="n"/>
+      <c r="BV217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="C218" s="5" t="n"/>
@@ -6442,8 +6750,8 @@
       <c r="Y218" s="5" t="n"/>
       <c r="AB218" s="5" t="n"/>
       <c r="AI218" s="5" t="n"/>
-      <c r="AP218" s="5" t="n"/>
-      <c r="BM218" s="5" t="n"/>
+      <c r="AS218" s="5" t="n"/>
+      <c r="BV218" s="5" t="n"/>
     </row>
     <row r="219">
       <c r="C219" s="5" t="n"/>
@@ -6456,8 +6764,8 @@
       <c r="Y219" s="5" t="n"/>
       <c r="AB219" s="5" t="n"/>
       <c r="AI219" s="5" t="n"/>
-      <c r="AP219" s="5" t="n"/>
-      <c r="BM219" s="5" t="n"/>
+      <c r="AS219" s="5" t="n"/>
+      <c r="BV219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="C220" s="5" t="n"/>
@@ -6470,8 +6778,8 @@
       <c r="Y220" s="5" t="n"/>
       <c r="AB220" s="5" t="n"/>
       <c r="AI220" s="5" t="n"/>
-      <c r="AP220" s="5" t="n"/>
-      <c r="BM220" s="5" t="n"/>
+      <c r="AS220" s="5" t="n"/>
+      <c r="BV220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="C221" s="5" t="n"/>
@@ -6484,8 +6792,8 @@
       <c r="Y221" s="5" t="n"/>
       <c r="AB221" s="5" t="n"/>
       <c r="AI221" s="5" t="n"/>
-      <c r="AP221" s="5" t="n"/>
-      <c r="BM221" s="5" t="n"/>
+      <c r="AS221" s="5" t="n"/>
+      <c r="BV221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="C222" s="5" t="n"/>
@@ -6498,8 +6806,8 @@
       <c r="Y222" s="5" t="n"/>
       <c r="AB222" s="5" t="n"/>
       <c r="AI222" s="5" t="n"/>
-      <c r="AP222" s="5" t="n"/>
-      <c r="BM222" s="5" t="n"/>
+      <c r="AS222" s="5" t="n"/>
+      <c r="BV222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="C223" s="5" t="n"/>
@@ -6512,8 +6820,8 @@
       <c r="Y223" s="5" t="n"/>
       <c r="AB223" s="5" t="n"/>
       <c r="AI223" s="5" t="n"/>
-      <c r="AP223" s="5" t="n"/>
-      <c r="BM223" s="5" t="n"/>
+      <c r="AS223" s="5" t="n"/>
+      <c r="BV223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="C224" s="5" t="n"/>
@@ -6526,8 +6834,8 @@
       <c r="Y224" s="5" t="n"/>
       <c r="AB224" s="5" t="n"/>
       <c r="AI224" s="5" t="n"/>
-      <c r="AP224" s="5" t="n"/>
-      <c r="BM224" s="5" t="n"/>
+      <c r="AS224" s="5" t="n"/>
+      <c r="BV224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="C225" s="5" t="n"/>
@@ -6540,8 +6848,8 @@
       <c r="Y225" s="5" t="n"/>
       <c r="AB225" s="5" t="n"/>
       <c r="AI225" s="5" t="n"/>
-      <c r="AP225" s="5" t="n"/>
-      <c r="BM225" s="5" t="n"/>
+      <c r="AS225" s="5" t="n"/>
+      <c r="BV225" s="5" t="n"/>
     </row>
     <row r="226">
       <c r="C226" s="5" t="n"/>
@@ -6554,8 +6862,8 @@
       <c r="Y226" s="5" t="n"/>
       <c r="AB226" s="5" t="n"/>
       <c r="AI226" s="5" t="n"/>
-      <c r="AP226" s="5" t="n"/>
-      <c r="BM226" s="5" t="n"/>
+      <c r="AS226" s="5" t="n"/>
+      <c r="BV226" s="5" t="n"/>
     </row>
     <row r="227">
       <c r="C227" s="5" t="n"/>
@@ -6568,8 +6876,8 @@
       <c r="Y227" s="5" t="n"/>
       <c r="AB227" s="5" t="n"/>
       <c r="AI227" s="5" t="n"/>
-      <c r="AP227" s="5" t="n"/>
-      <c r="BM227" s="5" t="n"/>
+      <c r="AS227" s="5" t="n"/>
+      <c r="BV227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="C228" s="5" t="n"/>
@@ -6582,8 +6890,8 @@
       <c r="Y228" s="5" t="n"/>
       <c r="AB228" s="5" t="n"/>
       <c r="AI228" s="5" t="n"/>
-      <c r="AP228" s="5" t="n"/>
-      <c r="BM228" s="5" t="n"/>
+      <c r="AS228" s="5" t="n"/>
+      <c r="BV228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="C229" s="5" t="n"/>
@@ -6596,8 +6904,8 @@
       <c r="Y229" s="5" t="n"/>
       <c r="AB229" s="5" t="n"/>
       <c r="AI229" s="5" t="n"/>
-      <c r="AP229" s="5" t="n"/>
-      <c r="BM229" s="5" t="n"/>
+      <c r="AS229" s="5" t="n"/>
+      <c r="BV229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="C230" s="5" t="n"/>
@@ -6610,8 +6918,8 @@
       <c r="Y230" s="5" t="n"/>
       <c r="AB230" s="5" t="n"/>
       <c r="AI230" s="5" t="n"/>
-      <c r="AP230" s="5" t="n"/>
-      <c r="BM230" s="5" t="n"/>
+      <c r="AS230" s="5" t="n"/>
+      <c r="BV230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="C231" s="5" t="n"/>
@@ -6624,8 +6932,8 @@
       <c r="Y231" s="5" t="n"/>
       <c r="AB231" s="5" t="n"/>
       <c r="AI231" s="5" t="n"/>
-      <c r="AP231" s="5" t="n"/>
-      <c r="BM231" s="5" t="n"/>
+      <c r="AS231" s="5" t="n"/>
+      <c r="BV231" s="5" t="n"/>
     </row>
     <row r="232">
       <c r="C232" s="5" t="n"/>
@@ -6638,8 +6946,8 @@
       <c r="Y232" s="5" t="n"/>
       <c r="AB232" s="5" t="n"/>
       <c r="AI232" s="5" t="n"/>
-      <c r="AP232" s="5" t="n"/>
-      <c r="BM232" s="5" t="n"/>
+      <c r="AS232" s="5" t="n"/>
+      <c r="BV232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="C233" s="5" t="n"/>
@@ -6652,8 +6960,8 @@
       <c r="Y233" s="5" t="n"/>
       <c r="AB233" s="5" t="n"/>
       <c r="AI233" s="5" t="n"/>
-      <c r="AP233" s="5" t="n"/>
-      <c r="BM233" s="5" t="n"/>
+      <c r="AS233" s="5" t="n"/>
+      <c r="BV233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="C234" s="5" t="n"/>
@@ -6666,8 +6974,8 @@
       <c r="Y234" s="5" t="n"/>
       <c r="AB234" s="5" t="n"/>
       <c r="AI234" s="5" t="n"/>
-      <c r="AP234" s="5" t="n"/>
-      <c r="BM234" s="5" t="n"/>
+      <c r="AS234" s="5" t="n"/>
+      <c r="BV234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="C235" s="5" t="n"/>
@@ -6680,8 +6988,8 @@
       <c r="Y235" s="5" t="n"/>
       <c r="AB235" s="5" t="n"/>
       <c r="AI235" s="5" t="n"/>
-      <c r="AP235" s="5" t="n"/>
-      <c r="BM235" s="5" t="n"/>
+      <c r="AS235" s="5" t="n"/>
+      <c r="BV235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="C236" s="5" t="n"/>
@@ -6694,8 +7002,8 @@
       <c r="Y236" s="5" t="n"/>
       <c r="AB236" s="5" t="n"/>
       <c r="AI236" s="5" t="n"/>
-      <c r="AP236" s="5" t="n"/>
-      <c r="BM236" s="5" t="n"/>
+      <c r="AS236" s="5" t="n"/>
+      <c r="BV236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="C237" s="5" t="n"/>
@@ -6708,8 +7016,8 @@
       <c r="Y237" s="5" t="n"/>
       <c r="AB237" s="5" t="n"/>
       <c r="AI237" s="5" t="n"/>
-      <c r="AP237" s="5" t="n"/>
-      <c r="BM237" s="5" t="n"/>
+      <c r="AS237" s="5" t="n"/>
+      <c r="BV237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="C238" s="5" t="n"/>
@@ -6722,8 +7030,8 @@
       <c r="Y238" s="5" t="n"/>
       <c r="AB238" s="5" t="n"/>
       <c r="AI238" s="5" t="n"/>
-      <c r="AP238" s="5" t="n"/>
-      <c r="BM238" s="5" t="n"/>
+      <c r="AS238" s="5" t="n"/>
+      <c r="BV238" s="5" t="n"/>
     </row>
     <row r="239">
       <c r="C239" s="5" t="n"/>
@@ -6736,8 +7044,8 @@
       <c r="Y239" s="5" t="n"/>
       <c r="AB239" s="5" t="n"/>
       <c r="AI239" s="5" t="n"/>
-      <c r="AP239" s="5" t="n"/>
-      <c r="BM239" s="5" t="n"/>
+      <c r="AS239" s="5" t="n"/>
+      <c r="BV239" s="5" t="n"/>
     </row>
     <row r="240">
       <c r="C240" s="5" t="n"/>
@@ -6750,8 +7058,8 @@
       <c r="Y240" s="5" t="n"/>
       <c r="AB240" s="5" t="n"/>
       <c r="AI240" s="5" t="n"/>
-      <c r="AP240" s="5" t="n"/>
-      <c r="BM240" s="5" t="n"/>
+      <c r="AS240" s="5" t="n"/>
+      <c r="BV240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="C241" s="5" t="n"/>
@@ -6764,8 +7072,8 @@
       <c r="Y241" s="5" t="n"/>
       <c r="AB241" s="5" t="n"/>
       <c r="AI241" s="5" t="n"/>
-      <c r="AP241" s="5" t="n"/>
-      <c r="BM241" s="5" t="n"/>
+      <c r="AS241" s="5" t="n"/>
+      <c r="BV241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="C242" s="5" t="n"/>
@@ -6778,8 +7086,8 @@
       <c r="Y242" s="5" t="n"/>
       <c r="AB242" s="5" t="n"/>
       <c r="AI242" s="5" t="n"/>
-      <c r="AP242" s="5" t="n"/>
-      <c r="BM242" s="5" t="n"/>
+      <c r="AS242" s="5" t="n"/>
+      <c r="BV242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="C243" s="5" t="n"/>
@@ -6792,8 +7100,8 @@
       <c r="Y243" s="5" t="n"/>
       <c r="AB243" s="5" t="n"/>
       <c r="AI243" s="5" t="n"/>
-      <c r="AP243" s="5" t="n"/>
-      <c r="BM243" s="5" t="n"/>
+      <c r="AS243" s="5" t="n"/>
+      <c r="BV243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="C244" s="5" t="n"/>
@@ -6806,8 +7114,8 @@
       <c r="Y244" s="5" t="n"/>
       <c r="AB244" s="5" t="n"/>
       <c r="AI244" s="5" t="n"/>
-      <c r="AP244" s="5" t="n"/>
-      <c r="BM244" s="5" t="n"/>
+      <c r="AS244" s="5" t="n"/>
+      <c r="BV244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="C245" s="5" t="n"/>
@@ -6820,8 +7128,8 @@
       <c r="Y245" s="5" t="n"/>
       <c r="AB245" s="5" t="n"/>
       <c r="AI245" s="5" t="n"/>
-      <c r="AP245" s="5" t="n"/>
-      <c r="BM245" s="5" t="n"/>
+      <c r="AS245" s="5" t="n"/>
+      <c r="BV245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="C246" s="5" t="n"/>
@@ -6834,8 +7142,8 @@
       <c r="Y246" s="5" t="n"/>
       <c r="AB246" s="5" t="n"/>
       <c r="AI246" s="5" t="n"/>
-      <c r="AP246" s="5" t="n"/>
-      <c r="BM246" s="5" t="n"/>
+      <c r="AS246" s="5" t="n"/>
+      <c r="BV246" s="5" t="n"/>
     </row>
     <row r="247">
       <c r="C247" s="5" t="n"/>
@@ -6848,8 +7156,8 @@
       <c r="Y247" s="5" t="n"/>
       <c r="AB247" s="5" t="n"/>
       <c r="AI247" s="5" t="n"/>
-      <c r="AP247" s="5" t="n"/>
-      <c r="BM247" s="5" t="n"/>
+      <c r="AS247" s="5" t="n"/>
+      <c r="BV247" s="5" t="n"/>
     </row>
     <row r="248">
       <c r="C248" s="5" t="n"/>
@@ -6862,8 +7170,8 @@
       <c r="Y248" s="5" t="n"/>
       <c r="AB248" s="5" t="n"/>
       <c r="AI248" s="5" t="n"/>
-      <c r="AP248" s="5" t="n"/>
-      <c r="BM248" s="5" t="n"/>
+      <c r="AS248" s="5" t="n"/>
+      <c r="BV248" s="5" t="n"/>
     </row>
     <row r="249">
       <c r="C249" s="5" t="n"/>
@@ -6876,8 +7184,8 @@
       <c r="Y249" s="5" t="n"/>
       <c r="AB249" s="5" t="n"/>
       <c r="AI249" s="5" t="n"/>
-      <c r="AP249" s="5" t="n"/>
-      <c r="BM249" s="5" t="n"/>
+      <c r="AS249" s="5" t="n"/>
+      <c r="BV249" s="5" t="n"/>
     </row>
     <row r="250">
       <c r="C250" s="5" t="n"/>
@@ -6890,8 +7198,8 @@
       <c r="Y250" s="5" t="n"/>
       <c r="AB250" s="5" t="n"/>
       <c r="AI250" s="5" t="n"/>
-      <c r="AP250" s="5" t="n"/>
-      <c r="BM250" s="5" t="n"/>
+      <c r="AS250" s="5" t="n"/>
+      <c r="BV250" s="5" t="n"/>
     </row>
     <row r="251">
       <c r="C251" s="5" t="n"/>
@@ -6904,8 +7212,8 @@
       <c r="Y251" s="5" t="n"/>
       <c r="AB251" s="5" t="n"/>
       <c r="AI251" s="5" t="n"/>
-      <c r="AP251" s="5" t="n"/>
-      <c r="BM251" s="5" t="n"/>
+      <c r="AS251" s="5" t="n"/>
+      <c r="BV251" s="5" t="n"/>
     </row>
     <row r="252">
       <c r="C252" s="5" t="n"/>
@@ -6918,8 +7226,8 @@
       <c r="Y252" s="5" t="n"/>
       <c r="AB252" s="5" t="n"/>
       <c r="AI252" s="5" t="n"/>
-      <c r="AP252" s="5" t="n"/>
-      <c r="BM252" s="5" t="n"/>
+      <c r="AS252" s="5" t="n"/>
+      <c r="BV252" s="5" t="n"/>
     </row>
     <row r="253">
       <c r="C253" s="5" t="n"/>
@@ -6932,8 +7240,8 @@
       <c r="Y253" s="5" t="n"/>
       <c r="AB253" s="5" t="n"/>
       <c r="AI253" s="5" t="n"/>
-      <c r="AP253" s="5" t="n"/>
-      <c r="BM253" s="5" t="n"/>
+      <c r="AS253" s="5" t="n"/>
+      <c r="BV253" s="5" t="n"/>
     </row>
     <row r="254">
       <c r="C254" s="5" t="n"/>
@@ -6946,8 +7254,8 @@
       <c r="Y254" s="5" t="n"/>
       <c r="AB254" s="5" t="n"/>
       <c r="AI254" s="5" t="n"/>
-      <c r="AP254" s="5" t="n"/>
-      <c r="BM254" s="5" t="n"/>
+      <c r="AS254" s="5" t="n"/>
+      <c r="BV254" s="5" t="n"/>
     </row>
     <row r="255">
       <c r="C255" s="5" t="n"/>
@@ -6960,8 +7268,8 @@
       <c r="Y255" s="5" t="n"/>
       <c r="AB255" s="5" t="n"/>
       <c r="AI255" s="5" t="n"/>
-      <c r="AP255" s="5" t="n"/>
-      <c r="BM255" s="5" t="n"/>
+      <c r="AS255" s="5" t="n"/>
+      <c r="BV255" s="5" t="n"/>
     </row>
     <row r="256">
       <c r="C256" s="5" t="n"/>
@@ -6974,8 +7282,8 @@
       <c r="Y256" s="5" t="n"/>
       <c r="AB256" s="5" t="n"/>
       <c r="AI256" s="5" t="n"/>
-      <c r="AP256" s="5" t="n"/>
-      <c r="BM256" s="5" t="n"/>
+      <c r="AS256" s="5" t="n"/>
+      <c r="BV256" s="5" t="n"/>
     </row>
     <row r="257">
       <c r="C257" s="5" t="n"/>
@@ -6988,8 +7296,8 @@
       <c r="Y257" s="5" t="n"/>
       <c r="AB257" s="5" t="n"/>
       <c r="AI257" s="5" t="n"/>
-      <c r="AP257" s="5" t="n"/>
-      <c r="BM257" s="5" t="n"/>
+      <c r="AS257" s="5" t="n"/>
+      <c r="BV257" s="5" t="n"/>
     </row>
     <row r="258">
       <c r="C258" s="5" t="n"/>
@@ -7002,8 +7310,8 @@
       <c r="Y258" s="5" t="n"/>
       <c r="AB258" s="5" t="n"/>
       <c r="AI258" s="5" t="n"/>
-      <c r="AP258" s="5" t="n"/>
-      <c r="BM258" s="5" t="n"/>
+      <c r="AS258" s="5" t="n"/>
+      <c r="BV258" s="5" t="n"/>
     </row>
     <row r="259">
       <c r="C259" s="5" t="n"/>
@@ -7016,8 +7324,8 @@
       <c r="Y259" s="5" t="n"/>
       <c r="AB259" s="5" t="n"/>
       <c r="AI259" s="5" t="n"/>
-      <c r="AP259" s="5" t="n"/>
-      <c r="BM259" s="5" t="n"/>
+      <c r="AS259" s="5" t="n"/>
+      <c r="BV259" s="5" t="n"/>
     </row>
     <row r="260">
       <c r="C260" s="5" t="n"/>
@@ -7030,8 +7338,8 @@
       <c r="Y260" s="5" t="n"/>
       <c r="AB260" s="5" t="n"/>
       <c r="AI260" s="5" t="n"/>
-      <c r="AP260" s="5" t="n"/>
-      <c r="BM260" s="5" t="n"/>
+      <c r="AS260" s="5" t="n"/>
+      <c r="BV260" s="5" t="n"/>
     </row>
     <row r="261">
       <c r="C261" s="5" t="n"/>
@@ -7044,8 +7352,8 @@
       <c r="Y261" s="5" t="n"/>
       <c r="AB261" s="5" t="n"/>
       <c r="AI261" s="5" t="n"/>
-      <c r="AP261" s="5" t="n"/>
-      <c r="BM261" s="5" t="n"/>
+      <c r="AS261" s="5" t="n"/>
+      <c r="BV261" s="5" t="n"/>
     </row>
     <row r="262">
       <c r="C262" s="5" t="n"/>
@@ -7058,8 +7366,8 @@
       <c r="Y262" s="5" t="n"/>
       <c r="AB262" s="5" t="n"/>
       <c r="AI262" s="5" t="n"/>
-      <c r="AP262" s="5" t="n"/>
-      <c r="BM262" s="5" t="n"/>
+      <c r="AS262" s="5" t="n"/>
+      <c r="BV262" s="5" t="n"/>
     </row>
     <row r="263">
       <c r="C263" s="5" t="n"/>
@@ -7072,8 +7380,8 @@
       <c r="Y263" s="5" t="n"/>
       <c r="AB263" s="5" t="n"/>
       <c r="AI263" s="5" t="n"/>
-      <c r="AP263" s="5" t="n"/>
-      <c r="BM263" s="5" t="n"/>
+      <c r="AS263" s="5" t="n"/>
+      <c r="BV263" s="5" t="n"/>
     </row>
     <row r="264">
       <c r="C264" s="5" t="n"/>
@@ -7086,8 +7394,8 @@
       <c r="Y264" s="5" t="n"/>
       <c r="AB264" s="5" t="n"/>
       <c r="AI264" s="5" t="n"/>
-      <c r="AP264" s="5" t="n"/>
-      <c r="BM264" s="5" t="n"/>
+      <c r="AS264" s="5" t="n"/>
+      <c r="BV264" s="5" t="n"/>
     </row>
     <row r="265">
       <c r="C265" s="5" t="n"/>
@@ -7100,8 +7408,8 @@
       <c r="Y265" s="5" t="n"/>
       <c r="AB265" s="5" t="n"/>
       <c r="AI265" s="5" t="n"/>
-      <c r="AP265" s="5" t="n"/>
-      <c r="BM265" s="5" t="n"/>
+      <c r="AS265" s="5" t="n"/>
+      <c r="BV265" s="5" t="n"/>
     </row>
     <row r="266">
       <c r="C266" s="5" t="n"/>
@@ -7114,8 +7422,8 @@
       <c r="Y266" s="5" t="n"/>
       <c r="AB266" s="5" t="n"/>
       <c r="AI266" s="5" t="n"/>
-      <c r="AP266" s="5" t="n"/>
-      <c r="BM266" s="5" t="n"/>
+      <c r="AS266" s="5" t="n"/>
+      <c r="BV266" s="5" t="n"/>
     </row>
     <row r="267">
       <c r="C267" s="5" t="n"/>
@@ -7128,8 +7436,8 @@
       <c r="Y267" s="5" t="n"/>
       <c r="AB267" s="5" t="n"/>
       <c r="AI267" s="5" t="n"/>
-      <c r="AP267" s="5" t="n"/>
-      <c r="BM267" s="5" t="n"/>
+      <c r="AS267" s="5" t="n"/>
+      <c r="BV267" s="5" t="n"/>
     </row>
     <row r="268">
       <c r="C268" s="5" t="n"/>
@@ -7142,8 +7450,8 @@
       <c r="Y268" s="5" t="n"/>
       <c r="AB268" s="5" t="n"/>
       <c r="AI268" s="5" t="n"/>
-      <c r="AP268" s="5" t="n"/>
-      <c r="BM268" s="5" t="n"/>
+      <c r="AS268" s="5" t="n"/>
+      <c r="BV268" s="5" t="n"/>
     </row>
     <row r="269">
       <c r="C269" s="5" t="n"/>
@@ -7156,8 +7464,8 @@
       <c r="Y269" s="5" t="n"/>
       <c r="AB269" s="5" t="n"/>
       <c r="AI269" s="5" t="n"/>
-      <c r="AP269" s="5" t="n"/>
-      <c r="BM269" s="5" t="n"/>
+      <c r="AS269" s="5" t="n"/>
+      <c r="BV269" s="5" t="n"/>
     </row>
     <row r="270">
       <c r="C270" s="5" t="n"/>
@@ -7170,8 +7478,8 @@
       <c r="Y270" s="5" t="n"/>
       <c r="AB270" s="5" t="n"/>
       <c r="AI270" s="5" t="n"/>
-      <c r="AP270" s="5" t="n"/>
-      <c r="BM270" s="5" t="n"/>
+      <c r="AS270" s="5" t="n"/>
+      <c r="BV270" s="5" t="n"/>
     </row>
     <row r="271">
       <c r="C271" s="5" t="n"/>
@@ -7184,8 +7492,8 @@
       <c r="Y271" s="5" t="n"/>
       <c r="AB271" s="5" t="n"/>
       <c r="AI271" s="5" t="n"/>
-      <c r="AP271" s="5" t="n"/>
-      <c r="BM271" s="5" t="n"/>
+      <c r="AS271" s="5" t="n"/>
+      <c r="BV271" s="5" t="n"/>
     </row>
     <row r="272">
       <c r="C272" s="5" t="n"/>
@@ -7198,8 +7506,8 @@
       <c r="Y272" s="5" t="n"/>
       <c r="AB272" s="5" t="n"/>
       <c r="AI272" s="5" t="n"/>
-      <c r="AP272" s="5" t="n"/>
-      <c r="BM272" s="5" t="n"/>
+      <c r="AS272" s="5" t="n"/>
+      <c r="BV272" s="5" t="n"/>
     </row>
     <row r="273">
       <c r="C273" s="5" t="n"/>
@@ -7212,8 +7520,8 @@
       <c r="Y273" s="5" t="n"/>
       <c r="AB273" s="5" t="n"/>
       <c r="AI273" s="5" t="n"/>
-      <c r="AP273" s="5" t="n"/>
-      <c r="BM273" s="5" t="n"/>
+      <c r="AS273" s="5" t="n"/>
+      <c r="BV273" s="5" t="n"/>
     </row>
     <row r="274">
       <c r="C274" s="5" t="n"/>
@@ -7226,8 +7534,8 @@
       <c r="Y274" s="5" t="n"/>
       <c r="AB274" s="5" t="n"/>
       <c r="AI274" s="5" t="n"/>
-      <c r="AP274" s="5" t="n"/>
-      <c r="BM274" s="5" t="n"/>
+      <c r="AS274" s="5" t="n"/>
+      <c r="BV274" s="5" t="n"/>
     </row>
     <row r="275">
       <c r="C275" s="5" t="n"/>
@@ -7240,8 +7548,8 @@
       <c r="Y275" s="5" t="n"/>
       <c r="AB275" s="5" t="n"/>
       <c r="AI275" s="5" t="n"/>
-      <c r="AP275" s="5" t="n"/>
-      <c r="BM275" s="5" t="n"/>
+      <c r="AS275" s="5" t="n"/>
+      <c r="BV275" s="5" t="n"/>
     </row>
     <row r="276">
       <c r="C276" s="5" t="n"/>
@@ -7254,8 +7562,8 @@
       <c r="Y276" s="5" t="n"/>
       <c r="AB276" s="5" t="n"/>
       <c r="AI276" s="5" t="n"/>
-      <c r="AP276" s="5" t="n"/>
-      <c r="BM276" s="5" t="n"/>
+      <c r="AS276" s="5" t="n"/>
+      <c r="BV276" s="5" t="n"/>
     </row>
     <row r="277">
       <c r="C277" s="5" t="n"/>
@@ -7268,8 +7576,8 @@
       <c r="Y277" s="5" t="n"/>
       <c r="AB277" s="5" t="n"/>
       <c r="AI277" s="5" t="n"/>
-      <c r="AP277" s="5" t="n"/>
-      <c r="BM277" s="5" t="n"/>
+      <c r="AS277" s="5" t="n"/>
+      <c r="BV277" s="5" t="n"/>
     </row>
     <row r="278">
       <c r="C278" s="5" t="n"/>
@@ -7282,8 +7590,8 @@
       <c r="Y278" s="5" t="n"/>
       <c r="AB278" s="5" t="n"/>
       <c r="AI278" s="5" t="n"/>
-      <c r="AP278" s="5" t="n"/>
-      <c r="BM278" s="5" t="n"/>
+      <c r="AS278" s="5" t="n"/>
+      <c r="BV278" s="5" t="n"/>
     </row>
     <row r="279">
       <c r="C279" s="5" t="n"/>
@@ -7296,8 +7604,8 @@
       <c r="Y279" s="5" t="n"/>
       <c r="AB279" s="5" t="n"/>
       <c r="AI279" s="5" t="n"/>
-      <c r="AP279" s="5" t="n"/>
-      <c r="BM279" s="5" t="n"/>
+      <c r="AS279" s="5" t="n"/>
+      <c r="BV279" s="5" t="n"/>
     </row>
     <row r="280">
       <c r="C280" s="5" t="n"/>
@@ -7310,8 +7618,8 @@
       <c r="Y280" s="5" t="n"/>
       <c r="AB280" s="5" t="n"/>
       <c r="AI280" s="5" t="n"/>
-      <c r="AP280" s="5" t="n"/>
-      <c r="BM280" s="5" t="n"/>
+      <c r="AS280" s="5" t="n"/>
+      <c r="BV280" s="5" t="n"/>
     </row>
     <row r="281">
       <c r="C281" s="5" t="n"/>
@@ -7324,8 +7632,8 @@
       <c r="Y281" s="5" t="n"/>
       <c r="AB281" s="5" t="n"/>
       <c r="AI281" s="5" t="n"/>
-      <c r="AP281" s="5" t="n"/>
-      <c r="BM281" s="5" t="n"/>
+      <c r="AS281" s="5" t="n"/>
+      <c r="BV281" s="5" t="n"/>
     </row>
     <row r="282">
       <c r="C282" s="5" t="n"/>
@@ -7338,8 +7646,8 @@
       <c r="Y282" s="5" t="n"/>
       <c r="AB282" s="5" t="n"/>
       <c r="AI282" s="5" t="n"/>
-      <c r="AP282" s="5" t="n"/>
-      <c r="BM282" s="5" t="n"/>
+      <c r="AS282" s="5" t="n"/>
+      <c r="BV282" s="5" t="n"/>
     </row>
     <row r="283">
       <c r="C283" s="5" t="n"/>
@@ -7352,8 +7660,8 @@
       <c r="Y283" s="5" t="n"/>
       <c r="AB283" s="5" t="n"/>
       <c r="AI283" s="5" t="n"/>
-      <c r="AP283" s="5" t="n"/>
-      <c r="BM283" s="5" t="n"/>
+      <c r="AS283" s="5" t="n"/>
+      <c r="BV283" s="5" t="n"/>
     </row>
     <row r="284">
       <c r="C284" s="5" t="n"/>
@@ -7366,8 +7674,8 @@
       <c r="Y284" s="5" t="n"/>
       <c r="AB284" s="5" t="n"/>
       <c r="AI284" s="5" t="n"/>
-      <c r="AP284" s="5" t="n"/>
-      <c r="BM284" s="5" t="n"/>
+      <c r="AS284" s="5" t="n"/>
+      <c r="BV284" s="5" t="n"/>
     </row>
     <row r="285">
       <c r="C285" s="5" t="n"/>
@@ -7380,8 +7688,8 @@
       <c r="Y285" s="5" t="n"/>
       <c r="AB285" s="5" t="n"/>
       <c r="AI285" s="5" t="n"/>
-      <c r="AP285" s="5" t="n"/>
-      <c r="BM285" s="5" t="n"/>
+      <c r="AS285" s="5" t="n"/>
+      <c r="BV285" s="5" t="n"/>
     </row>
     <row r="286">
       <c r="C286" s="5" t="n"/>
@@ -7394,8 +7702,8 @@
       <c r="Y286" s="5" t="n"/>
       <c r="AB286" s="5" t="n"/>
       <c r="AI286" s="5" t="n"/>
-      <c r="AP286" s="5" t="n"/>
-      <c r="BM286" s="5" t="n"/>
+      <c r="AS286" s="5" t="n"/>
+      <c r="BV286" s="5" t="n"/>
     </row>
     <row r="287">
       <c r="C287" s="5" t="n"/>
@@ -7408,8 +7716,8 @@
       <c r="Y287" s="5" t="n"/>
       <c r="AB287" s="5" t="n"/>
       <c r="AI287" s="5" t="n"/>
-      <c r="AP287" s="5" t="n"/>
-      <c r="BM287" s="5" t="n"/>
+      <c r="AS287" s="5" t="n"/>
+      <c r="BV287" s="5" t="n"/>
     </row>
     <row r="288">
       <c r="C288" s="5" t="n"/>
@@ -7422,8 +7730,8 @@
       <c r="Y288" s="5" t="n"/>
       <c r="AB288" s="5" t="n"/>
       <c r="AI288" s="5" t="n"/>
-      <c r="AP288" s="5" t="n"/>
-      <c r="BM288" s="5" t="n"/>
+      <c r="AS288" s="5" t="n"/>
+      <c r="BV288" s="5" t="n"/>
     </row>
     <row r="289">
       <c r="C289" s="5" t="n"/>
@@ -7436,8 +7744,8 @@
       <c r="Y289" s="5" t="n"/>
       <c r="AB289" s="5" t="n"/>
       <c r="AI289" s="5" t="n"/>
-      <c r="AP289" s="5" t="n"/>
-      <c r="BM289" s="5" t="n"/>
+      <c r="AS289" s="5" t="n"/>
+      <c r="BV289" s="5" t="n"/>
     </row>
     <row r="290">
       <c r="C290" s="5" t="n"/>
@@ -7450,8 +7758,8 @@
       <c r="Y290" s="5" t="n"/>
       <c r="AB290" s="5" t="n"/>
       <c r="AI290" s="5" t="n"/>
-      <c r="AP290" s="5" t="n"/>
-      <c r="BM290" s="5" t="n"/>
+      <c r="AS290" s="5" t="n"/>
+      <c r="BV290" s="5" t="n"/>
     </row>
     <row r="291">
       <c r="C291" s="5" t="n"/>
@@ -7464,8 +7772,8 @@
       <c r="Y291" s="5" t="n"/>
       <c r="AB291" s="5" t="n"/>
       <c r="AI291" s="5" t="n"/>
-      <c r="AP291" s="5" t="n"/>
-      <c r="BM291" s="5" t="n"/>
+      <c r="AS291" s="5" t="n"/>
+      <c r="BV291" s="5" t="n"/>
     </row>
     <row r="292">
       <c r="C292" s="5" t="n"/>
@@ -7478,8 +7786,8 @@
       <c r="Y292" s="5" t="n"/>
       <c r="AB292" s="5" t="n"/>
       <c r="AI292" s="5" t="n"/>
-      <c r="AP292" s="5" t="n"/>
-      <c r="BM292" s="5" t="n"/>
+      <c r="AS292" s="5" t="n"/>
+      <c r="BV292" s="5" t="n"/>
     </row>
     <row r="293">
       <c r="C293" s="5" t="n"/>
@@ -7492,8 +7800,8 @@
       <c r="Y293" s="5" t="n"/>
       <c r="AB293" s="5" t="n"/>
       <c r="AI293" s="5" t="n"/>
-      <c r="AP293" s="5" t="n"/>
-      <c r="BM293" s="5" t="n"/>
+      <c r="AS293" s="5" t="n"/>
+      <c r="BV293" s="5" t="n"/>
     </row>
     <row r="294">
       <c r="C294" s="5" t="n"/>
@@ -7506,8 +7814,8 @@
       <c r="Y294" s="5" t="n"/>
       <c r="AB294" s="5" t="n"/>
       <c r="AI294" s="5" t="n"/>
-      <c r="AP294" s="5" t="n"/>
-      <c r="BM294" s="5" t="n"/>
+      <c r="AS294" s="5" t="n"/>
+      <c r="BV294" s="5" t="n"/>
     </row>
     <row r="295">
       <c r="C295" s="5" t="n"/>
@@ -7520,8 +7828,8 @@
       <c r="Y295" s="5" t="n"/>
       <c r="AB295" s="5" t="n"/>
       <c r="AI295" s="5" t="n"/>
-      <c r="AP295" s="5" t="n"/>
-      <c r="BM295" s="5" t="n"/>
+      <c r="AS295" s="5" t="n"/>
+      <c r="BV295" s="5" t="n"/>
     </row>
     <row r="296">
       <c r="C296" s="5" t="n"/>
@@ -7534,8 +7842,8 @@
       <c r="Y296" s="5" t="n"/>
       <c r="AB296" s="5" t="n"/>
       <c r="AI296" s="5" t="n"/>
-      <c r="AP296" s="5" t="n"/>
-      <c r="BM296" s="5" t="n"/>
+      <c r="AS296" s="5" t="n"/>
+      <c r="BV296" s="5" t="n"/>
     </row>
     <row r="297">
       <c r="C297" s="5" t="n"/>
@@ -7548,8 +7856,8 @@
       <c r="Y297" s="5" t="n"/>
       <c r="AB297" s="5" t="n"/>
       <c r="AI297" s="5" t="n"/>
-      <c r="AP297" s="5" t="n"/>
-      <c r="BM297" s="5" t="n"/>
+      <c r="AS297" s="5" t="n"/>
+      <c r="BV297" s="5" t="n"/>
     </row>
     <row r="298">
       <c r="C298" s="5" t="n"/>
@@ -7562,8 +7870,8 @@
       <c r="Y298" s="5" t="n"/>
       <c r="AB298" s="5" t="n"/>
       <c r="AI298" s="5" t="n"/>
-      <c r="AP298" s="5" t="n"/>
-      <c r="BM298" s="5" t="n"/>
+      <c r="AS298" s="5" t="n"/>
+      <c r="BV298" s="5" t="n"/>
     </row>
     <row r="299">
       <c r="C299" s="5" t="n"/>
@@ -7576,8 +7884,8 @@
       <c r="Y299" s="5" t="n"/>
       <c r="AB299" s="5" t="n"/>
       <c r="AI299" s="5" t="n"/>
-      <c r="AP299" s="5" t="n"/>
-      <c r="BM299" s="5" t="n"/>
+      <c r="AS299" s="5" t="n"/>
+      <c r="BV299" s="5" t="n"/>
     </row>
     <row r="300">
       <c r="C300" s="5" t="n"/>
@@ -7590,8 +7898,8 @@
       <c r="Y300" s="5" t="n"/>
       <c r="AB300" s="5" t="n"/>
       <c r="AI300" s="5" t="n"/>
-      <c r="AP300" s="5" t="n"/>
-      <c r="BM300" s="5" t="n"/>
+      <c r="AS300" s="5" t="n"/>
+      <c r="BV300" s="5" t="n"/>
     </row>
     <row r="301">
       <c r="C301" s="5" t="n"/>
@@ -7604,8 +7912,8 @@
       <c r="Y301" s="5" t="n"/>
       <c r="AB301" s="5" t="n"/>
       <c r="AI301" s="5" t="n"/>
-      <c r="AP301" s="5" t="n"/>
-      <c r="BM301" s="5" t="n"/>
+      <c r="AS301" s="5" t="n"/>
+      <c r="BV301" s="5" t="n"/>
     </row>
     <row r="302">
       <c r="C302" s="5" t="n"/>
@@ -7618,8 +7926,8 @@
       <c r="Y302" s="5" t="n"/>
       <c r="AB302" s="5" t="n"/>
       <c r="AI302" s="5" t="n"/>
-      <c r="AP302" s="5" t="n"/>
-      <c r="BM302" s="5" t="n"/>
+      <c r="AS302" s="5" t="n"/>
+      <c r="BV302" s="5" t="n"/>
     </row>
     <row r="303">
       <c r="C303" s="5" t="n"/>
@@ -7632,8 +7940,8 @@
       <c r="Y303" s="5" t="n"/>
       <c r="AB303" s="5" t="n"/>
       <c r="AI303" s="5" t="n"/>
-      <c r="AP303" s="5" t="n"/>
-      <c r="BM303" s="5" t="n"/>
+      <c r="AS303" s="5" t="n"/>
+      <c r="BV303" s="5" t="n"/>
     </row>
     <row r="304">
       <c r="C304" s="5" t="n"/>
@@ -7646,8 +7954,8 @@
       <c r="Y304" s="5" t="n"/>
       <c r="AB304" s="5" t="n"/>
       <c r="AI304" s="5" t="n"/>
-      <c r="AP304" s="5" t="n"/>
-      <c r="BM304" s="5" t="n"/>
+      <c r="AS304" s="5" t="n"/>
+      <c r="BV304" s="5" t="n"/>
     </row>
     <row r="305">
       <c r="C305" s="5" t="n"/>
@@ -7660,8 +7968,8 @@
       <c r="Y305" s="5" t="n"/>
       <c r="AB305" s="5" t="n"/>
       <c r="AI305" s="5" t="n"/>
-      <c r="AP305" s="5" t="n"/>
-      <c r="BM305" s="5" t="n"/>
+      <c r="AS305" s="5" t="n"/>
+      <c r="BV305" s="5" t="n"/>
     </row>
     <row r="306">
       <c r="C306" s="5" t="n"/>
@@ -7674,8 +7982,8 @@
       <c r="Y306" s="5" t="n"/>
       <c r="AB306" s="5" t="n"/>
       <c r="AI306" s="5" t="n"/>
-      <c r="AP306" s="5" t="n"/>
-      <c r="BM306" s="5" t="n"/>
+      <c r="AS306" s="5" t="n"/>
+      <c r="BV306" s="5" t="n"/>
     </row>
     <row r="307">
       <c r="C307" s="5" t="n"/>
@@ -7688,8 +7996,8 @@
       <c r="Y307" s="5" t="n"/>
       <c r="AB307" s="5" t="n"/>
       <c r="AI307" s="5" t="n"/>
-      <c r="AP307" s="5" t="n"/>
-      <c r="BM307" s="5" t="n"/>
+      <c r="AS307" s="5" t="n"/>
+      <c r="BV307" s="5" t="n"/>
     </row>
     <row r="308">
       <c r="C308" s="5" t="n"/>
@@ -7702,8 +8010,8 @@
       <c r="Y308" s="5" t="n"/>
       <c r="AB308" s="5" t="n"/>
       <c r="AI308" s="5" t="n"/>
-      <c r="AP308" s="5" t="n"/>
-      <c r="BM308" s="5" t="n"/>
+      <c r="AS308" s="5" t="n"/>
+      <c r="BV308" s="5" t="n"/>
     </row>
     <row r="309">
       <c r="C309" s="5" t="n"/>
@@ -7716,8 +8024,8 @@
       <c r="Y309" s="5" t="n"/>
       <c r="AB309" s="5" t="n"/>
       <c r="AI309" s="5" t="n"/>
-      <c r="AP309" s="5" t="n"/>
-      <c r="BM309" s="5" t="n"/>
+      <c r="AS309" s="5" t="n"/>
+      <c r="BV309" s="5" t="n"/>
     </row>
     <row r="310">
       <c r="C310" s="5" t="n"/>
@@ -7730,8 +8038,8 @@
       <c r="Y310" s="5" t="n"/>
       <c r="AB310" s="5" t="n"/>
       <c r="AI310" s="5" t="n"/>
-      <c r="AP310" s="5" t="n"/>
-      <c r="BM310" s="5" t="n"/>
+      <c r="AS310" s="5" t="n"/>
+      <c r="BV310" s="5" t="n"/>
     </row>
     <row r="311">
       <c r="C311" s="5" t="n"/>
@@ -7744,8 +8052,8 @@
       <c r="Y311" s="5" t="n"/>
       <c r="AB311" s="5" t="n"/>
       <c r="AI311" s="5" t="n"/>
-      <c r="AP311" s="5" t="n"/>
-      <c r="BM311" s="5" t="n"/>
+      <c r="AS311" s="5" t="n"/>
+      <c r="BV311" s="5" t="n"/>
     </row>
     <row r="312">
       <c r="C312" s="5" t="n"/>
@@ -7758,8 +8066,8 @@
       <c r="Y312" s="5" t="n"/>
       <c r="AB312" s="5" t="n"/>
       <c r="AI312" s="5" t="n"/>
-      <c r="AP312" s="5" t="n"/>
-      <c r="BM312" s="5" t="n"/>
+      <c r="AS312" s="5" t="n"/>
+      <c r="BV312" s="5" t="n"/>
     </row>
     <row r="313">
       <c r="C313" s="5" t="n"/>
@@ -7772,8 +8080,8 @@
       <c r="Y313" s="5" t="n"/>
       <c r="AB313" s="5" t="n"/>
       <c r="AI313" s="5" t="n"/>
-      <c r="AP313" s="5" t="n"/>
-      <c r="BM313" s="5" t="n"/>
+      <c r="AS313" s="5" t="n"/>
+      <c r="BV313" s="5" t="n"/>
     </row>
     <row r="314">
       <c r="C314" s="5" t="n"/>
@@ -7786,8 +8094,8 @@
       <c r="Y314" s="5" t="n"/>
       <c r="AB314" s="5" t="n"/>
       <c r="AI314" s="5" t="n"/>
-      <c r="AP314" s="5" t="n"/>
-      <c r="BM314" s="5" t="n"/>
+      <c r="AS314" s="5" t="n"/>
+      <c r="BV314" s="5" t="n"/>
     </row>
     <row r="315">
       <c r="C315" s="5" t="n"/>
@@ -7800,8 +8108,8 @@
       <c r="Y315" s="5" t="n"/>
       <c r="AB315" s="5" t="n"/>
       <c r="AI315" s="5" t="n"/>
-      <c r="AP315" s="5" t="n"/>
-      <c r="BM315" s="5" t="n"/>
+      <c r="AS315" s="5" t="n"/>
+      <c r="BV315" s="5" t="n"/>
     </row>
     <row r="316">
       <c r="C316" s="5" t="n"/>
@@ -7814,8 +8122,8 @@
       <c r="Y316" s="5" t="n"/>
       <c r="AB316" s="5" t="n"/>
       <c r="AI316" s="5" t="n"/>
-      <c r="AP316" s="5" t="n"/>
-      <c r="BM316" s="5" t="n"/>
+      <c r="AS316" s="5" t="n"/>
+      <c r="BV316" s="5" t="n"/>
     </row>
     <row r="317">
       <c r="C317" s="5" t="n"/>
@@ -7828,8 +8136,8 @@
       <c r="Y317" s="5" t="n"/>
       <c r="AB317" s="5" t="n"/>
       <c r="AI317" s="5" t="n"/>
-      <c r="AP317" s="5" t="n"/>
-      <c r="BM317" s="5" t="n"/>
+      <c r="AS317" s="5" t="n"/>
+      <c r="BV317" s="5" t="n"/>
     </row>
     <row r="318">
       <c r="C318" s="5" t="n"/>
@@ -7842,8 +8150,8 @@
       <c r="Y318" s="5" t="n"/>
       <c r="AB318" s="5" t="n"/>
       <c r="AI318" s="5" t="n"/>
-      <c r="AP318" s="5" t="n"/>
-      <c r="BM318" s="5" t="n"/>
+      <c r="AS318" s="5" t="n"/>
+      <c r="BV318" s="5" t="n"/>
     </row>
     <row r="319">
       <c r="C319" s="5" t="n"/>
@@ -7856,8 +8164,8 @@
       <c r="Y319" s="5" t="n"/>
       <c r="AB319" s="5" t="n"/>
       <c r="AI319" s="5" t="n"/>
-      <c r="AP319" s="5" t="n"/>
-      <c r="BM319" s="5" t="n"/>
+      <c r="AS319" s="5" t="n"/>
+      <c r="BV319" s="5" t="n"/>
     </row>
     <row r="320">
       <c r="C320" s="5" t="n"/>
@@ -7870,8 +8178,8 @@
       <c r="Y320" s="5" t="n"/>
       <c r="AB320" s="5" t="n"/>
       <c r="AI320" s="5" t="n"/>
-      <c r="AP320" s="5" t="n"/>
-      <c r="BM320" s="5" t="n"/>
+      <c r="AS320" s="5" t="n"/>
+      <c r="BV320" s="5" t="n"/>
     </row>
     <row r="321">
       <c r="C321" s="5" t="n"/>
@@ -7884,8 +8192,8 @@
       <c r="Y321" s="5" t="n"/>
       <c r="AB321" s="5" t="n"/>
       <c r="AI321" s="5" t="n"/>
-      <c r="AP321" s="5" t="n"/>
-      <c r="BM321" s="5" t="n"/>
+      <c r="AS321" s="5" t="n"/>
+      <c r="BV321" s="5" t="n"/>
     </row>
     <row r="322">
       <c r="C322" s="5" t="n"/>
@@ -7898,8 +8206,8 @@
       <c r="Y322" s="5" t="n"/>
       <c r="AB322" s="5" t="n"/>
       <c r="AI322" s="5" t="n"/>
-      <c r="AP322" s="5" t="n"/>
-      <c r="BM322" s="5" t="n"/>
+      <c r="AS322" s="5" t="n"/>
+      <c r="BV322" s="5" t="n"/>
     </row>
     <row r="323">
       <c r="C323" s="5" t="n"/>
@@ -7912,8 +8220,8 @@
       <c r="Y323" s="5" t="n"/>
       <c r="AB323" s="5" t="n"/>
       <c r="AI323" s="5" t="n"/>
-      <c r="AP323" s="5" t="n"/>
-      <c r="BM323" s="5" t="n"/>
+      <c r="AS323" s="5" t="n"/>
+      <c r="BV323" s="5" t="n"/>
     </row>
     <row r="324">
       <c r="C324" s="5" t="n"/>
@@ -7926,8 +8234,8 @@
       <c r="Y324" s="5" t="n"/>
       <c r="AB324" s="5" t="n"/>
       <c r="AI324" s="5" t="n"/>
-      <c r="AP324" s="5" t="n"/>
-      <c r="BM324" s="5" t="n"/>
+      <c r="AS324" s="5" t="n"/>
+      <c r="BV324" s="5" t="n"/>
     </row>
     <row r="325">
       <c r="C325" s="5" t="n"/>
@@ -7940,8 +8248,8 @@
       <c r="Y325" s="5" t="n"/>
       <c r="AB325" s="5" t="n"/>
       <c r="AI325" s="5" t="n"/>
-      <c r="AP325" s="5" t="n"/>
-      <c r="BM325" s="5" t="n"/>
+      <c r="AS325" s="5" t="n"/>
+      <c r="BV325" s="5" t="n"/>
     </row>
     <row r="326">
       <c r="C326" s="5" t="n"/>
@@ -7954,8 +8262,8 @@
       <c r="Y326" s="5" t="n"/>
       <c r="AB326" s="5" t="n"/>
       <c r="AI326" s="5" t="n"/>
-      <c r="AP326" s="5" t="n"/>
-      <c r="BM326" s="5" t="n"/>
+      <c r="AS326" s="5" t="n"/>
+      <c r="BV326" s="5" t="n"/>
     </row>
     <row r="327">
       <c r="C327" s="5" t="n"/>
@@ -7968,8 +8276,8 @@
       <c r="Y327" s="5" t="n"/>
       <c r="AB327" s="5" t="n"/>
       <c r="AI327" s="5" t="n"/>
-      <c r="AP327" s="5" t="n"/>
-      <c r="BM327" s="5" t="n"/>
+      <c r="AS327" s="5" t="n"/>
+      <c r="BV327" s="5" t="n"/>
     </row>
     <row r="328">
       <c r="C328" s="5" t="n"/>
@@ -7982,8 +8290,8 @@
       <c r="Y328" s="5" t="n"/>
       <c r="AB328" s="5" t="n"/>
       <c r="AI328" s="5" t="n"/>
-      <c r="AP328" s="5" t="n"/>
-      <c r="BM328" s="5" t="n"/>
+      <c r="AS328" s="5" t="n"/>
+      <c r="BV328" s="5" t="n"/>
     </row>
     <row r="329">
       <c r="C329" s="5" t="n"/>
@@ -7996,8 +8304,8 @@
       <c r="Y329" s="5" t="n"/>
       <c r="AB329" s="5" t="n"/>
       <c r="AI329" s="5" t="n"/>
-      <c r="AP329" s="5" t="n"/>
-      <c r="BM329" s="5" t="n"/>
+      <c r="AS329" s="5" t="n"/>
+      <c r="BV329" s="5" t="n"/>
     </row>
     <row r="330">
       <c r="C330" s="5" t="n"/>
@@ -8010,8 +8318,8 @@
       <c r="Y330" s="5" t="n"/>
       <c r="AB330" s="5" t="n"/>
       <c r="AI330" s="5" t="n"/>
-      <c r="AP330" s="5" t="n"/>
-      <c r="BM330" s="5" t="n"/>
+      <c r="AS330" s="5" t="n"/>
+      <c r="BV330" s="5" t="n"/>
     </row>
     <row r="331">
       <c r="C331" s="5" t="n"/>
@@ -8024,8 +8332,8 @@
       <c r="Y331" s="5" t="n"/>
       <c r="AB331" s="5" t="n"/>
       <c r="AI331" s="5" t="n"/>
-      <c r="AP331" s="5" t="n"/>
-      <c r="BM331" s="5" t="n"/>
+      <c r="AS331" s="5" t="n"/>
+      <c r="BV331" s="5" t="n"/>
     </row>
     <row r="332">
       <c r="C332" s="5" t="n"/>
@@ -8038,8 +8346,8 @@
       <c r="Y332" s="5" t="n"/>
       <c r="AB332" s="5" t="n"/>
       <c r="AI332" s="5" t="n"/>
-      <c r="AP332" s="5" t="n"/>
-      <c r="BM332" s="5" t="n"/>
+      <c r="AS332" s="5" t="n"/>
+      <c r="BV332" s="5" t="n"/>
     </row>
     <row r="333">
       <c r="C333" s="5" t="n"/>
@@ -8052,8 +8360,8 @@
       <c r="Y333" s="5" t="n"/>
       <c r="AB333" s="5" t="n"/>
       <c r="AI333" s="5" t="n"/>
-      <c r="AP333" s="5" t="n"/>
-      <c r="BM333" s="5" t="n"/>
+      <c r="AS333" s="5" t="n"/>
+      <c r="BV333" s="5" t="n"/>
     </row>
     <row r="334">
       <c r="C334" s="5" t="n"/>
@@ -8066,8 +8374,8 @@
       <c r="Y334" s="5" t="n"/>
       <c r="AB334" s="5" t="n"/>
       <c r="AI334" s="5" t="n"/>
-      <c r="AP334" s="5" t="n"/>
-      <c r="BM334" s="5" t="n"/>
+      <c r="AS334" s="5" t="n"/>
+      <c r="BV334" s="5" t="n"/>
     </row>
     <row r="335">
       <c r="C335" s="5" t="n"/>
@@ -8080,8 +8388,8 @@
       <c r="Y335" s="5" t="n"/>
       <c r="AB335" s="5" t="n"/>
       <c r="AI335" s="5" t="n"/>
-      <c r="AP335" s="5" t="n"/>
-      <c r="BM335" s="5" t="n"/>
+      <c r="AS335" s="5" t="n"/>
+      <c r="BV335" s="5" t="n"/>
     </row>
     <row r="336">
       <c r="C336" s="5" t="n"/>
@@ -8094,8 +8402,8 @@
       <c r="Y336" s="5" t="n"/>
       <c r="AB336" s="5" t="n"/>
       <c r="AI336" s="5" t="n"/>
-      <c r="AP336" s="5" t="n"/>
-      <c r="BM336" s="5" t="n"/>
+      <c r="AS336" s="5" t="n"/>
+      <c r="BV336" s="5" t="n"/>
     </row>
     <row r="337">
       <c r="C337" s="5" t="n"/>
@@ -8108,8 +8416,8 @@
       <c r="Y337" s="5" t="n"/>
       <c r="AB337" s="5" t="n"/>
       <c r="AI337" s="5" t="n"/>
-      <c r="AP337" s="5" t="n"/>
-      <c r="BM337" s="5" t="n"/>
+      <c r="AS337" s="5" t="n"/>
+      <c r="BV337" s="5" t="n"/>
     </row>
     <row r="338">
       <c r="C338" s="5" t="n"/>
@@ -8122,8 +8430,8 @@
       <c r="Y338" s="5" t="n"/>
       <c r="AB338" s="5" t="n"/>
       <c r="AI338" s="5" t="n"/>
-      <c r="AP338" s="5" t="n"/>
-      <c r="BM338" s="5" t="n"/>
+      <c r="AS338" s="5" t="n"/>
+      <c r="BV338" s="5" t="n"/>
     </row>
     <row r="339">
       <c r="C339" s="5" t="n"/>
@@ -8136,8 +8444,8 @@
       <c r="Y339" s="5" t="n"/>
       <c r="AB339" s="5" t="n"/>
       <c r="AI339" s="5" t="n"/>
-      <c r="AP339" s="5" t="n"/>
-      <c r="BM339" s="5" t="n"/>
+      <c r="AS339" s="5" t="n"/>
+      <c r="BV339" s="5" t="n"/>
     </row>
     <row r="340">
       <c r="C340" s="5" t="n"/>
@@ -8150,8 +8458,8 @@
       <c r="Y340" s="5" t="n"/>
       <c r="AB340" s="5" t="n"/>
       <c r="AI340" s="5" t="n"/>
-      <c r="AP340" s="5" t="n"/>
-      <c r="BM340" s="5" t="n"/>
+      <c r="AS340" s="5" t="n"/>
+      <c r="BV340" s="5" t="n"/>
     </row>
     <row r="341">
       <c r="C341" s="5" t="n"/>
@@ -8164,8 +8472,8 @@
       <c r="Y341" s="5" t="n"/>
       <c r="AB341" s="5" t="n"/>
       <c r="AI341" s="5" t="n"/>
-      <c r="AP341" s="5" t="n"/>
-      <c r="BM341" s="5" t="n"/>
+      <c r="AS341" s="5" t="n"/>
+      <c r="BV341" s="5" t="n"/>
     </row>
     <row r="342">
       <c r="C342" s="5" t="n"/>
@@ -8178,8 +8486,8 @@
       <c r="Y342" s="5" t="n"/>
       <c r="AB342" s="5" t="n"/>
       <c r="AI342" s="5" t="n"/>
-      <c r="AP342" s="5" t="n"/>
-      <c r="BM342" s="5" t="n"/>
+      <c r="AS342" s="5" t="n"/>
+      <c r="BV342" s="5" t="n"/>
     </row>
     <row r="343">
       <c r="C343" s="5" t="n"/>
@@ -8192,8 +8500,8 @@
       <c r="Y343" s="5" t="n"/>
       <c r="AB343" s="5" t="n"/>
       <c r="AI343" s="5" t="n"/>
-      <c r="AP343" s="5" t="n"/>
-      <c r="BM343" s="5" t="n"/>
+      <c r="AS343" s="5" t="n"/>
+      <c r="BV343" s="5" t="n"/>
     </row>
     <row r="344">
       <c r="C344" s="5" t="n"/>
@@ -8206,8 +8514,8 @@
       <c r="Y344" s="5" t="n"/>
       <c r="AB344" s="5" t="n"/>
       <c r="AI344" s="5" t="n"/>
-      <c r="AP344" s="5" t="n"/>
-      <c r="BM344" s="5" t="n"/>
+      <c r="AS344" s="5" t="n"/>
+      <c r="BV344" s="5" t="n"/>
     </row>
     <row r="345">
       <c r="C345" s="5" t="n"/>
@@ -8220,8 +8528,8 @@
       <c r="Y345" s="5" t="n"/>
       <c r="AB345" s="5" t="n"/>
       <c r="AI345" s="5" t="n"/>
-      <c r="AP345" s="5" t="n"/>
-      <c r="BM345" s="5" t="n"/>
+      <c r="AS345" s="5" t="n"/>
+      <c r="BV345" s="5" t="n"/>
     </row>
     <row r="346">
       <c r="C346" s="5" t="n"/>
@@ -8234,8 +8542,8 @@
       <c r="Y346" s="5" t="n"/>
       <c r="AB346" s="5" t="n"/>
       <c r="AI346" s="5" t="n"/>
-      <c r="AP346" s="5" t="n"/>
-      <c r="BM346" s="5" t="n"/>
+      <c r="AS346" s="5" t="n"/>
+      <c r="BV346" s="5" t="n"/>
     </row>
     <row r="347">
       <c r="C347" s="5" t="n"/>
@@ -8248,8 +8556,8 @@
       <c r="Y347" s="5" t="n"/>
       <c r="AB347" s="5" t="n"/>
       <c r="AI347" s="5" t="n"/>
-      <c r="AP347" s="5" t="n"/>
-      <c r="BM347" s="5" t="n"/>
+      <c r="AS347" s="5" t="n"/>
+      <c r="BV347" s="5" t="n"/>
     </row>
     <row r="348">
       <c r="C348" s="5" t="n"/>
@@ -8262,8 +8570,8 @@
       <c r="Y348" s="5" t="n"/>
       <c r="AB348" s="5" t="n"/>
       <c r="AI348" s="5" t="n"/>
-      <c r="AP348" s="5" t="n"/>
-      <c r="BM348" s="5" t="n"/>
+      <c r="AS348" s="5" t="n"/>
+      <c r="BV348" s="5" t="n"/>
     </row>
     <row r="349">
       <c r="C349" s="5" t="n"/>
@@ -8276,8 +8584,8 @@
       <c r="Y349" s="5" t="n"/>
       <c r="AB349" s="5" t="n"/>
       <c r="AI349" s="5" t="n"/>
-      <c r="AP349" s="5" t="n"/>
-      <c r="BM349" s="5" t="n"/>
+      <c r="AS349" s="5" t="n"/>
+      <c r="BV349" s="5" t="n"/>
     </row>
     <row r="350">
       <c r="C350" s="5" t="n"/>
@@ -8290,8 +8598,8 @@
       <c r="Y350" s="5" t="n"/>
       <c r="AB350" s="5" t="n"/>
       <c r="AI350" s="5" t="n"/>
-      <c r="AP350" s="5" t="n"/>
-      <c r="BM350" s="5" t="n"/>
+      <c r="AS350" s="5" t="n"/>
+      <c r="BV350" s="5" t="n"/>
     </row>
     <row r="351">
       <c r="C351" s="5" t="n"/>
@@ -8304,8 +8612,8 @@
       <c r="Y351" s="5" t="n"/>
       <c r="AB351" s="5" t="n"/>
       <c r="AI351" s="5" t="n"/>
-      <c r="AP351" s="5" t="n"/>
-      <c r="BM351" s="5" t="n"/>
+      <c r="AS351" s="5" t="n"/>
+      <c r="BV351" s="5" t="n"/>
     </row>
     <row r="352">
       <c r="C352" s="5" t="n"/>
@@ -8318,8 +8626,8 @@
       <c r="Y352" s="5" t="n"/>
       <c r="AB352" s="5" t="n"/>
       <c r="AI352" s="5" t="n"/>
-      <c r="AP352" s="5" t="n"/>
-      <c r="BM352" s="5" t="n"/>
+      <c r="AS352" s="5" t="n"/>
+      <c r="BV352" s="5" t="n"/>
     </row>
     <row r="353">
       <c r="C353" s="5" t="n"/>
@@ -8332,8 +8640,8 @@
       <c r="Y353" s="5" t="n"/>
       <c r="AB353" s="5" t="n"/>
       <c r="AI353" s="5" t="n"/>
-      <c r="AP353" s="5" t="n"/>
-      <c r="BM353" s="5" t="n"/>
+      <c r="AS353" s="5" t="n"/>
+      <c r="BV353" s="5" t="n"/>
     </row>
     <row r="354">
       <c r="C354" s="5" t="n"/>
@@ -8346,8 +8654,8 @@
       <c r="Y354" s="5" t="n"/>
       <c r="AB354" s="5" t="n"/>
       <c r="AI354" s="5" t="n"/>
-      <c r="AP354" s="5" t="n"/>
-      <c r="BM354" s="5" t="n"/>
+      <c r="AS354" s="5" t="n"/>
+      <c r="BV354" s="5" t="n"/>
     </row>
     <row r="355">
       <c r="C355" s="5" t="n"/>
@@ -8360,8 +8668,8 @@
       <c r="Y355" s="5" t="n"/>
       <c r="AB355" s="5" t="n"/>
       <c r="AI355" s="5" t="n"/>
-      <c r="AP355" s="5" t="n"/>
-      <c r="BM355" s="5" t="n"/>
+      <c r="AS355" s="5" t="n"/>
+      <c r="BV355" s="5" t="n"/>
     </row>
     <row r="356">
       <c r="C356" s="5" t="n"/>
@@ -8374,8 +8682,8 @@
       <c r="Y356" s="5" t="n"/>
       <c r="AB356" s="5" t="n"/>
       <c r="AI356" s="5" t="n"/>
-      <c r="AP356" s="5" t="n"/>
-      <c r="BM356" s="5" t="n"/>
+      <c r="AS356" s="5" t="n"/>
+      <c r="BV356" s="5" t="n"/>
     </row>
     <row r="357">
       <c r="C357" s="5" t="n"/>
@@ -8388,8 +8696,8 @@
       <c r="Y357" s="5" t="n"/>
       <c r="AB357" s="5" t="n"/>
       <c r="AI357" s="5" t="n"/>
-      <c r="AP357" s="5" t="n"/>
-      <c r="BM357" s="5" t="n"/>
+      <c r="AS357" s="5" t="n"/>
+      <c r="BV357" s="5" t="n"/>
     </row>
     <row r="358">
       <c r="C358" s="5" t="n"/>
@@ -8402,8 +8710,8 @@
       <c r="Y358" s="5" t="n"/>
       <c r="AB358" s="5" t="n"/>
       <c r="AI358" s="5" t="n"/>
-      <c r="AP358" s="5" t="n"/>
-      <c r="BM358" s="5" t="n"/>
+      <c r="AS358" s="5" t="n"/>
+      <c r="BV358" s="5" t="n"/>
     </row>
     <row r="359">
       <c r="C359" s="5" t="n"/>
@@ -8416,8 +8724,8 @@
       <c r="Y359" s="5" t="n"/>
       <c r="AB359" s="5" t="n"/>
       <c r="AI359" s="5" t="n"/>
-      <c r="AP359" s="5" t="n"/>
-      <c r="BM359" s="5" t="n"/>
+      <c r="AS359" s="5" t="n"/>
+      <c r="BV359" s="5" t="n"/>
     </row>
     <row r="360">
       <c r="C360" s="5" t="n"/>
@@ -8430,8 +8738,8 @@
       <c r="Y360" s="5" t="n"/>
       <c r="AB360" s="5" t="n"/>
       <c r="AI360" s="5" t="n"/>
-      <c r="AP360" s="5" t="n"/>
-      <c r="BM360" s="5" t="n"/>
+      <c r="AS360" s="5" t="n"/>
+      <c r="BV360" s="5" t="n"/>
     </row>
     <row r="361">
       <c r="C361" s="5" t="n"/>
@@ -8444,8 +8752,8 @@
       <c r="Y361" s="5" t="n"/>
       <c r="AB361" s="5" t="n"/>
       <c r="AI361" s="5" t="n"/>
-      <c r="AP361" s="5" t="n"/>
-      <c r="BM361" s="5" t="n"/>
+      <c r="AS361" s="5" t="n"/>
+      <c r="BV361" s="5" t="n"/>
     </row>
     <row r="362">
       <c r="C362" s="5" t="n"/>
@@ -8458,8 +8766,8 @@
       <c r="Y362" s="5" t="n"/>
       <c r="AB362" s="5" t="n"/>
       <c r="AI362" s="5" t="n"/>
-      <c r="AP362" s="5" t="n"/>
-      <c r="BM362" s="5" t="n"/>
+      <c r="AS362" s="5" t="n"/>
+      <c r="BV362" s="5" t="n"/>
     </row>
     <row r="363">
       <c r="C363" s="5" t="n"/>
@@ -8472,8 +8780,8 @@
       <c r="Y363" s="5" t="n"/>
       <c r="AB363" s="5" t="n"/>
       <c r="AI363" s="5" t="n"/>
-      <c r="AP363" s="5" t="n"/>
-      <c r="BM363" s="5" t="n"/>
+      <c r="AS363" s="5" t="n"/>
+      <c r="BV363" s="5" t="n"/>
     </row>
     <row r="364">
       <c r="C364" s="5" t="n"/>
@@ -8486,8 +8794,8 @@
       <c r="Y364" s="5" t="n"/>
       <c r="AB364" s="5" t="n"/>
       <c r="AI364" s="5" t="n"/>
-      <c r="AP364" s="5" t="n"/>
-      <c r="BM364" s="5" t="n"/>
+      <c r="AS364" s="5" t="n"/>
+      <c r="BV364" s="5" t="n"/>
     </row>
     <row r="365">
       <c r="C365" s="5" t="n"/>
@@ -8500,8 +8808,8 @@
       <c r="Y365" s="5" t="n"/>
       <c r="AB365" s="5" t="n"/>
       <c r="AI365" s="5" t="n"/>
-      <c r="AP365" s="5" t="n"/>
-      <c r="BM365" s="5" t="n"/>
+      <c r="AS365" s="5" t="n"/>
+      <c r="BV365" s="5" t="n"/>
     </row>
     <row r="366">
       <c r="C366" s="5" t="n"/>
@@ -8514,8 +8822,8 @@
       <c r="Y366" s="5" t="n"/>
       <c r="AB366" s="5" t="n"/>
       <c r="AI366" s="5" t="n"/>
-      <c r="AP366" s="5" t="n"/>
-      <c r="BM366" s="5" t="n"/>
+      <c r="AS366" s="5" t="n"/>
+      <c r="BV366" s="5" t="n"/>
     </row>
     <row r="367">
       <c r="C367" s="5" t="n"/>
@@ -8528,8 +8836,8 @@
       <c r="Y367" s="5" t="n"/>
       <c r="AB367" s="5" t="n"/>
       <c r="AI367" s="5" t="n"/>
-      <c r="AP367" s="5" t="n"/>
-      <c r="BM367" s="5" t="n"/>
+      <c r="AS367" s="5" t="n"/>
+      <c r="BV367" s="5" t="n"/>
     </row>
     <row r="368">
       <c r="C368" s="5" t="n"/>
@@ -8542,8 +8850,8 @@
       <c r="Y368" s="5" t="n"/>
       <c r="AB368" s="5" t="n"/>
       <c r="AI368" s="5" t="n"/>
-      <c r="AP368" s="5" t="n"/>
-      <c r="BM368" s="5" t="n"/>
+      <c r="AS368" s="5" t="n"/>
+      <c r="BV368" s="5" t="n"/>
     </row>
     <row r="369">
       <c r="C369" s="5" t="n"/>
@@ -8556,8 +8864,8 @@
       <c r="Y369" s="5" t="n"/>
       <c r="AB369" s="5" t="n"/>
       <c r="AI369" s="5" t="n"/>
-      <c r="AP369" s="5" t="n"/>
-      <c r="BM369" s="5" t="n"/>
+      <c r="AS369" s="5" t="n"/>
+      <c r="BV369" s="5" t="n"/>
     </row>
     <row r="370">
       <c r="C370" s="5" t="n"/>
@@ -8570,8 +8878,8 @@
       <c r="Y370" s="5" t="n"/>
       <c r="AB370" s="5" t="n"/>
       <c r="AI370" s="5" t="n"/>
-      <c r="AP370" s="5" t="n"/>
-      <c r="BM370" s="5" t="n"/>
+      <c r="AS370" s="5" t="n"/>
+      <c r="BV370" s="5" t="n"/>
     </row>
     <row r="371">
       <c r="C371" s="5" t="n"/>
@@ -8584,8 +8892,8 @@
       <c r="Y371" s="5" t="n"/>
       <c r="AB371" s="5" t="n"/>
       <c r="AI371" s="5" t="n"/>
-      <c r="AP371" s="5" t="n"/>
-      <c r="BM371" s="5" t="n"/>
+      <c r="AS371" s="5" t="n"/>
+      <c r="BV371" s="5" t="n"/>
     </row>
     <row r="372">
       <c r="C372" s="5" t="n"/>
@@ -8598,8 +8906,8 @@
       <c r="Y372" s="5" t="n"/>
       <c r="AB372" s="5" t="n"/>
       <c r="AI372" s="5" t="n"/>
-      <c r="AP372" s="5" t="n"/>
-      <c r="BM372" s="5" t="n"/>
+      <c r="AS372" s="5" t="n"/>
+      <c r="BV372" s="5" t="n"/>
     </row>
     <row r="373">
       <c r="C373" s="5" t="n"/>
@@ -8612,8 +8920,8 @@
       <c r="Y373" s="5" t="n"/>
       <c r="AB373" s="5" t="n"/>
       <c r="AI373" s="5" t="n"/>
-      <c r="AP373" s="5" t="n"/>
-      <c r="BM373" s="5" t="n"/>
+      <c r="AS373" s="5" t="n"/>
+      <c r="BV373" s="5" t="n"/>
     </row>
     <row r="374">
       <c r="C374" s="5" t="n"/>
@@ -8626,8 +8934,8 @@
       <c r="Y374" s="5" t="n"/>
       <c r="AB374" s="5" t="n"/>
       <c r="AI374" s="5" t="n"/>
-      <c r="AP374" s="5" t="n"/>
-      <c r="BM374" s="5" t="n"/>
+      <c r="AS374" s="5" t="n"/>
+      <c r="BV374" s="5" t="n"/>
     </row>
     <row r="375">
       <c r="C375" s="5" t="n"/>
@@ -8640,8 +8948,8 @@
       <c r="Y375" s="5" t="n"/>
       <c r="AB375" s="5" t="n"/>
       <c r="AI375" s="5" t="n"/>
-      <c r="AP375" s="5" t="n"/>
-      <c r="BM375" s="5" t="n"/>
+      <c r="AS375" s="5" t="n"/>
+      <c r="BV375" s="5" t="n"/>
     </row>
     <row r="376">
       <c r="C376" s="5" t="n"/>
@@ -8654,8 +8962,8 @@
       <c r="Y376" s="5" t="n"/>
       <c r="AB376" s="5" t="n"/>
       <c r="AI376" s="5" t="n"/>
-      <c r="AP376" s="5" t="n"/>
-      <c r="BM376" s="5" t="n"/>
+      <c r="AS376" s="5" t="n"/>
+      <c r="BV376" s="5" t="n"/>
     </row>
     <row r="377">
       <c r="C377" s="5" t="n"/>
@@ -8668,8 +8976,8 @@
       <c r="Y377" s="5" t="n"/>
       <c r="AB377" s="5" t="n"/>
       <c r="AI377" s="5" t="n"/>
-      <c r="AP377" s="5" t="n"/>
-      <c r="BM377" s="5" t="n"/>
+      <c r="AS377" s="5" t="n"/>
+      <c r="BV377" s="5" t="n"/>
     </row>
     <row r="378">
       <c r="C378" s="5" t="n"/>
@@ -8682,8 +8990,8 @@
       <c r="Y378" s="5" t="n"/>
       <c r="AB378" s="5" t="n"/>
       <c r="AI378" s="5" t="n"/>
-      <c r="AP378" s="5" t="n"/>
-      <c r="BM378" s="5" t="n"/>
+      <c r="AS378" s="5" t="n"/>
+      <c r="BV378" s="5" t="n"/>
     </row>
     <row r="379">
       <c r="C379" s="5" t="n"/>
@@ -8696,8 +9004,8 @@
       <c r="Y379" s="5" t="n"/>
       <c r="AB379" s="5" t="n"/>
       <c r="AI379" s="5" t="n"/>
-      <c r="AP379" s="5" t="n"/>
-      <c r="BM379" s="5" t="n"/>
+      <c r="AS379" s="5" t="n"/>
+      <c r="BV379" s="5" t="n"/>
     </row>
     <row r="380">
       <c r="C380" s="5" t="n"/>
@@ -8710,8 +9018,8 @@
       <c r="Y380" s="5" t="n"/>
       <c r="AB380" s="5" t="n"/>
       <c r="AI380" s="5" t="n"/>
-      <c r="AP380" s="5" t="n"/>
-      <c r="BM380" s="5" t="n"/>
+      <c r="AS380" s="5" t="n"/>
+      <c r="BV380" s="5" t="n"/>
     </row>
     <row r="381">
       <c r="C381" s="5" t="n"/>
@@ -8724,8 +9032,8 @@
       <c r="Y381" s="5" t="n"/>
       <c r="AB381" s="5" t="n"/>
       <c r="AI381" s="5" t="n"/>
-      <c r="AP381" s="5" t="n"/>
-      <c r="BM381" s="5" t="n"/>
+      <c r="AS381" s="5" t="n"/>
+      <c r="BV381" s="5" t="n"/>
     </row>
     <row r="382">
       <c r="C382" s="5" t="n"/>
@@ -8738,8 +9046,8 @@
       <c r="Y382" s="5" t="n"/>
       <c r="AB382" s="5" t="n"/>
       <c r="AI382" s="5" t="n"/>
-      <c r="AP382" s="5" t="n"/>
-      <c r="BM382" s="5" t="n"/>
+      <c r="AS382" s="5" t="n"/>
+      <c r="BV382" s="5" t="n"/>
     </row>
     <row r="383">
       <c r="C383" s="5" t="n"/>
@@ -8752,8 +9060,8 @@
       <c r="Y383" s="5" t="n"/>
       <c r="AB383" s="5" t="n"/>
       <c r="AI383" s="5" t="n"/>
-      <c r="AP383" s="5" t="n"/>
-      <c r="BM383" s="5" t="n"/>
+      <c r="AS383" s="5" t="n"/>
+      <c r="BV383" s="5" t="n"/>
     </row>
     <row r="384">
       <c r="C384" s="5" t="n"/>
@@ -8766,8 +9074,8 @@
       <c r="Y384" s="5" t="n"/>
       <c r="AB384" s="5" t="n"/>
       <c r="AI384" s="5" t="n"/>
-      <c r="AP384" s="5" t="n"/>
-      <c r="BM384" s="5" t="n"/>
+      <c r="AS384" s="5" t="n"/>
+      <c r="BV384" s="5" t="n"/>
     </row>
     <row r="385">
       <c r="C385" s="5" t="n"/>
@@ -8780,8 +9088,8 @@
       <c r="Y385" s="5" t="n"/>
       <c r="AB385" s="5" t="n"/>
       <c r="AI385" s="5" t="n"/>
-      <c r="AP385" s="5" t="n"/>
-      <c r="BM385" s="5" t="n"/>
+      <c r="AS385" s="5" t="n"/>
+      <c r="BV385" s="5" t="n"/>
     </row>
     <row r="386">
       <c r="C386" s="5" t="n"/>
@@ -8794,8 +9102,8 @@
       <c r="Y386" s="5" t="n"/>
       <c r="AB386" s="5" t="n"/>
       <c r="AI386" s="5" t="n"/>
-      <c r="AP386" s="5" t="n"/>
-      <c r="BM386" s="5" t="n"/>
+      <c r="AS386" s="5" t="n"/>
+      <c r="BV386" s="5" t="n"/>
     </row>
     <row r="387">
       <c r="C387" s="5" t="n"/>
@@ -8808,8 +9116,8 @@
       <c r="Y387" s="5" t="n"/>
       <c r="AB387" s="5" t="n"/>
       <c r="AI387" s="5" t="n"/>
-      <c r="AP387" s="5" t="n"/>
-      <c r="BM387" s="5" t="n"/>
+      <c r="AS387" s="5" t="n"/>
+      <c r="BV387" s="5" t="n"/>
     </row>
     <row r="388">
       <c r="C388" s="5" t="n"/>
@@ -8822,8 +9130,8 @@
       <c r="Y388" s="5" t="n"/>
       <c r="AB388" s="5" t="n"/>
       <c r="AI388" s="5" t="n"/>
-      <c r="AP388" s="5" t="n"/>
-      <c r="BM388" s="5" t="n"/>
+      <c r="AS388" s="5" t="n"/>
+      <c r="BV388" s="5" t="n"/>
     </row>
     <row r="389">
       <c r="C389" s="5" t="n"/>
@@ -8836,8 +9144,8 @@
       <c r="Y389" s="5" t="n"/>
       <c r="AB389" s="5" t="n"/>
       <c r="AI389" s="5" t="n"/>
-      <c r="AP389" s="5" t="n"/>
-      <c r="BM389" s="5" t="n"/>
+      <c r="AS389" s="5" t="n"/>
+      <c r="BV389" s="5" t="n"/>
     </row>
     <row r="390">
       <c r="C390" s="5" t="n"/>
@@ -8850,8 +9158,8 @@
       <c r="Y390" s="5" t="n"/>
       <c r="AB390" s="5" t="n"/>
       <c r="AI390" s="5" t="n"/>
-      <c r="AP390" s="5" t="n"/>
-      <c r="BM390" s="5" t="n"/>
+      <c r="AS390" s="5" t="n"/>
+      <c r="BV390" s="5" t="n"/>
     </row>
     <row r="391">
       <c r="C391" s="5" t="n"/>
@@ -8864,8 +9172,8 @@
       <c r="Y391" s="5" t="n"/>
       <c r="AB391" s="5" t="n"/>
       <c r="AI391" s="5" t="n"/>
-      <c r="AP391" s="5" t="n"/>
-      <c r="BM391" s="5" t="n"/>
+      <c r="AS391" s="5" t="n"/>
+      <c r="BV391" s="5" t="n"/>
     </row>
     <row r="392">
       <c r="C392" s="5" t="n"/>
@@ -8878,8 +9186,8 @@
       <c r="Y392" s="5" t="n"/>
       <c r="AB392" s="5" t="n"/>
       <c r="AI392" s="5" t="n"/>
-      <c r="AP392" s="5" t="n"/>
-      <c r="BM392" s="5" t="n"/>
+      <c r="AS392" s="5" t="n"/>
+      <c r="BV392" s="5" t="n"/>
     </row>
     <row r="393">
       <c r="C393" s="5" t="n"/>
@@ -8892,8 +9200,8 @@
       <c r="Y393" s="5" t="n"/>
       <c r="AB393" s="5" t="n"/>
       <c r="AI393" s="5" t="n"/>
-      <c r="AP393" s="5" t="n"/>
-      <c r="BM393" s="5" t="n"/>
+      <c r="AS393" s="5" t="n"/>
+      <c r="BV393" s="5" t="n"/>
     </row>
     <row r="394">
       <c r="C394" s="5" t="n"/>
@@ -8906,8 +9214,8 @@
       <c r="Y394" s="5" t="n"/>
       <c r="AB394" s="5" t="n"/>
       <c r="AI394" s="5" t="n"/>
-      <c r="AP394" s="5" t="n"/>
-      <c r="BM394" s="5" t="n"/>
+      <c r="AS394" s="5" t="n"/>
+      <c r="BV394" s="5" t="n"/>
     </row>
     <row r="395">
       <c r="C395" s="5" t="n"/>
@@ -8920,8 +9228,8 @@
       <c r="Y395" s="5" t="n"/>
       <c r="AB395" s="5" t="n"/>
       <c r="AI395" s="5" t="n"/>
-      <c r="AP395" s="5" t="n"/>
-      <c r="BM395" s="5" t="n"/>
+      <c r="AS395" s="5" t="n"/>
+      <c r="BV395" s="5" t="n"/>
     </row>
     <row r="396">
       <c r="C396" s="5" t="n"/>
@@ -8934,8 +9242,8 @@
       <c r="Y396" s="5" t="n"/>
       <c r="AB396" s="5" t="n"/>
       <c r="AI396" s="5" t="n"/>
-      <c r="AP396" s="5" t="n"/>
-      <c r="BM396" s="5" t="n"/>
+      <c r="AS396" s="5" t="n"/>
+      <c r="BV396" s="5" t="n"/>
     </row>
     <row r="397">
       <c r="C397" s="5" t="n"/>
@@ -8948,8 +9256,8 @@
       <c r="Y397" s="5" t="n"/>
       <c r="AB397" s="5" t="n"/>
       <c r="AI397" s="5" t="n"/>
-      <c r="AP397" s="5" t="n"/>
-      <c r="BM397" s="5" t="n"/>
+      <c r="AS397" s="5" t="n"/>
+      <c r="BV397" s="5" t="n"/>
     </row>
     <row r="398">
       <c r="C398" s="5" t="n"/>
@@ -8962,8 +9270,8 @@
       <c r="Y398" s="5" t="n"/>
       <c r="AB398" s="5" t="n"/>
       <c r="AI398" s="5" t="n"/>
-      <c r="AP398" s="5" t="n"/>
-      <c r="BM398" s="5" t="n"/>
+      <c r="AS398" s="5" t="n"/>
+      <c r="BV398" s="5" t="n"/>
     </row>
     <row r="399">
       <c r="C399" s="5" t="n"/>
@@ -8976,8 +9284,8 @@
       <c r="Y399" s="5" t="n"/>
       <c r="AB399" s="5" t="n"/>
       <c r="AI399" s="5" t="n"/>
-      <c r="AP399" s="5" t="n"/>
-      <c r="BM399" s="5" t="n"/>
+      <c r="AS399" s="5" t="n"/>
+      <c r="BV399" s="5" t="n"/>
     </row>
     <row r="400">
       <c r="C400" s="5" t="n"/>
@@ -8990,8 +9298,8 @@
       <c r="Y400" s="5" t="n"/>
       <c r="AB400" s="5" t="n"/>
       <c r="AI400" s="5" t="n"/>
-      <c r="AP400" s="5" t="n"/>
-      <c r="BM400" s="5" t="n"/>
+      <c r="AS400" s="5" t="n"/>
+      <c r="BV400" s="5" t="n"/>
     </row>
     <row r="401">
       <c r="C401" s="5" t="n"/>
@@ -9004,8 +9312,8 @@
       <c r="Y401" s="5" t="n"/>
       <c r="AB401" s="5" t="n"/>
       <c r="AI401" s="5" t="n"/>
-      <c r="AP401" s="5" t="n"/>
-      <c r="BM401" s="5" t="n"/>
+      <c r="AS401" s="5" t="n"/>
+      <c r="BV401" s="5" t="n"/>
     </row>
     <row r="402">
       <c r="C402" s="5" t="n"/>
@@ -9018,8 +9326,8 @@
       <c r="Y402" s="5" t="n"/>
       <c r="AB402" s="5" t="n"/>
       <c r="AI402" s="5" t="n"/>
-      <c r="AP402" s="5" t="n"/>
-      <c r="BM402" s="5" t="n"/>
+      <c r="AS402" s="5" t="n"/>
+      <c r="BV402" s="5" t="n"/>
     </row>
     <row r="403">
       <c r="C403" s="5" t="n"/>
@@ -9032,8 +9340,8 @@
       <c r="Y403" s="5" t="n"/>
       <c r="AB403" s="5" t="n"/>
       <c r="AI403" s="5" t="n"/>
-      <c r="AP403" s="5" t="n"/>
-      <c r="BM403" s="5" t="n"/>
+      <c r="AS403" s="5" t="n"/>
+      <c r="BV403" s="5" t="n"/>
     </row>
     <row r="404">
       <c r="C404" s="5" t="n"/>
@@ -9046,8 +9354,8 @@
       <c r="Y404" s="5" t="n"/>
       <c r="AB404" s="5" t="n"/>
       <c r="AI404" s="5" t="n"/>
-      <c r="AP404" s="5" t="n"/>
-      <c r="BM404" s="5" t="n"/>
+      <c r="AS404" s="5" t="n"/>
+      <c r="BV404" s="5" t="n"/>
     </row>
     <row r="405">
       <c r="C405" s="5" t="n"/>
@@ -9060,8 +9368,8 @@
       <c r="Y405" s="5" t="n"/>
       <c r="AB405" s="5" t="n"/>
       <c r="AI405" s="5" t="n"/>
-      <c r="AP405" s="5" t="n"/>
-      <c r="BM405" s="5" t="n"/>
+      <c r="AS405" s="5" t="n"/>
+      <c r="BV405" s="5" t="n"/>
     </row>
     <row r="406">
       <c r="C406" s="5" t="n"/>
@@ -9074,8 +9382,8 @@
       <c r="Y406" s="5" t="n"/>
       <c r="AB406" s="5" t="n"/>
       <c r="AI406" s="5" t="n"/>
-      <c r="AP406" s="5" t="n"/>
-      <c r="BM406" s="5" t="n"/>
+      <c r="AS406" s="5" t="n"/>
+      <c r="BV406" s="5" t="n"/>
     </row>
     <row r="407">
       <c r="C407" s="5" t="n"/>
@@ -9088,8 +9396,8 @@
       <c r="Y407" s="5" t="n"/>
       <c r="AB407" s="5" t="n"/>
       <c r="AI407" s="5" t="n"/>
-      <c r="AP407" s="5" t="n"/>
-      <c r="BM407" s="5" t="n"/>
+      <c r="AS407" s="5" t="n"/>
+      <c r="BV407" s="5" t="n"/>
     </row>
     <row r="408">
       <c r="C408" s="5" t="n"/>
@@ -9102,8 +9410,8 @@
       <c r="Y408" s="5" t="n"/>
       <c r="AB408" s="5" t="n"/>
       <c r="AI408" s="5" t="n"/>
-      <c r="AP408" s="5" t="n"/>
-      <c r="BM408" s="5" t="n"/>
+      <c r="AS408" s="5" t="n"/>
+      <c r="BV408" s="5" t="n"/>
     </row>
     <row r="409">
       <c r="C409" s="5" t="n"/>
@@ -9116,8 +9424,8 @@
       <c r="Y409" s="5" t="n"/>
       <c r="AB409" s="5" t="n"/>
       <c r="AI409" s="5" t="n"/>
-      <c r="AP409" s="5" t="n"/>
-      <c r="BM409" s="5" t="n"/>
+      <c r="AS409" s="5" t="n"/>
+      <c r="BV409" s="5" t="n"/>
     </row>
     <row r="410">
       <c r="C410" s="5" t="n"/>
@@ -9130,8 +9438,8 @@
       <c r="Y410" s="5" t="n"/>
       <c r="AB410" s="5" t="n"/>
       <c r="AI410" s="5" t="n"/>
-      <c r="AP410" s="5" t="n"/>
-      <c r="BM410" s="5" t="n"/>
+      <c r="AS410" s="5" t="n"/>
+      <c r="BV410" s="5" t="n"/>
     </row>
     <row r="411">
       <c r="C411" s="5" t="n"/>
@@ -9144,8 +9452,8 @@
       <c r="Y411" s="5" t="n"/>
       <c r="AB411" s="5" t="n"/>
       <c r="AI411" s="5" t="n"/>
-      <c r="AP411" s="5" t="n"/>
-      <c r="BM411" s="5" t="n"/>
+      <c r="AS411" s="5" t="n"/>
+      <c r="BV411" s="5" t="n"/>
     </row>
     <row r="412">
       <c r="C412" s="5" t="n"/>
@@ -9158,8 +9466,8 @@
       <c r="Y412" s="5" t="n"/>
       <c r="AB412" s="5" t="n"/>
       <c r="AI412" s="5" t="n"/>
-      <c r="AP412" s="5" t="n"/>
-      <c r="BM412" s="5" t="n"/>
+      <c r="AS412" s="5" t="n"/>
+      <c r="BV412" s="5" t="n"/>
     </row>
     <row r="413">
       <c r="C413" s="5" t="n"/>
@@ -9172,8 +9480,8 @@
       <c r="Y413" s="5" t="n"/>
       <c r="AB413" s="5" t="n"/>
       <c r="AI413" s="5" t="n"/>
-      <c r="AP413" s="5" t="n"/>
-      <c r="BM413" s="5" t="n"/>
+      <c r="AS413" s="5" t="n"/>
+      <c r="BV413" s="5" t="n"/>
     </row>
     <row r="414">
       <c r="C414" s="5" t="n"/>
@@ -9186,8 +9494,8 @@
       <c r="Y414" s="5" t="n"/>
       <c r="AB414" s="5" t="n"/>
       <c r="AI414" s="5" t="n"/>
-      <c r="AP414" s="5" t="n"/>
-      <c r="BM414" s="5" t="n"/>
+      <c r="AS414" s="5" t="n"/>
+      <c r="BV414" s="5" t="n"/>
     </row>
     <row r="415">
       <c r="C415" s="5" t="n"/>
@@ -9200,8 +9508,8 @@
       <c r="Y415" s="5" t="n"/>
       <c r="AB415" s="5" t="n"/>
       <c r="AI415" s="5" t="n"/>
-      <c r="AP415" s="5" t="n"/>
-      <c r="BM415" s="5" t="n"/>
+      <c r="AS415" s="5" t="n"/>
+      <c r="BV415" s="5" t="n"/>
     </row>
     <row r="416">
       <c r="C416" s="5" t="n"/>
@@ -9214,8 +9522,8 @@
       <c r="Y416" s="5" t="n"/>
       <c r="AB416" s="5" t="n"/>
       <c r="AI416" s="5" t="n"/>
-      <c r="AP416" s="5" t="n"/>
-      <c r="BM416" s="5" t="n"/>
+      <c r="AS416" s="5" t="n"/>
+      <c r="BV416" s="5" t="n"/>
     </row>
     <row r="417">
       <c r="C417" s="5" t="n"/>
@@ -9228,8 +9536,8 @@
       <c r="Y417" s="5" t="n"/>
       <c r="AB417" s="5" t="n"/>
       <c r="AI417" s="5" t="n"/>
-      <c r="AP417" s="5" t="n"/>
-      <c r="BM417" s="5" t="n"/>
+      <c r="AS417" s="5" t="n"/>
+      <c r="BV417" s="5" t="n"/>
     </row>
     <row r="418">
       <c r="C418" s="5" t="n"/>
@@ -9242,8 +9550,8 @@
       <c r="Y418" s="5" t="n"/>
       <c r="AB418" s="5" t="n"/>
       <c r="AI418" s="5" t="n"/>
-      <c r="AP418" s="5" t="n"/>
-      <c r="BM418" s="5" t="n"/>
+      <c r="AS418" s="5" t="n"/>
+      <c r="BV418" s="5" t="n"/>
     </row>
     <row r="419">
       <c r="C419" s="5" t="n"/>
@@ -9256,8 +9564,8 @@
       <c r="Y419" s="5" t="n"/>
       <c r="AB419" s="5" t="n"/>
       <c r="AI419" s="5" t="n"/>
-      <c r="AP419" s="5" t="n"/>
-      <c r="BM419" s="5" t="n"/>
+      <c r="AS419" s="5" t="n"/>
+      <c r="BV419" s="5" t="n"/>
     </row>
     <row r="420">
       <c r="C420" s="5" t="n"/>
@@ -9270,8 +9578,8 @@
       <c r="Y420" s="5" t="n"/>
       <c r="AB420" s="5" t="n"/>
       <c r="AI420" s="5" t="n"/>
-      <c r="AP420" s="5" t="n"/>
-      <c r="BM420" s="5" t="n"/>
+      <c r="AS420" s="5" t="n"/>
+      <c r="BV420" s="5" t="n"/>
     </row>
     <row r="421">
       <c r="C421" s="5" t="n"/>
@@ -9284,8 +9592,8 @@
       <c r="Y421" s="5" t="n"/>
       <c r="AB421" s="5" t="n"/>
       <c r="AI421" s="5" t="n"/>
-      <c r="AP421" s="5" t="n"/>
-      <c r="BM421" s="5" t="n"/>
+      <c r="AS421" s="5" t="n"/>
+      <c r="BV421" s="5" t="n"/>
     </row>
     <row r="422">
       <c r="C422" s="5" t="n"/>
@@ -9298,8 +9606,8 @@
       <c r="Y422" s="5" t="n"/>
       <c r="AB422" s="5" t="n"/>
       <c r="AI422" s="5" t="n"/>
-      <c r="AP422" s="5" t="n"/>
-      <c r="BM422" s="5" t="n"/>
+      <c r="AS422" s="5" t="n"/>
+      <c r="BV422" s="5" t="n"/>
     </row>
     <row r="423">
       <c r="C423" s="5" t="n"/>
@@ -9312,8 +9620,8 @@
       <c r="Y423" s="5" t="n"/>
       <c r="AB423" s="5" t="n"/>
       <c r="AI423" s="5" t="n"/>
-      <c r="AP423" s="5" t="n"/>
-      <c r="BM423" s="5" t="n"/>
+      <c r="AS423" s="5" t="n"/>
+      <c r="BV423" s="5" t="n"/>
     </row>
     <row r="424">
       <c r="C424" s="5" t="n"/>
@@ -9326,8 +9634,8 @@
       <c r="Y424" s="5" t="n"/>
       <c r="AB424" s="5" t="n"/>
       <c r="AI424" s="5" t="n"/>
-      <c r="AP424" s="5" t="n"/>
-      <c r="BM424" s="5" t="n"/>
+      <c r="AS424" s="5" t="n"/>
+      <c r="BV424" s="5" t="n"/>
     </row>
     <row r="425">
       <c r="C425" s="5" t="n"/>
@@ -9340,8 +9648,8 @@
       <c r="Y425" s="5" t="n"/>
       <c r="AB425" s="5" t="n"/>
       <c r="AI425" s="5" t="n"/>
-      <c r="AP425" s="5" t="n"/>
-      <c r="BM425" s="5" t="n"/>
+      <c r="AS425" s="5" t="n"/>
+      <c r="BV425" s="5" t="n"/>
     </row>
     <row r="426">
       <c r="C426" s="5" t="n"/>
@@ -9354,8 +9662,8 @@
       <c r="Y426" s="5" t="n"/>
       <c r="AB426" s="5" t="n"/>
       <c r="AI426" s="5" t="n"/>
-      <c r="AP426" s="5" t="n"/>
-      <c r="BM426" s="5" t="n"/>
+      <c r="AS426" s="5" t="n"/>
+      <c r="BV426" s="5" t="n"/>
     </row>
     <row r="427">
       <c r="C427" s="5" t="n"/>
@@ -9368,8 +9676,8 @@
       <c r="Y427" s="5" t="n"/>
       <c r="AB427" s="5" t="n"/>
       <c r="AI427" s="5" t="n"/>
-      <c r="AP427" s="5" t="n"/>
-      <c r="BM427" s="5" t="n"/>
+      <c r="AS427" s="5" t="n"/>
+      <c r="BV427" s="5" t="n"/>
     </row>
     <row r="428">
       <c r="C428" s="5" t="n"/>
@@ -9382,8 +9690,8 @@
       <c r="Y428" s="5" t="n"/>
       <c r="AB428" s="5" t="n"/>
       <c r="AI428" s="5" t="n"/>
-      <c r="AP428" s="5" t="n"/>
-      <c r="BM428" s="5" t="n"/>
+      <c r="AS428" s="5" t="n"/>
+      <c r="BV428" s="5" t="n"/>
     </row>
     <row r="429">
       <c r="C429" s="5" t="n"/>
@@ -9396,8 +9704,8 @@
       <c r="Y429" s="5" t="n"/>
       <c r="AB429" s="5" t="n"/>
       <c r="AI429" s="5" t="n"/>
-      <c r="AP429" s="5" t="n"/>
-      <c r="BM429" s="5" t="n"/>
+      <c r="AS429" s="5" t="n"/>
+      <c r="BV429" s="5" t="n"/>
     </row>
     <row r="430">
       <c r="C430" s="5" t="n"/>
@@ -9410,8 +9718,8 @@
       <c r="Y430" s="5" t="n"/>
       <c r="AB430" s="5" t="n"/>
       <c r="AI430" s="5" t="n"/>
-      <c r="AP430" s="5" t="n"/>
-      <c r="BM430" s="5" t="n"/>
+      <c r="AS430" s="5" t="n"/>
+      <c r="BV430" s="5" t="n"/>
     </row>
     <row r="431">
       <c r="C431" s="5" t="n"/>
@@ -9424,8 +9732,8 @@
       <c r="Y431" s="5" t="n"/>
       <c r="AB431" s="5" t="n"/>
       <c r="AI431" s="5" t="n"/>
-      <c r="AP431" s="5" t="n"/>
-      <c r="BM431" s="5" t="n"/>
+      <c r="AS431" s="5" t="n"/>
+      <c r="BV431" s="5" t="n"/>
     </row>
     <row r="432">
       <c r="C432" s="5" t="n"/>
@@ -9438,8 +9746,8 @@
       <c r="Y432" s="5" t="n"/>
       <c r="AB432" s="5" t="n"/>
       <c r="AI432" s="5" t="n"/>
-      <c r="AP432" s="5" t="n"/>
-      <c r="BM432" s="5" t="n"/>
+      <c r="AS432" s="5" t="n"/>
+      <c r="BV432" s="5" t="n"/>
     </row>
     <row r="433">
       <c r="C433" s="5" t="n"/>
@@ -9452,8 +9760,8 @@
       <c r="Y433" s="5" t="n"/>
       <c r="AB433" s="5" t="n"/>
       <c r="AI433" s="5" t="n"/>
-      <c r="AP433" s="5" t="n"/>
-      <c r="BM433" s="5" t="n"/>
+      <c r="AS433" s="5" t="n"/>
+      <c r="BV433" s="5" t="n"/>
     </row>
     <row r="434">
       <c r="C434" s="5" t="n"/>
@@ -9466,8 +9774,8 @@
       <c r="Y434" s="5" t="n"/>
       <c r="AB434" s="5" t="n"/>
       <c r="AI434" s="5" t="n"/>
-      <c r="AP434" s="5" t="n"/>
-      <c r="BM434" s="5" t="n"/>
+      <c r="AS434" s="5" t="n"/>
+      <c r="BV434" s="5" t="n"/>
     </row>
     <row r="435">
       <c r="C435" s="5" t="n"/>
@@ -9480,8 +9788,8 @@
       <c r="Y435" s="5" t="n"/>
       <c r="AB435" s="5" t="n"/>
       <c r="AI435" s="5" t="n"/>
-      <c r="AP435" s="5" t="n"/>
-      <c r="BM435" s="5" t="n"/>
+      <c r="AS435" s="5" t="n"/>
+      <c r="BV435" s="5" t="n"/>
     </row>
     <row r="436">
       <c r="C436" s="5" t="n"/>
@@ -9494,8 +9802,8 @@
       <c r="Y436" s="5" t="n"/>
       <c r="AB436" s="5" t="n"/>
       <c r="AI436" s="5" t="n"/>
-      <c r="AP436" s="5" t="n"/>
-      <c r="BM436" s="5" t="n"/>
+      <c r="AS436" s="5" t="n"/>
+      <c r="BV436" s="5" t="n"/>
     </row>
     <row r="437">
       <c r="C437" s="5" t="n"/>
@@ -9508,8 +9816,8 @@
       <c r="Y437" s="5" t="n"/>
       <c r="AB437" s="5" t="n"/>
       <c r="AI437" s="5" t="n"/>
-      <c r="AP437" s="5" t="n"/>
-      <c r="BM437" s="5" t="n"/>
+      <c r="AS437" s="5" t="n"/>
+      <c r="BV437" s="5" t="n"/>
     </row>
     <row r="438">
       <c r="C438" s="5" t="n"/>
@@ -9522,8 +9830,8 @@
       <c r="Y438" s="5" t="n"/>
       <c r="AB438" s="5" t="n"/>
       <c r="AI438" s="5" t="n"/>
-      <c r="AP438" s="5" t="n"/>
-      <c r="BM438" s="5" t="n"/>
+      <c r="AS438" s="5" t="n"/>
+      <c r="BV438" s="5" t="n"/>
     </row>
     <row r="439">
       <c r="C439" s="5" t="n"/>
@@ -9536,8 +9844,8 @@
       <c r="Y439" s="5" t="n"/>
       <c r="AB439" s="5" t="n"/>
       <c r="AI439" s="5" t="n"/>
-      <c r="AP439" s="5" t="n"/>
-      <c r="BM439" s="5" t="n"/>
+      <c r="AS439" s="5" t="n"/>
+      <c r="BV439" s="5" t="n"/>
     </row>
     <row r="440">
       <c r="C440" s="5" t="n"/>
@@ -9550,8 +9858,8 @@
       <c r="Y440" s="5" t="n"/>
       <c r="AB440" s="5" t="n"/>
       <c r="AI440" s="5" t="n"/>
-      <c r="AP440" s="5" t="n"/>
-      <c r="BM440" s="5" t="n"/>
+      <c r="AS440" s="5" t="n"/>
+      <c r="BV440" s="5" t="n"/>
     </row>
     <row r="441">
       <c r="C441" s="5" t="n"/>
@@ -9564,8 +9872,8 @@
       <c r="Y441" s="5" t="n"/>
       <c r="AB441" s="5" t="n"/>
       <c r="AI441" s="5" t="n"/>
-      <c r="AP441" s="5" t="n"/>
-      <c r="BM441" s="5" t="n"/>
+      <c r="AS441" s="5" t="n"/>
+      <c r="BV441" s="5" t="n"/>
     </row>
     <row r="442">
       <c r="C442" s="5" t="n"/>
@@ -9578,8 +9886,8 @@
       <c r="Y442" s="5" t="n"/>
       <c r="AB442" s="5" t="n"/>
       <c r="AI442" s="5" t="n"/>
-      <c r="AP442" s="5" t="n"/>
-      <c r="BM442" s="5" t="n"/>
+      <c r="AS442" s="5" t="n"/>
+      <c r="BV442" s="5" t="n"/>
     </row>
     <row r="443">
       <c r="C443" s="5" t="n"/>
@@ -9592,8 +9900,8 @@
       <c r="Y443" s="5" t="n"/>
       <c r="AB443" s="5" t="n"/>
       <c r="AI443" s="5" t="n"/>
-      <c r="AP443" s="5" t="n"/>
-      <c r="BM443" s="5" t="n"/>
+      <c r="AS443" s="5" t="n"/>
+      <c r="BV443" s="5" t="n"/>
     </row>
     <row r="444">
       <c r="C444" s="5" t="n"/>
@@ -9606,8 +9914,8 @@
       <c r="Y444" s="5" t="n"/>
       <c r="AB444" s="5" t="n"/>
       <c r="AI444" s="5" t="n"/>
-      <c r="AP444" s="5" t="n"/>
-      <c r="BM444" s="5" t="n"/>
+      <c r="AS444" s="5" t="n"/>
+      <c r="BV444" s="5" t="n"/>
     </row>
     <row r="445">
       <c r="C445" s="5" t="n"/>
@@ -9620,8 +9928,8 @@
       <c r="Y445" s="5" t="n"/>
       <c r="AB445" s="5" t="n"/>
       <c r="AI445" s="5" t="n"/>
-      <c r="AP445" s="5" t="n"/>
-      <c r="BM445" s="5" t="n"/>
+      <c r="AS445" s="5" t="n"/>
+      <c r="BV445" s="5" t="n"/>
     </row>
     <row r="446">
       <c r="C446" s="5" t="n"/>
@@ -9634,8 +9942,8 @@
       <c r="Y446" s="5" t="n"/>
       <c r="AB446" s="5" t="n"/>
       <c r="AI446" s="5" t="n"/>
-      <c r="AP446" s="5" t="n"/>
-      <c r="BM446" s="5" t="n"/>
+      <c r="AS446" s="5" t="n"/>
+      <c r="BV446" s="5" t="n"/>
     </row>
     <row r="447">
       <c r="C447" s="5" t="n"/>
@@ -9648,8 +9956,8 @@
       <c r="Y447" s="5" t="n"/>
       <c r="AB447" s="5" t="n"/>
       <c r="AI447" s="5" t="n"/>
-      <c r="AP447" s="5" t="n"/>
-      <c r="BM447" s="5" t="n"/>
+      <c r="AS447" s="5" t="n"/>
+      <c r="BV447" s="5" t="n"/>
     </row>
     <row r="448">
       <c r="C448" s="5" t="n"/>
@@ -9662,8 +9970,8 @@
       <c r="Y448" s="5" t="n"/>
       <c r="AB448" s="5" t="n"/>
       <c r="AI448" s="5" t="n"/>
-      <c r="AP448" s="5" t="n"/>
-      <c r="BM448" s="5" t="n"/>
+      <c r="AS448" s="5" t="n"/>
+      <c r="BV448" s="5" t="n"/>
     </row>
     <row r="449">
       <c r="C449" s="5" t="n"/>
@@ -9676,8 +9984,8 @@
       <c r="Y449" s="5" t="n"/>
       <c r="AB449" s="5" t="n"/>
       <c r="AI449" s="5" t="n"/>
-      <c r="AP449" s="5" t="n"/>
-      <c r="BM449" s="5" t="n"/>
+      <c r="AS449" s="5" t="n"/>
+      <c r="BV449" s="5" t="n"/>
     </row>
     <row r="450">
       <c r="C450" s="5" t="n"/>
@@ -9690,8 +9998,8 @@
       <c r="Y450" s="5" t="n"/>
       <c r="AB450" s="5" t="n"/>
       <c r="AI450" s="5" t="n"/>
-      <c r="AP450" s="5" t="n"/>
-      <c r="BM450" s="5" t="n"/>
+      <c r="AS450" s="5" t="n"/>
+      <c r="BV450" s="5" t="n"/>
     </row>
     <row r="451">
       <c r="C451" s="5" t="n"/>
@@ -9704,8 +10012,8 @@
       <c r="Y451" s="5" t="n"/>
       <c r="AB451" s="5" t="n"/>
       <c r="AI451" s="5" t="n"/>
-      <c r="AP451" s="5" t="n"/>
-      <c r="BM451" s="5" t="n"/>
+      <c r="AS451" s="5" t="n"/>
+      <c r="BV451" s="5" t="n"/>
     </row>
     <row r="452">
       <c r="C452" s="5" t="n"/>
@@ -9718,8 +10026,8 @@
       <c r="Y452" s="5" t="n"/>
       <c r="AB452" s="5" t="n"/>
       <c r="AI452" s="5" t="n"/>
-      <c r="AP452" s="5" t="n"/>
-      <c r="BM452" s="5" t="n"/>
+      <c r="AS452" s="5" t="n"/>
+      <c r="BV452" s="5" t="n"/>
     </row>
     <row r="453">
       <c r="C453" s="5" t="n"/>
@@ -9732,8 +10040,8 @@
       <c r="Y453" s="5" t="n"/>
       <c r="AB453" s="5" t="n"/>
       <c r="AI453" s="5" t="n"/>
-      <c r="AP453" s="5" t="n"/>
-      <c r="BM453" s="5" t="n"/>
+      <c r="AS453" s="5" t="n"/>
+      <c r="BV453" s="5" t="n"/>
     </row>
     <row r="454">
       <c r="C454" s="5" t="n"/>
@@ -9746,8 +10054,8 @@
       <c r="Y454" s="5" t="n"/>
       <c r="AB454" s="5" t="n"/>
       <c r="AI454" s="5" t="n"/>
-      <c r="AP454" s="5" t="n"/>
-      <c r="BM454" s="5" t="n"/>
+      <c r="AS454" s="5" t="n"/>
+      <c r="BV454" s="5" t="n"/>
     </row>
     <row r="455">
       <c r="C455" s="5" t="n"/>
@@ -9760,8 +10068,8 @@
       <c r="Y455" s="5" t="n"/>
       <c r="AB455" s="5" t="n"/>
       <c r="AI455" s="5" t="n"/>
-      <c r="AP455" s="5" t="n"/>
-      <c r="BM455" s="5" t="n"/>
+      <c r="AS455" s="5" t="n"/>
+      <c r="BV455" s="5" t="n"/>
     </row>
     <row r="456">
       <c r="C456" s="5" t="n"/>
@@ -9774,8 +10082,8 @@
       <c r="Y456" s="5" t="n"/>
       <c r="AB456" s="5" t="n"/>
       <c r="AI456" s="5" t="n"/>
-      <c r="AP456" s="5" t="n"/>
-      <c r="BM456" s="5" t="n"/>
+      <c r="AS456" s="5" t="n"/>
+      <c r="BV456" s="5" t="n"/>
     </row>
     <row r="457">
       <c r="C457" s="5" t="n"/>
@@ -9788,8 +10096,8 @@
       <c r="Y457" s="5" t="n"/>
       <c r="AB457" s="5" t="n"/>
       <c r="AI457" s="5" t="n"/>
-      <c r="AP457" s="5" t="n"/>
-      <c r="BM457" s="5" t="n"/>
+      <c r="AS457" s="5" t="n"/>
+      <c r="BV457" s="5" t="n"/>
     </row>
     <row r="458">
       <c r="C458" s="5" t="n"/>
@@ -9802,8 +10110,8 @@
       <c r="Y458" s="5" t="n"/>
       <c r="AB458" s="5" t="n"/>
       <c r="AI458" s="5" t="n"/>
-      <c r="AP458" s="5" t="n"/>
-      <c r="BM458" s="5" t="n"/>
+      <c r="AS458" s="5" t="n"/>
+      <c r="BV458" s="5" t="n"/>
     </row>
     <row r="459">
       <c r="C459" s="5" t="n"/>
@@ -9816,8 +10124,8 @@
       <c r="Y459" s="5" t="n"/>
       <c r="AB459" s="5" t="n"/>
       <c r="AI459" s="5" t="n"/>
-      <c r="AP459" s="5" t="n"/>
-      <c r="BM459" s="5" t="n"/>
+      <c r="AS459" s="5" t="n"/>
+      <c r="BV459" s="5" t="n"/>
     </row>
     <row r="460">
       <c r="C460" s="5" t="n"/>
@@ -9830,8 +10138,8 @@
       <c r="Y460" s="5" t="n"/>
       <c r="AB460" s="5" t="n"/>
       <c r="AI460" s="5" t="n"/>
-      <c r="AP460" s="5" t="n"/>
-      <c r="BM460" s="5" t="n"/>
+      <c r="AS460" s="5" t="n"/>
+      <c r="BV460" s="5" t="n"/>
     </row>
     <row r="461">
       <c r="C461" s="5" t="n"/>
@@ -9844,8 +10152,8 @@
       <c r="Y461" s="5" t="n"/>
       <c r="AB461" s="5" t="n"/>
       <c r="AI461" s="5" t="n"/>
-      <c r="AP461" s="5" t="n"/>
-      <c r="BM461" s="5" t="n"/>
+      <c r="AS461" s="5" t="n"/>
+      <c r="BV461" s="5" t="n"/>
     </row>
     <row r="462">
       <c r="C462" s="5" t="n"/>
@@ -9858,8 +10166,8 @@
       <c r="Y462" s="5" t="n"/>
       <c r="AB462" s="5" t="n"/>
       <c r="AI462" s="5" t="n"/>
-      <c r="AP462" s="5" t="n"/>
-      <c r="BM462" s="5" t="n"/>
+      <c r="AS462" s="5" t="n"/>
+      <c r="BV462" s="5" t="n"/>
     </row>
     <row r="463">
       <c r="C463" s="5" t="n"/>
@@ -9872,8 +10180,8 @@
       <c r="Y463" s="5" t="n"/>
       <c r="AB463" s="5" t="n"/>
       <c r="AI463" s="5" t="n"/>
-      <c r="AP463" s="5" t="n"/>
-      <c r="BM463" s="5" t="n"/>
+      <c r="AS463" s="5" t="n"/>
+      <c r="BV463" s="5" t="n"/>
     </row>
     <row r="464">
       <c r="C464" s="5" t="n"/>
@@ -9886,8 +10194,8 @@
       <c r="Y464" s="5" t="n"/>
       <c r="AB464" s="5" t="n"/>
       <c r="AI464" s="5" t="n"/>
-      <c r="AP464" s="5" t="n"/>
-      <c r="BM464" s="5" t="n"/>
+      <c r="AS464" s="5" t="n"/>
+      <c r="BV464" s="5" t="n"/>
     </row>
     <row r="465">
       <c r="C465" s="5" t="n"/>
@@ -9900,8 +10208,8 @@
       <c r="Y465" s="5" t="n"/>
       <c r="AB465" s="5" t="n"/>
       <c r="AI465" s="5" t="n"/>
-      <c r="AP465" s="5" t="n"/>
-      <c r="BM465" s="5" t="n"/>
+      <c r="AS465" s="5" t="n"/>
+      <c r="BV465" s="5" t="n"/>
     </row>
     <row r="466">
       <c r="C466" s="5" t="n"/>
@@ -9914,8 +10222,8 @@
       <c r="Y466" s="5" t="n"/>
       <c r="AB466" s="5" t="n"/>
       <c r="AI466" s="5" t="n"/>
-      <c r="AP466" s="5" t="n"/>
-      <c r="BM466" s="5" t="n"/>
+      <c r="AS466" s="5" t="n"/>
+      <c r="BV466" s="5" t="n"/>
     </row>
     <row r="467">
       <c r="C467" s="5" t="n"/>
@@ -9928,8 +10236,8 @@
       <c r="Y467" s="5" t="n"/>
       <c r="AB467" s="5" t="n"/>
       <c r="AI467" s="5" t="n"/>
-      <c r="AP467" s="5" t="n"/>
-      <c r="BM467" s="5" t="n"/>
+      <c r="AS467" s="5" t="n"/>
+      <c r="BV467" s="5" t="n"/>
     </row>
     <row r="468">
       <c r="C468" s="5" t="n"/>
@@ -9942,8 +10250,8 @@
       <c r="Y468" s="5" t="n"/>
       <c r="AB468" s="5" t="n"/>
       <c r="AI468" s="5" t="n"/>
-      <c r="AP468" s="5" t="n"/>
-      <c r="BM468" s="5" t="n"/>
+      <c r="AS468" s="5" t="n"/>
+      <c r="BV468" s="5" t="n"/>
     </row>
     <row r="469">
       <c r="C469" s="5" t="n"/>
@@ -9956,8 +10264,8 @@
       <c r="Y469" s="5" t="n"/>
       <c r="AB469" s="5" t="n"/>
       <c r="AI469" s="5" t="n"/>
-      <c r="AP469" s="5" t="n"/>
-      <c r="BM469" s="5" t="n"/>
+      <c r="AS469" s="5" t="n"/>
+      <c r="BV469" s="5" t="n"/>
     </row>
     <row r="470">
       <c r="C470" s="5" t="n"/>
@@ -9970,8 +10278,8 @@
       <c r="Y470" s="5" t="n"/>
       <c r="AB470" s="5" t="n"/>
       <c r="AI470" s="5" t="n"/>
-      <c r="AP470" s="5" t="n"/>
-      <c r="BM470" s="5" t="n"/>
+      <c r="AS470" s="5" t="n"/>
+      <c r="BV470" s="5" t="n"/>
     </row>
     <row r="471">
       <c r="C471" s="5" t="n"/>
@@ -9984,8 +10292,8 @@
       <c r="Y471" s="5" t="n"/>
       <c r="AB471" s="5" t="n"/>
       <c r="AI471" s="5" t="n"/>
-      <c r="AP471" s="5" t="n"/>
-      <c r="BM471" s="5" t="n"/>
+      <c r="AS471" s="5" t="n"/>
+      <c r="BV471" s="5" t="n"/>
     </row>
     <row r="472">
       <c r="C472" s="5" t="n"/>
@@ -9998,8 +10306,8 @@
       <c r="Y472" s="5" t="n"/>
       <c r="AB472" s="5" t="n"/>
       <c r="AI472" s="5" t="n"/>
-      <c r="AP472" s="5" t="n"/>
-      <c r="BM472" s="5" t="n"/>
+      <c r="AS472" s="5" t="n"/>
+      <c r="BV472" s="5" t="n"/>
     </row>
     <row r="473">
       <c r="C473" s="5" t="n"/>
@@ -10012,8 +10320,8 @@
       <c r="Y473" s="5" t="n"/>
       <c r="AB473" s="5" t="n"/>
       <c r="AI473" s="5" t="n"/>
-      <c r="AP473" s="5" t="n"/>
-      <c r="BM473" s="5" t="n"/>
+      <c r="AS473" s="5" t="n"/>
+      <c r="BV473" s="5" t="n"/>
     </row>
     <row r="474">
       <c r="C474" s="5" t="n"/>
@@ -10026,8 +10334,8 @@
       <c r="Y474" s="5" t="n"/>
       <c r="AB474" s="5" t="n"/>
       <c r="AI474" s="5" t="n"/>
-      <c r="AP474" s="5" t="n"/>
-      <c r="BM474" s="5" t="n"/>
+      <c r="AS474" s="5" t="n"/>
+      <c r="BV474" s="5" t="n"/>
     </row>
     <row r="475">
       <c r="C475" s="5" t="n"/>
@@ -10040,8 +10348,8 @@
       <c r="Y475" s="5" t="n"/>
       <c r="AB475" s="5" t="n"/>
       <c r="AI475" s="5" t="n"/>
-      <c r="AP475" s="5" t="n"/>
-      <c r="BM475" s="5" t="n"/>
+      <c r="AS475" s="5" t="n"/>
+      <c r="BV475" s="5" t="n"/>
     </row>
     <row r="476">
       <c r="C476" s="5" t="n"/>
@@ -10054,8 +10362,8 @@
       <c r="Y476" s="5" t="n"/>
       <c r="AB476" s="5" t="n"/>
       <c r="AI476" s="5" t="n"/>
-      <c r="AP476" s="5" t="n"/>
-      <c r="BM476" s="5" t="n"/>
+      <c r="AS476" s="5" t="n"/>
+      <c r="BV476" s="5" t="n"/>
     </row>
     <row r="477">
       <c r="C477" s="5" t="n"/>
@@ -10068,8 +10376,8 @@
       <c r="Y477" s="5" t="n"/>
       <c r="AB477" s="5" t="n"/>
       <c r="AI477" s="5" t="n"/>
-      <c r="AP477" s="5" t="n"/>
-      <c r="BM477" s="5" t="n"/>
+      <c r="AS477" s="5" t="n"/>
+      <c r="BV477" s="5" t="n"/>
     </row>
     <row r="478">
       <c r="C478" s="5" t="n"/>
@@ -10082,8 +10390,8 @@
       <c r="Y478" s="5" t="n"/>
       <c r="AB478" s="5" t="n"/>
       <c r="AI478" s="5" t="n"/>
-      <c r="AP478" s="5" t="n"/>
-      <c r="BM478" s="5" t="n"/>
+      <c r="AS478" s="5" t="n"/>
+      <c r="BV478" s="5" t="n"/>
     </row>
     <row r="479">
       <c r="C479" s="5" t="n"/>
@@ -10096,8 +10404,8 @@
       <c r="Y479" s="5" t="n"/>
       <c r="AB479" s="5" t="n"/>
       <c r="AI479" s="5" t="n"/>
-      <c r="AP479" s="5" t="n"/>
-      <c r="BM479" s="5" t="n"/>
+      <c r="AS479" s="5" t="n"/>
+      <c r="BV479" s="5" t="n"/>
     </row>
     <row r="480">
       <c r="C480" s="5" t="n"/>
@@ -10110,8 +10418,8 @@
       <c r="Y480" s="5" t="n"/>
       <c r="AB480" s="5" t="n"/>
       <c r="AI480" s="5" t="n"/>
-      <c r="AP480" s="5" t="n"/>
-      <c r="BM480" s="5" t="n"/>
+      <c r="AS480" s="5" t="n"/>
+      <c r="BV480" s="5" t="n"/>
     </row>
     <row r="481">
       <c r="C481" s="5" t="n"/>
@@ -10124,8 +10432,8 @@
       <c r="Y481" s="5" t="n"/>
       <c r="AB481" s="5" t="n"/>
       <c r="AI481" s="5" t="n"/>
-      <c r="AP481" s="5" t="n"/>
-      <c r="BM481" s="5" t="n"/>
+      <c r="AS481" s="5" t="n"/>
+      <c r="BV481" s="5" t="n"/>
     </row>
     <row r="482">
       <c r="C482" s="5" t="n"/>
@@ -10138,8 +10446,8 @@
       <c r="Y482" s="5" t="n"/>
       <c r="AB482" s="5" t="n"/>
       <c r="AI482" s="5" t="n"/>
-      <c r="AP482" s="5" t="n"/>
-      <c r="BM482" s="5" t="n"/>
+      <c r="AS482" s="5" t="n"/>
+      <c r="BV482" s="5" t="n"/>
     </row>
     <row r="483">
       <c r="C483" s="5" t="n"/>
@@ -10152,8 +10460,8 @@
       <c r="Y483" s="5" t="n"/>
       <c r="AB483" s="5" t="n"/>
       <c r="AI483" s="5" t="n"/>
-      <c r="AP483" s="5" t="n"/>
-      <c r="BM483" s="5" t="n"/>
+      <c r="AS483" s="5" t="n"/>
+      <c r="BV483" s="5" t="n"/>
     </row>
     <row r="484">
       <c r="C484" s="5" t="n"/>
@@ -10166,8 +10474,8 @@
       <c r="Y484" s="5" t="n"/>
       <c r="AB484" s="5" t="n"/>
       <c r="AI484" s="5" t="n"/>
-      <c r="AP484" s="5" t="n"/>
-      <c r="BM484" s="5" t="n"/>
+      <c r="AS484" s="5" t="n"/>
+      <c r="BV484" s="5" t="n"/>
     </row>
     <row r="485">
       <c r="C485" s="5" t="n"/>
@@ -10180,8 +10488,8 @@
       <c r="Y485" s="5" t="n"/>
       <c r="AB485" s="5" t="n"/>
       <c r="AI485" s="5" t="n"/>
-      <c r="AP485" s="5" t="n"/>
-      <c r="BM485" s="5" t="n"/>
+      <c r="AS485" s="5" t="n"/>
+      <c r="BV485" s="5" t="n"/>
     </row>
     <row r="486">
       <c r="C486" s="5" t="n"/>
@@ -10194,8 +10502,8 @@
       <c r="Y486" s="5" t="n"/>
       <c r="AB486" s="5" t="n"/>
       <c r="AI486" s="5" t="n"/>
-      <c r="AP486" s="5" t="n"/>
-      <c r="BM486" s="5" t="n"/>
+      <c r="AS486" s="5" t="n"/>
+      <c r="BV486" s="5" t="n"/>
     </row>
     <row r="487">
       <c r="C487" s="5" t="n"/>
@@ -10208,8 +10516,8 @@
       <c r="Y487" s="5" t="n"/>
       <c r="AB487" s="5" t="n"/>
       <c r="AI487" s="5" t="n"/>
-      <c r="AP487" s="5" t="n"/>
-      <c r="BM487" s="5" t="n"/>
+      <c r="AS487" s="5" t="n"/>
+      <c r="BV487" s="5" t="n"/>
     </row>
     <row r="488">
       <c r="C488" s="5" t="n"/>
@@ -10222,8 +10530,8 @@
       <c r="Y488" s="5" t="n"/>
       <c r="AB488" s="5" t="n"/>
       <c r="AI488" s="5" t="n"/>
-      <c r="AP488" s="5" t="n"/>
-      <c r="BM488" s="5" t="n"/>
+      <c r="AS488" s="5" t="n"/>
+      <c r="BV488" s="5" t="n"/>
     </row>
     <row r="489">
       <c r="C489" s="5" t="n"/>
@@ -10236,8 +10544,8 @@
       <c r="Y489" s="5" t="n"/>
       <c r="AB489" s="5" t="n"/>
       <c r="AI489" s="5" t="n"/>
-      <c r="AP489" s="5" t="n"/>
-      <c r="BM489" s="5" t="n"/>
+      <c r="AS489" s="5" t="n"/>
+      <c r="BV489" s="5" t="n"/>
     </row>
     <row r="490">
       <c r="C490" s="5" t="n"/>
@@ -10250,8 +10558,8 @@
       <c r="Y490" s="5" t="n"/>
       <c r="AB490" s="5" t="n"/>
       <c r="AI490" s="5" t="n"/>
-      <c r="AP490" s="5" t="n"/>
-      <c r="BM490" s="5" t="n"/>
+      <c r="AS490" s="5" t="n"/>
+      <c r="BV490" s="5" t="n"/>
     </row>
     <row r="491">
       <c r="C491" s="5" t="n"/>
@@ -10264,8 +10572,8 @@
       <c r="Y491" s="5" t="n"/>
       <c r="AB491" s="5" t="n"/>
       <c r="AI491" s="5" t="n"/>
-      <c r="AP491" s="5" t="n"/>
-      <c r="BM491" s="5" t="n"/>
+      <c r="AS491" s="5" t="n"/>
+      <c r="BV491" s="5" t="n"/>
     </row>
     <row r="492">
       <c r="C492" s="5" t="n"/>
@@ -10278,8 +10586,8 @@
       <c r="Y492" s="5" t="n"/>
       <c r="AB492" s="5" t="n"/>
       <c r="AI492" s="5" t="n"/>
-      <c r="AP492" s="5" t="n"/>
-      <c r="BM492" s="5" t="n"/>
+      <c r="AS492" s="5" t="n"/>
+      <c r="BV492" s="5" t="n"/>
     </row>
     <row r="493">
       <c r="C493" s="5" t="n"/>
@@ -10292,8 +10600,8 @@
       <c r="Y493" s="5" t="n"/>
       <c r="AB493" s="5" t="n"/>
       <c r="AI493" s="5" t="n"/>
-      <c r="AP493" s="5" t="n"/>
-      <c r="BM493" s="5" t="n"/>
+      <c r="AS493" s="5" t="n"/>
+      <c r="BV493" s="5" t="n"/>
     </row>
     <row r="494">
       <c r="C494" s="5" t="n"/>
@@ -10306,8 +10614,8 @@
       <c r="Y494" s="5" t="n"/>
       <c r="AB494" s="5" t="n"/>
       <c r="AI494" s="5" t="n"/>
-      <c r="AP494" s="5" t="n"/>
-      <c r="BM494" s="5" t="n"/>
+      <c r="AS494" s="5" t="n"/>
+      <c r="BV494" s="5" t="n"/>
     </row>
     <row r="495">
       <c r="C495" s="5" t="n"/>
@@ -10320,8 +10628,8 @@
       <c r="Y495" s="5" t="n"/>
       <c r="AB495" s="5" t="n"/>
       <c r="AI495" s="5" t="n"/>
-      <c r="AP495" s="5" t="n"/>
-      <c r="BM495" s="5" t="n"/>
+      <c r="AS495" s="5" t="n"/>
+      <c r="BV495" s="5" t="n"/>
     </row>
     <row r="496">
       <c r="C496" s="5" t="n"/>
@@ -10334,8 +10642,8 @@
       <c r="Y496" s="5" t="n"/>
       <c r="AB496" s="5" t="n"/>
       <c r="AI496" s="5" t="n"/>
-      <c r="AP496" s="5" t="n"/>
-      <c r="BM496" s="5" t="n"/>
+      <c r="AS496" s="5" t="n"/>
+      <c r="BV496" s="5" t="n"/>
     </row>
     <row r="497">
       <c r="C497" s="5" t="n"/>
@@ -10348,8 +10656,8 @@
       <c r="Y497" s="5" t="n"/>
       <c r="AB497" s="5" t="n"/>
       <c r="AI497" s="5" t="n"/>
-      <c r="AP497" s="5" t="n"/>
-      <c r="BM497" s="5" t="n"/>
+      <c r="AS497" s="5" t="n"/>
+      <c r="BV497" s="5" t="n"/>
     </row>
     <row r="498">
       <c r="C498" s="5" t="n"/>
@@ -10362,8 +10670,8 @@
       <c r="Y498" s="5" t="n"/>
       <c r="AB498" s="5" t="n"/>
       <c r="AI498" s="5" t="n"/>
-      <c r="AP498" s="5" t="n"/>
-      <c r="BM498" s="5" t="n"/>
+      <c r="AS498" s="5" t="n"/>
+      <c r="BV498" s="5" t="n"/>
     </row>
     <row r="499">
       <c r="C499" s="5" t="n"/>
@@ -10376,8 +10684,8 @@
       <c r="Y499" s="5" t="n"/>
       <c r="AB499" s="5" t="n"/>
       <c r="AI499" s="5" t="n"/>
-      <c r="AP499" s="5" t="n"/>
-      <c r="BM499" s="5" t="n"/>
+      <c r="AS499" s="5" t="n"/>
+      <c r="BV499" s="5" t="n"/>
     </row>
     <row r="500">
       <c r="C500" s="5" t="n"/>
@@ -10390,8 +10698,8 @@
       <c r="Y500" s="5" t="n"/>
       <c r="AB500" s="5" t="n"/>
       <c r="AI500" s="5" t="n"/>
-      <c r="AP500" s="5" t="n"/>
-      <c r="BM500" s="5" t="n"/>
+      <c r="AS500" s="5" t="n"/>
+      <c r="BV500" s="5" t="n"/>
     </row>
     <row r="501">
       <c r="C501" s="5" t="n"/>
@@ -10404,11 +10712,11 @@
       <c r="Y501" s="5" t="n"/>
       <c r="AB501" s="5" t="n"/>
       <c r="AI501" s="5" t="n"/>
-      <c r="AP501" s="5" t="n"/>
-      <c r="BM501" s="5" t="n"/>
+      <c r="AS501" s="5" t="n"/>
+      <c r="BV501" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="35">
+  <dataValidations count="37">
     <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$A$2:$A$2</formula1>
     </dataValidation>
@@ -10460,59 +10768,65 @@
     <dataValidation sqref="AO2:AO501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$Q$2:$Q$12</formula1>
     </dataValidation>
-    <dataValidation sqref="AQ2:AQ501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AT2:AT501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$R$2:$R$7</formula1>
     </dataValidation>
-    <dataValidation sqref="AR2:AR501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AU2:AU501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$S$2:$S$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AV2:AV501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$T$2:$T$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AT2:AT501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AW2:AW501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$U$2:$U$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AU2:AU501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AX2:AX501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$V$2:$V$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AV2:AV501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AY2:AY501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$W$2:$W$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AW2:AW501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="AZ2:AZ501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$X$2:$X$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BA2:BA501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$Y$2:$Y$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AY2:AY501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BB2:BB501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$Z$2:$Z$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AZ2:AZ501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BC2:BC501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$AA$2:$AA$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BA2:BA501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BD2:BD501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$AB$2:$AB$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BB2:BB501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BE2:BE501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$AC$2:$AC$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BC2:BC501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
-      <formula1>=opsi!$AD$2:$AD$3</formula1>
+    <dataValidation sqref="BF2:BF501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+      <formula1>=opsi!$AD$2:$AD$5</formula1>
     </dataValidation>
-    <dataValidation sqref="BD2:BD501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
-      <formula1>=opsi!$AE$2:$AE$6</formula1>
+    <dataValidation sqref="BI2:BI501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+      <formula1>=opsi!$AE$2:$AE$4</formula1>
     </dataValidation>
-    <dataValidation sqref="BE2:BE501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BL2:BL501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$AF$2:$AF$3</formula1>
     </dataValidation>
-    <dataValidation sqref="BF2:BF501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
-      <formula1>=opsi!$AG$2:$AG$3</formula1>
+    <dataValidation sqref="BM2:BM501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+      <formula1>=opsi!$AG$2:$AG$6</formula1>
     </dataValidation>
-    <dataValidation sqref="BG2:BG501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+    <dataValidation sqref="BN2:BN501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
       <formula1>=opsi!$AH$2:$AH$3</formula1>
     </dataValidation>
-    <dataValidation sqref="CE2:CE501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
-      <formula1>=opsi!$AI$2:$AI$2</formula1>
+    <dataValidation sqref="BO2:BO501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+      <formula1>=opsi!$AI$2:$AI$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="BP2:BP501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+      <formula1>=opsi!$AJ$2:$AJ$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="CN2:CN501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opsi tidak dikenal" error="Pilih salah satu opsi form (teks harus persis)." type="list">
+      <formula1>=opsi!$AK$2:$AK$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10525,7 +10839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE4"/>
+  <dimension ref="A1:CN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10611,6 +10925,15 @@
     <col width="24" customWidth="1" min="81" max="81"/>
     <col width="24" customWidth="1" min="82" max="82"/>
     <col width="24" customWidth="1" min="83" max="83"/>
+    <col width="24" customWidth="1" min="84" max="84"/>
+    <col width="24" customWidth="1" min="85" max="85"/>
+    <col width="24" customWidth="1" min="86" max="86"/>
+    <col width="24" customWidth="1" min="87" max="87"/>
+    <col width="24" customWidth="1" min="88" max="88"/>
+    <col width="24" customWidth="1" min="89" max="89"/>
+    <col width="24" customWidth="1" min="90" max="90"/>
+    <col width="24" customWidth="1" min="91" max="91"/>
+    <col width="24" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1">
@@ -10821,210 +11144,255 @@
       </c>
       <c r="AP1" s="4" t="inlineStr">
         <is>
+          <t>13. d. Apa input yang digunakan?</t>
+        </is>
+      </c>
+      <c r="AQ1" s="4" t="inlineStr">
+        <is>
+          <t>13. e. Bagaimana proses produksinya?</t>
+        </is>
+      </c>
+      <c r="AR1" s="4" t="inlineStr">
+        <is>
+          <t>13. f. Apa produk utama yang dihasilkan?</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
           <t>Pilih dari Master KBLI</t>
         </is>
       </c>
-      <c r="AQ1" s="4" t="inlineStr">
+      <c r="AT1" s="4" t="inlineStr">
         <is>
           <t>14. a. Apa jaringan usaha dari usaha/perusahaan ini?</t>
         </is>
       </c>
-      <c r="AR1" s="4" t="inlineStr">
+      <c r="AU1" s="4" t="inlineStr">
         <is>
           <t>16. a. Apakah usaha/perusahaan ini menggunakan internet dalam menjalankan usaha?</t>
         </is>
       </c>
-      <c r="AS1" s="4" t="inlineStr">
+      <c r="AV1" s="4" t="inlineStr">
         <is>
           <t>16. b1. Menerima pesanan barang/jasa</t>
         </is>
       </c>
-      <c r="AT1" s="4" t="inlineStr">
+      <c r="AW1" s="4" t="inlineStr">
         <is>
           <t>16. b2. Produksi barang/jasa</t>
         </is>
       </c>
-      <c r="AU1" s="4" t="inlineStr">
+      <c r="AX1" s="4" t="inlineStr">
         <is>
           <t>16. b3. Distribusi barang/jasa</t>
         </is>
       </c>
-      <c r="AV1" s="4" t="inlineStr">
+      <c r="AY1" s="4" t="inlineStr">
         <is>
           <t>16. b4. Membeli bahan baku online</t>
         </is>
       </c>
-      <c r="AW1" s="4" t="inlineStr">
+      <c r="AZ1" s="4" t="inlineStr">
         <is>
           <t>16. b5. Promosi</t>
         </is>
       </c>
-      <c r="AX1" s="4" t="inlineStr">
+      <c r="BA1" s="4" t="inlineStr">
         <is>
           <t>16. b6. Lainnya</t>
         </is>
       </c>
-      <c r="AY1" s="4" t="inlineStr">
+      <c r="BB1" s="4" t="inlineStr">
         <is>
           <t>16. c. Apakah usaha/perusahaan ini memanfaatkan teknologi digital Aritifical Intelligence (AI), Internet of Things (IoT), big data, printer 3D, blockchain, atau cloud computing?</t>
         </is>
       </c>
-      <c r="AZ1" s="4" t="inlineStr">
+      <c r="BC1" s="4" t="inlineStr">
         <is>
           <t>17. a. Apakah usaha/perusahaan ini memproduksi barang/jasa yang ramah lingkungan?</t>
         </is>
       </c>
-      <c r="BA1" s="4" t="inlineStr">
+      <c r="BD1" s="4" t="inlineStr">
         <is>
           <t>17. b. Apakah usaha/perusahaan ini menggunakan input untuk tujuan perlindungan lingkungan dan/atau pembelian barang dan jasa yang ramah lingkungan?</t>
         </is>
       </c>
-      <c r="BB1" s="4" t="inlineStr">
+      <c r="BE1" s="4" t="inlineStr">
         <is>
           <t>18. Apakah usaha/perusahaan ini menggunakan produk karya seni, sastra, desain, teknologi atau warisan budaya, baik diproduksi sendiri maupun oleh pihak lain?</t>
         </is>
       </c>
-      <c r="BC1" s="4" t="inlineStr">
+      <c r="BF1" s="4" t="inlineStr">
+        <is>
+          <t>19. a. Apakah usaha/perusahaan ini menghasilkan produk bersertifikat halal?</t>
+        </is>
+      </c>
+      <c r="BG1" s="4" t="inlineStr">
+        <is>
+          <t>19. b. Berapa jumlah varian produk yang sudah bersertifikat halal BPJPH?</t>
+        </is>
+      </c>
+      <c r="BH1" s="4" t="inlineStr">
+        <is>
+          <t>19. c. Berapa jumlah varian produk yang belum bersertifikat halal BPJPH?</t>
+        </is>
+      </c>
+      <c r="BI1" s="4" t="inlineStr">
+        <is>
+          <t>20. a. Apakah usaha/perusahaan ini memiliki izin edar?</t>
+        </is>
+      </c>
+      <c r="BJ1" s="4" t="inlineStr">
+        <is>
+          <t>20. b. Berapa jumlah varian produk yang sudah memiliki izin edar BPOM?</t>
+        </is>
+      </c>
+      <c r="BK1" s="4" t="inlineStr">
+        <is>
+          <t>20. c. Berapa jumlah varian produk yang belum memiliki izin edar BPOM?</t>
+        </is>
+      </c>
+      <c r="BL1" s="4" t="inlineStr">
         <is>
           <t>21. Apakah usaha/perusahaan ini bermitra dengan Koperasi Desa/Kelurahan Merah Putih (KDKMP)?</t>
         </is>
       </c>
-      <c r="BD1" s="4" t="inlineStr">
+      <c r="BM1" s="4" t="inlineStr">
         <is>
           <t>22. Apakah usaha/perusahaan ini terlibat dalam program Makan Bergizi Gratis (MBG)?</t>
         </is>
       </c>
-      <c r="BE1" s="4" t="inlineStr">
+      <c r="BN1" s="4" t="inlineStr">
         <is>
           <t>23. a. Penjualan dan/atau pembelian barang</t>
         </is>
       </c>
-      <c r="BF1" s="4" t="inlineStr">
+      <c r="BO1" s="4" t="inlineStr">
         <is>
           <t>23. b. Penjualan jasa</t>
         </is>
       </c>
-      <c r="BG1" s="4" t="inlineStr">
+      <c r="BP1" s="4" t="inlineStr">
         <is>
           <t>23. c. Pembelian jasa</t>
         </is>
       </c>
-      <c r="BH1" s="4" t="inlineStr">
+      <c r="BQ1" s="4" t="inlineStr">
         <is>
           <t>24. a1. Pekerja laki-laki</t>
         </is>
       </c>
-      <c r="BI1" s="4" t="inlineStr">
+      <c r="BR1" s="4" t="inlineStr">
         <is>
           <t>24. b1. Pekerja perempuan</t>
         </is>
       </c>
-      <c r="BJ1" s="4" t="inlineStr">
+      <c r="BS1" s="4" t="inlineStr">
         <is>
           <t>24. a2. Pekerja dibayar</t>
         </is>
       </c>
-      <c r="BK1" s="4" t="inlineStr">
+      <c r="BT1" s="4" t="inlineStr">
         <is>
           <t>24. b2. Pekerja tidak dibayar</t>
         </is>
       </c>
-      <c r="BL1" s="4" t="inlineStr">
+      <c r="BU1" s="4" t="inlineStr">
         <is>
           <t>25. Tahun berapa usaha/perusahaan ini mulai beroperasi secara komersial?</t>
         </is>
       </c>
-      <c r="BM1" s="4" t="inlineStr">
+      <c r="BV1" s="4" t="inlineStr">
         <is>
           <t>idsubsls</t>
         </is>
       </c>
-      <c r="BN1" s="4" t="inlineStr">
+      <c r="BW1" s="4" t="inlineStr">
         <is>
           <t>26. a. Total upah dan gaji, serta jaminan sosial pegawai</t>
         </is>
       </c>
-      <c r="BO1" s="4" t="inlineStr">
+      <c r="BX1" s="4" t="inlineStr">
         <is>
           <t>26. b. Biaya produksi</t>
         </is>
       </c>
-      <c r="BP1" s="4" t="inlineStr">
+      <c r="BY1" s="4" t="inlineStr">
         <is>
           <t>26. c. Biaya pembelian barang yang terjual</t>
         </is>
       </c>
-      <c r="BQ1" s="4" t="inlineStr">
+      <c r="BZ1" s="4" t="inlineStr">
         <is>
           <t>26. d. Biaya operasional (air, listrik, gas, internet, pulsa, pemeliharaan, biaya angkutan, dll.)</t>
         </is>
       </c>
-      <c r="BR1" s="4" t="inlineStr">
+      <c r="CA1" s="4" t="inlineStr">
         <is>
           <t>26. e. Biaya non-operasional</t>
         </is>
       </c>
-      <c r="BS1" s="4" t="inlineStr">
+      <c r="CB1" s="4" t="inlineStr">
         <is>
           <t>27. a. Nilai produksi/pendapatan/penjualan barang dan jasa</t>
         </is>
       </c>
-      <c r="BT1" s="4" t="inlineStr">
+      <c r="CC1" s="4" t="inlineStr">
         <is>
           <t>27. b. Pendapatan lainnya yang dihasilkan perusahaan</t>
         </is>
       </c>
-      <c r="BU1" s="4" t="inlineStr">
+      <c r="CD1" s="4" t="inlineStr">
         <is>
           <t>27. d. Berapa persentase pendapatan yang dilakukan secara online ?</t>
         </is>
       </c>
-      <c r="BV1" s="4" t="inlineStr">
+      <c r="CE1" s="4" t="inlineStr">
         <is>
           <t>28. a. Nilai aset tanah dan bangunan pada 31 Desember 2025</t>
         </is>
       </c>
-      <c r="BW1" s="4" t="inlineStr">
+      <c r="CF1" s="4" t="inlineStr">
         <is>
           <t>28. b. Nilai aset selain tanah dan bangunan pada 31 Desember 2025</t>
         </is>
       </c>
-      <c r="BX1" s="4" t="inlineStr">
+      <c r="CG1" s="4" t="inlineStr">
         <is>
           <t>28. d. Berapa luas tanah yang dikuasai dan digunakan untuk kegiatan usaha pada 31 Desember 2025 ? (m2)</t>
         </is>
       </c>
-      <c r="BY1" s="4" t="inlineStr">
+      <c r="CH1" s="4" t="inlineStr">
         <is>
           <t>29. a. Pribadi/Perorangan</t>
         </is>
       </c>
-      <c r="BZ1" s="4" t="inlineStr">
+      <c r="CI1" s="4" t="inlineStr">
         <is>
           <t>29. b. Lembaga Nonprofit yang Melayani Rumah Tangga</t>
         </is>
       </c>
-      <c r="CA1" s="4" t="inlineStr">
+      <c r="CJ1" s="4" t="inlineStr">
         <is>
           <t>29. c. Korporasi Publik</t>
         </is>
       </c>
-      <c r="CB1" s="4" t="inlineStr">
+      <c r="CK1" s="4" t="inlineStr">
         <is>
           <t>29. d. Korporasi Non Publik</t>
         </is>
       </c>
-      <c r="CC1" s="4" t="inlineStr">
+      <c r="CL1" s="4" t="inlineStr">
         <is>
           <t>29. e. Pemerintah</t>
         </is>
       </c>
-      <c r="CD1" s="4" t="inlineStr">
+      <c r="CM1" s="4" t="inlineStr">
         <is>
           <t>29. f. Asing</t>
         </is>
       </c>
-      <c r="CE1" s="4" t="inlineStr">
+      <c r="CN1" s="4" t="inlineStr">
         <is>
           <t>Nama Pemberi Informasi</t>
         </is>
@@ -11127,7 +11495,11 @@
           <t>115.200</t>
         </is>
       </c>
-      <c r="U2" s="6" t="inlineStr"/>
+      <c r="U2" s="6" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
       <c r="V2" s="6" t="inlineStr">
         <is>
           <t>2. Baru</t>
@@ -11220,193 +11592,636 @@
           <t>4. Toko, ruko, dan sejenisnya</t>
         </is>
       </c>
-      <c r="AP2" s="7" t="inlineStr">
+      <c r="AP2" s="6" t="inlineStr"/>
+      <c r="AQ2" s="6" t="inlineStr"/>
+      <c r="AR2" s="6" t="inlineStr">
+        <is>
+          <t>Makanan ringan dan minuman kemasan</t>
+        </is>
+      </c>
+      <c r="AS2" s="7" t="inlineStr">
         <is>
           <t>47112</t>
         </is>
       </c>
-      <c r="AQ2" s="6" t="inlineStr">
+      <c r="AT2" s="6" t="inlineStr">
         <is>
           <t>1. Tunggal</t>
         </is>
       </c>
-      <c r="AR2" s="6" t="inlineStr">
+      <c r="AU2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="AS2" s="6" t="inlineStr"/>
-      <c r="AT2" s="6" t="inlineStr"/>
-      <c r="AU2" s="6" t="inlineStr"/>
       <c r="AV2" s="6" t="inlineStr"/>
       <c r="AW2" s="6" t="inlineStr"/>
       <c r="AX2" s="6" t="inlineStr"/>
       <c r="AY2" s="6" t="inlineStr"/>
-      <c r="AZ2" s="6" t="inlineStr">
+      <c r="AZ2" s="6" t="inlineStr"/>
+      <c r="BA2" s="6" t="inlineStr"/>
+      <c r="BB2" s="6" t="inlineStr"/>
+      <c r="BC2" s="6" t="inlineStr">
         <is>
           <t>3. Tidak sama sekali</t>
         </is>
       </c>
-      <c r="BA2" s="6" t="inlineStr">
+      <c r="BD2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="BB2" s="6" t="inlineStr">
+      <c r="BE2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="BC2" s="6" t="inlineStr">
+      <c r="BF2" s="6" t="inlineStr">
+        <is>
+          <t>3. Tidak/Belum</t>
+        </is>
+      </c>
+      <c r="BG2" s="6" t="inlineStr"/>
+      <c r="BH2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI2" s="6" t="inlineStr">
+        <is>
+          <t>3. Tidak</t>
+        </is>
+      </c>
+      <c r="BJ2" s="6" t="inlineStr"/>
+      <c r="BK2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="BD2" s="6" t="inlineStr">
+      <c r="BM2" s="6" t="inlineStr">
         <is>
           <t>5. Tidak terlibat MBG</t>
         </is>
       </c>
-      <c r="BE2" s="6" t="inlineStr">
+      <c r="BN2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="BF2" s="6" t="inlineStr">
+      <c r="BO2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="BG2" s="6" t="inlineStr">
+      <c r="BP2" s="6" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="BH2" s="6" t="inlineStr">
+      <c r="BQ2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BI2" s="6" t="inlineStr">
+      <c r="BR2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BJ2" s="6" t="inlineStr">
+      <c r="BS2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BK2" s="6" t="inlineStr">
+      <c r="BT2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL2" s="6" t="inlineStr">
+      <c r="BU2" s="6" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="BM2" s="7" t="inlineStr">
+      <c r="BV2" s="7" t="inlineStr">
         <is>
           <t>5108080008000202</t>
         </is>
       </c>
-      <c r="BN2" s="6" t="inlineStr">
+      <c r="BW2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BO2" s="6" t="inlineStr">
+      <c r="BX2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BP2" s="6" t="inlineStr">
+      <c r="BY2" s="6" t="inlineStr">
         <is>
           <t>4000000</t>
         </is>
       </c>
-      <c r="BQ2" s="6" t="inlineStr">
+      <c r="BZ2" s="6" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="BR2" s="6" t="inlineStr">
+      <c r="CA2" s="6" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="BS2" s="6" t="inlineStr">
+      <c r="CB2" s="6" t="inlineStr">
         <is>
           <t>6000000</t>
         </is>
       </c>
-      <c r="BT2" s="6" t="inlineStr">
+      <c r="CC2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BU2" s="6" t="inlineStr">
+      <c r="CD2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BV2" s="6" t="inlineStr">
+      <c r="CE2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BW2" s="6" t="inlineStr">
+      <c r="CF2" s="6" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
       </c>
-      <c r="BX2" s="6" t="inlineStr">
+      <c r="CG2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BY2" s="6" t="inlineStr">
+      <c r="CH2" s="6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="BZ2" s="6" t="inlineStr">
+      <c r="CI2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CA2" s="6" t="inlineStr">
+      <c r="CJ2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CB2" s="6" t="inlineStr">
+      <c r="CK2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC2" s="6" t="inlineStr">
+      <c r="CL2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CD2" s="6" t="inlineStr">
+      <c r="CM2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CE2" s="6" t="inlineStr">
+      <c r="CN2" s="6" t="inlineStr">
         <is>
           <t>Lainnya</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Baris kuning di atas FIKTIF — hanya contoh bentuk isian. Skrip hanya membaca tab 'gabungan'.</t>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>pml.contoh@gmail.com</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>ppl.contoh@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>KERIPIK CONTOH</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>81172</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Bangunan Lainnya (Selain Tempat Tinggal dan Campuran)</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>KERIPIK CONTOH</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>2. Baru</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>BANJAR DINAS KAJA KANGIN</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>1. Bangunan Khusus Usaha</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>-8.129</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>115.200</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>Tidak Ada</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>2. Baru</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>KERIPIK CONTOH</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>BANJAR DINAS KAJA KANGIN, Desa/Kel. TAMBLANG, Kec. KUBUTAMBAHAN, BULELENG, BALI, 81172</t>
+        </is>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>081200000000</t>
+        </is>
+      </c>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>10. Di luar kawasan</t>
+        </is>
+      </c>
+      <c r="AA3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="AB3" s="7" t="inlineStr"/>
+      <c r="AC3" s="6" t="inlineStr">
+        <is>
+          <t>3. Tidak memerlukan NIB</t>
+        </is>
+      </c>
+      <c r="AD3" s="6" t="inlineStr">
+        <is>
+          <t>13. Bukan Badan Usaha</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="AF3" s="6" t="inlineStr">
+        <is>
+          <t>NI MADE CONTOH</t>
+        </is>
+      </c>
+      <c r="AG3" s="6" t="inlineStr">
+        <is>
+          <t>2. Perempuan</t>
+        </is>
+      </c>
+      <c r="AH3" s="6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AI3" s="7" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="AJ3" s="6" t="inlineStr">
+        <is>
+          <t>Membuat keripik singkong</t>
+        </is>
+      </c>
+      <c r="AK3" s="6" t="inlineStr">
+        <is>
+          <t>1. Ya</t>
+        </is>
+      </c>
+      <c r="AL3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="inlineStr">
+        <is>
+          <t>1. Ya</t>
+        </is>
+      </c>
+      <c r="AN3" s="6" t="inlineStr"/>
+      <c r="AO3" s="6" t="inlineStr">
+        <is>
+          <t>4. Toko, ruko, dan sejenisnya</t>
+        </is>
+      </c>
+      <c r="AP3" s="6" t="inlineStr">
+        <is>
+          <t>Singkong, minyak goreng, bumbu</t>
+        </is>
+      </c>
+      <c r="AQ3" s="6" t="inlineStr">
+        <is>
+          <t>Mengupas, mengiris, menggoreng, dan mengemas</t>
+        </is>
+      </c>
+      <c r="AR3" s="6" t="inlineStr">
+        <is>
+          <t>Keripik singkong</t>
+        </is>
+      </c>
+      <c r="AS3" s="7" t="inlineStr">
+        <is>
+          <t>10794</t>
+        </is>
+      </c>
+      <c r="AT3" s="6" t="inlineStr">
+        <is>
+          <t>1. Tunggal</t>
+        </is>
+      </c>
+      <c r="AU3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="AV3" s="6" t="inlineStr"/>
+      <c r="AW3" s="6" t="inlineStr"/>
+      <c r="AX3" s="6" t="inlineStr"/>
+      <c r="AY3" s="6" t="inlineStr"/>
+      <c r="AZ3" s="6" t="inlineStr"/>
+      <c r="BA3" s="6" t="inlineStr"/>
+      <c r="BB3" s="6" t="inlineStr"/>
+      <c r="BC3" s="6" t="inlineStr">
+        <is>
+          <t>3. Tidak sama sekali</t>
+        </is>
+      </c>
+      <c r="BD3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="BE3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="BF3" s="6" t="inlineStr">
+        <is>
+          <t>3. Tidak/Belum</t>
+        </is>
+      </c>
+      <c r="BG3" s="6" t="inlineStr"/>
+      <c r="BH3" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI3" s="6" t="inlineStr">
+        <is>
+          <t>3. Tidak</t>
+        </is>
+      </c>
+      <c r="BJ3" s="6" t="inlineStr"/>
+      <c r="BK3" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="BM3" s="6" t="inlineStr">
+        <is>
+          <t>5. Tidak terlibat MBG</t>
+        </is>
+      </c>
+      <c r="BN3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="BO3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="BP3" s="6" t="inlineStr">
+        <is>
+          <t>2. Tidak</t>
+        </is>
+      </c>
+      <c r="BQ3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BS3" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BT3" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU3" s="6" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="BV3" s="7" t="inlineStr">
+        <is>
+          <t>5108080008000202</t>
+        </is>
+      </c>
+      <c r="BW3" s="6" t="inlineStr">
+        <is>
+          <t>2400000</t>
+        </is>
+      </c>
+      <c r="BX3" s="6" t="inlineStr">
+        <is>
+          <t>3500000</t>
+        </is>
+      </c>
+      <c r="BY3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" s="6" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="CA3" s="6" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="CB3" s="6" t="inlineStr">
+        <is>
+          <t>9000000</t>
+        </is>
+      </c>
+      <c r="CC3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CD3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CE3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CF3" s="6" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+      <c r="CG3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CH3" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="CI3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CL3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CM3" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CN3" s="6" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Baris kuning di atas FIKTIF — contoh bentuk isian usaha perdagangan (baris 2) dan usaha produksi (baris 3). Skrip hanya membaca tab 'input_usaha'.</t>
         </is>
       </c>
     </row>
@@ -16993,7 +17808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17144,30 +17959,40 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>halal</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>izin_edar</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>mitra_kdkmp</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>peran_mbg</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>barang_non_pddk</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>jasa_non_pddk</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>beli_jasa_non_pddk</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>nama_info_list</t>
         </is>
@@ -17321,30 +18146,40 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>1. Ya, oleh BPJPH</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>1. Ya, oleh BPOM</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>1. Ya</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1. Ya, sebagai SATUAN PELAYANAN PEMENUHAN GIZI (SPPG)</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>1. Ya</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>1. Ya</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>1. Ya</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>Lainnya</t>
         </is>
@@ -17468,25 +18303,35 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>2. Ya, bukan oleh BPJPH</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2. Ya, bukan oleh BPOM</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>2. Ya, sebagai supplier</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2. Tidak</t>
         </is>
@@ -17523,7 +18368,17 @@
           <t>3. Tidak sama sekali</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>3. Tidak/Belum</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr">
+        <is>
+          <t>3. Tidak</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>3. Ya, sebagai penerima manfaat MBG (Sekolah, Puskesmas)</t>
         </is>
@@ -17555,7 +18410,12 @@
           <t>4. Perwakilan</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>4. Dalam proses</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>4. Ya, peran lainnya</t>
         </is>
@@ -17587,7 +18447,7 @@
           <t>5. Pabrik</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>5. Tidak terlibat MBG</t>
         </is>
